--- a/outputs/models/tables/all_model_metrics.xlsx
+++ b/outputs/models/tables/all_model_metrics.xlsx
@@ -29,14 +29,13 @@
     <sheet name="metrics__Gaussian Process Regre" sheetId="20" r:id="rId20"/>
     <sheet name="metrics__Extreme Gradient Boost" sheetId="21" r:id="rId21"/>
     <sheet name="metrics__Light Gradient Boostin" sheetId="22" r:id="rId22"/>
-    <sheet name="metrics__Categorical Boosting" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="44">
   <si>
     <t>model</t>
   </si>
@@ -59,37 +58,40 @@
     <t>rank_by_overall_rmse</t>
   </si>
   <si>
+    <t>Gradient Boosting</t>
+  </si>
+  <si>
+    <t>Gaussian Process Regression</t>
+  </si>
+  <si>
+    <t>Adaptive Boosting</t>
+  </si>
+  <si>
     <t>Extra Trees</t>
+  </si>
+  <si>
+    <t>K Nearest Neighbors Five</t>
+  </si>
+  <si>
+    <t>K Nearest Neighbors Three</t>
+  </si>
+  <si>
+    <t>Bagging Regressor</t>
+  </si>
+  <si>
+    <t>Polynomial Regression Degree 3</t>
   </si>
   <si>
     <t>Decision Tree</t>
   </si>
   <si>
-    <t>Gaussian Process Regression</t>
+    <t>Polynomial Ridge Degree 3</t>
   </si>
   <si>
-    <t>Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Extreme Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Categorical Boosting</t>
+    <t>Support Vector Regression</t>
   </si>
   <si>
     <t>Random Forest</t>
-  </si>
-  <si>
-    <t>Bagging Regressor</t>
-  </si>
-  <si>
-    <t>Adaptive Boosting</t>
-  </si>
-  <si>
-    <t>Polynomial Regression Degree 3</t>
-  </si>
-  <si>
-    <t>Polynomial Ridge Degree 3</t>
   </si>
   <si>
     <t>Polynomial Regression Degree 2</t>
@@ -101,6 +103,9 @@
     <t>Linear Regression</t>
   </si>
   <si>
+    <t>Extreme Gradient Boosting</t>
+  </si>
+  <si>
     <t>Lasso Regression</t>
   </si>
   <si>
@@ -110,19 +115,10 @@
     <t>Ridge Regression</t>
   </si>
   <si>
-    <t>K Nearest Neighbors Five</t>
-  </si>
-  <si>
     <t>Histogram Gradient Boosting</t>
   </si>
   <si>
     <t>Light Gradient Boosting</t>
-  </si>
-  <si>
-    <t>Support Vector Regression</t>
-  </si>
-  <si>
-    <t>K Nearest Neighbors Three</t>
   </si>
   <si>
     <t>Stochastic Gradient Regression</t>
@@ -528,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -559,19 +555,19 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>36.50209694989105</v>
+        <v>3.168732906387079</v>
       </c>
       <c r="C2">
-        <v>56.46363727902722</v>
+        <v>6.525074842751619</v>
       </c>
       <c r="D2">
-        <v>0.3115079787479607</v>
+        <v>0.9455637350402234</v>
       </c>
       <c r="E2">
-        <v>0.2974571211713884</v>
+        <v>0.9395152611558036</v>
       </c>
       <c r="F2">
-        <v>43.96871790144956</v>
+        <v>9.736368691795033</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -582,19 +578,19 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>36.50209694989107</v>
+        <v>3.929159497152678</v>
       </c>
       <c r="C3">
-        <v>56.46363727902722</v>
+        <v>6.822468374053738</v>
       </c>
       <c r="D3">
-        <v>0.3115079787479607</v>
+        <v>0.9420084422883457</v>
       </c>
       <c r="E3">
-        <v>0.2974571211713884</v>
+        <v>0.9355649358759397</v>
       </c>
       <c r="F3">
-        <v>43.96871790144958</v>
+        <v>15.47612307072269</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -605,19 +601,19 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>36.50211144577678</v>
+        <v>3.803787878787881</v>
       </c>
       <c r="C4">
-        <v>56.46363727973788</v>
+        <v>7.100246612458202</v>
       </c>
       <c r="D4">
-        <v>0.3115079787302062</v>
+        <v>0.9339239374684735</v>
       </c>
       <c r="E4">
-        <v>0.2974571211532717</v>
+        <v>0.9265821527427482</v>
       </c>
       <c r="F4">
-        <v>43.96879424143795</v>
+        <v>10.00170950606536</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -628,19 +624,19 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>36.62474727363456</v>
+        <v>5.775431818181824</v>
       </c>
       <c r="C5">
-        <v>56.46469020353801</v>
+        <v>7.822140196304651</v>
       </c>
       <c r="D5">
-        <v>0.3114797871300989</v>
+        <v>0.9190809984302347</v>
       </c>
       <c r="E5">
-        <v>0.2974283542143867</v>
+        <v>0.9100899982558164</v>
       </c>
       <c r="F5">
-        <v>44.17276238103285</v>
+        <v>15.62301835777778</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -651,19 +647,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>36.68221718881645</v>
+        <v>3.220000000000001</v>
       </c>
       <c r="C6">
-        <v>56.47065577776298</v>
+        <v>8.079737322128098</v>
       </c>
       <c r="D6">
-        <v>0.311307091678354</v>
+        <v>0.9010022116065129</v>
       </c>
       <c r="E6">
-        <v>0.2972521343656674</v>
+        <v>0.89000245734057</v>
       </c>
       <c r="F6">
-        <v>44.06025933190316</v>
+        <v>6.552485325108222</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -674,19 +670,19 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>37.0774817460043</v>
+        <v>3.220000000000001</v>
       </c>
       <c r="C7">
-        <v>56.4823468839188</v>
+        <v>8.079737322128098</v>
       </c>
       <c r="D7">
-        <v>0.3109246067679114</v>
+        <v>0.9010022116065129</v>
       </c>
       <c r="E7">
-        <v>0.296861843640726</v>
+        <v>0.89000245734057</v>
       </c>
       <c r="F7">
-        <v>45.0521131016635</v>
+        <v>6.552485325108222</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -697,19 +693,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>40.12439201168747</v>
+        <v>6.724683766233768</v>
       </c>
       <c r="C8">
-        <v>57.22694292073815</v>
+        <v>9.014969095534857</v>
       </c>
       <c r="D8">
-        <v>0.2767615784138001</v>
+        <v>0.8883535513059304</v>
       </c>
       <c r="E8">
-        <v>0.2620016106263267</v>
+        <v>0.8759483903399227</v>
       </c>
       <c r="F8">
-        <v>52.48748353112757</v>
+        <v>14.80270446040569</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -720,19 +716,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>40.26839203969183</v>
+        <v>9.687263572354752</v>
       </c>
       <c r="C9">
-        <v>57.30588946629285</v>
+        <v>13.87049345667331</v>
       </c>
       <c r="D9">
-        <v>0.2697306555574985</v>
+        <v>0.602676471343589</v>
       </c>
       <c r="E9">
-        <v>0.2548271995484679</v>
+        <v>0.4323949590622701</v>
       </c>
       <c r="F9">
-        <v>52.08331988037873</v>
+        <v>19.7105839430405</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -743,19 +739,19 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>41.37632478835862</v>
+        <v>10.83068181818182</v>
       </c>
       <c r="C10">
-        <v>58.6155208638399</v>
+        <v>13.99155594877365</v>
       </c>
       <c r="D10">
-        <v>0.2413618016134406</v>
+        <v>0.6394045833539457</v>
       </c>
       <c r="E10">
-        <v>0.22587938940147</v>
+        <v>0.5993384259488284</v>
       </c>
       <c r="F10">
-        <v>53.47012151600998</v>
+        <v>22.80088606951673</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -766,19 +762,19 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>45.93310218664039</v>
+        <v>10.18948263078555</v>
       </c>
       <c r="C11">
-        <v>61.46651043144696</v>
+        <v>14.08231914778145</v>
       </c>
       <c r="D11">
-        <v>0.125344235740491</v>
+        <v>0.596743573226068</v>
       </c>
       <c r="E11">
-        <v>0.06951514440477766</v>
+        <v>0.4239193903229541</v>
       </c>
       <c r="F11">
-        <v>75.84562028343396</v>
+        <v>21.76325676280162</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -789,19 +785,19 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>45.83368966291799</v>
+        <v>8.160169082257129</v>
       </c>
       <c r="C12">
-        <v>61.73859126927061</v>
+        <v>14.79953532527325</v>
       </c>
       <c r="D12">
-        <v>0.117006433491492</v>
+        <v>0.5514224295634942</v>
       </c>
       <c r="E12">
-        <v>0.06064514201222548</v>
+        <v>0.5015804772927714</v>
       </c>
       <c r="F12">
-        <v>77.71204418012663</v>
+        <v>15.128891198559</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -812,19 +808,19 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>47.58581699448067</v>
+        <v>11.0568203838243</v>
       </c>
       <c r="C13">
-        <v>62.82814994632612</v>
+        <v>14.93980984405228</v>
       </c>
       <c r="D13">
-        <v>0.08167729649806676</v>
+        <v>0.6035202991550379</v>
       </c>
       <c r="E13">
-        <v>0.04341385051881955</v>
+        <v>0.5594669990611532</v>
       </c>
       <c r="F13">
-        <v>82.03919656927027</v>
+        <v>25.36427941689524</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -835,19 +831,19 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>47.36162114757483</v>
+        <v>13.70488226603412</v>
       </c>
       <c r="C14">
-        <v>62.84394243278399</v>
+        <v>16.96819961741376</v>
       </c>
       <c r="D14">
-        <v>0.08140270925934742</v>
+        <v>0.5068381739464329</v>
       </c>
       <c r="E14">
-        <v>0.04312782214515359</v>
+        <v>0.3835477174330411</v>
       </c>
       <c r="F14">
-        <v>81.38673994146862</v>
+        <v>31.19930956978714</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -858,19 +854,19 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>47.88620327402283</v>
+        <v>13.29933925905086</v>
       </c>
       <c r="C15">
-        <v>63.48626724091056</v>
+        <v>17.11935361275002</v>
       </c>
       <c r="D15">
-        <v>0.06333200850025808</v>
+        <v>0.4991561221423056</v>
       </c>
       <c r="E15">
-        <v>0.04421633520434498</v>
+        <v>0.3739451526778821</v>
       </c>
       <c r="F15">
-        <v>84.11703649434362</v>
+        <v>31.17984184084805</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -881,19 +877,19 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>47.8862242804854</v>
+        <v>14.26188733626295</v>
       </c>
       <c r="C16">
-        <v>63.48626725895862</v>
+        <v>18.50032274622348</v>
       </c>
       <c r="D16">
-        <v>0.06333200652419671</v>
+        <v>0.4291297958482495</v>
       </c>
       <c r="E16">
-        <v>0.04421633318795581</v>
+        <v>0.3656997731647216</v>
       </c>
       <c r="F16">
-        <v>84.11720260021775</v>
+        <v>35.28442817873522</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -904,19 +900,19 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>47.88695737276996</v>
+        <v>13.59132550326261</v>
       </c>
       <c r="C17">
-        <v>63.4862680821951</v>
+        <v>18.51985693081643</v>
       </c>
       <c r="D17">
-        <v>0.06333198969521825</v>
+        <v>0.5366126757423844</v>
       </c>
       <c r="E17">
-        <v>0.04421631601552883</v>
+        <v>0.485125195269316</v>
       </c>
       <c r="F17">
-        <v>84.12050988761703</v>
+        <v>35.8066922066379</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -927,19 +923,19 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>47.91481760345432</v>
+        <v>14.81590317265144</v>
       </c>
       <c r="C18">
-        <v>63.48742364228924</v>
+        <v>18.63968098754708</v>
       </c>
       <c r="D18">
-        <v>0.06330858689948143</v>
+        <v>0.413695775824967</v>
       </c>
       <c r="E18">
-        <v>0.04419243561171576</v>
+        <v>0.3485508620277411</v>
       </c>
       <c r="F18">
-        <v>84.2475009956124</v>
+        <v>36.757147188602</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -950,19 +946,19 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>45.39443137254902</v>
+        <v>18.5023261265749</v>
       </c>
       <c r="C19">
-        <v>66.13774847857172</v>
+        <v>24.1289274519747</v>
       </c>
       <c r="D19">
-        <v>0.04351266423337941</v>
+        <v>0.188873342686506</v>
       </c>
       <c r="E19">
-        <v>0.02399251452385656</v>
+        <v>0.09874815854056221</v>
       </c>
       <c r="F19">
-        <v>50.12863096442569</v>
+        <v>51.67758791843703</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -973,19 +969,19 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>50.80627450980393</v>
+        <v>20.81129154393988</v>
       </c>
       <c r="C20">
-        <v>66.50887338988493</v>
+        <v>27.49656691612221</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.001287141375970385</v>
       </c>
       <c r="E20">
-        <v>-0.02040816326530615</v>
+        <v>-0.1096809540266996</v>
       </c>
       <c r="F20">
-        <v>94.71910521263098</v>
+        <v>59.64493902013724</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -996,19 +992,19 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>50.8062745328758</v>
+        <v>20.82553719008264</v>
       </c>
       <c r="C21">
-        <v>66.50887338988493</v>
+        <v>27.51682461542172</v>
       </c>
       <c r="D21">
-        <v>-2.775557561562891E-17</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="F21">
-        <v>94.7191052054969</v>
+        <v>59.69155634320034</v>
       </c>
       <c r="G21">
         <v>20</v>
@@ -1019,19 +1015,19 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>46.35987000354851</v>
+        <v>20.82553719540273</v>
       </c>
       <c r="C22">
-        <v>67.26150972584821</v>
+        <v>27.51682461542173</v>
       </c>
       <c r="D22">
-        <v>-0.01859041019230226</v>
+        <v>-2.220446049250313E-16</v>
       </c>
       <c r="E22">
-        <v>-0.03937796958398188</v>
+        <v>-0.1111111111111114</v>
       </c>
       <c r="F22">
-        <v>72.17358518780009</v>
+        <v>59.69155641166542</v>
       </c>
       <c r="G22">
         <v>21</v>
@@ -1042,45 +1038,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>48.53196078431372</v>
+        <v>65.49041319640749</v>
       </c>
       <c r="C23">
-        <v>72.61990078769972</v>
+        <v>70.31822686371589</v>
       </c>
       <c r="D23">
-        <v>-0.1520182671638045</v>
+        <v>-10.41255790285233</v>
       </c>
       <c r="E23">
-        <v>-0.1755288440446985</v>
+        <v>-11.68061989205815</v>
       </c>
       <c r="F23">
-        <v>46.62395849637755</v>
+        <v>43.18148569896135</v>
       </c>
       <c r="G23">
         <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24">
-        <v>75.64417524649492</v>
-      </c>
-      <c r="C24">
-        <v>96.78816194033985</v>
-      </c>
-      <c r="D24">
-        <v>-0.8556777918946106</v>
-      </c>
-      <c r="E24">
-        <v>-0.8935487672393984</v>
-      </c>
-      <c r="F24">
-        <v>52.23996267027817</v>
-      </c>
-      <c r="G24">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1095,176 +1068,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>77.81013071895424</v>
+        <v>13.25454545454546</v>
       </c>
       <c r="C2">
-        <v>13901.53931742919</v>
+        <v>246.4873454545454</v>
       </c>
       <c r="D2">
-        <v>117.9047892048037</v>
+        <v>15.69991546010823</v>
       </c>
       <c r="E2">
-        <v>0.2429688145716846</v>
+        <v>0.8843113761068258</v>
       </c>
       <c r="F2">
-        <v>0.2275191985425353</v>
+        <v>0.8714570845631397</v>
       </c>
       <c r="G2">
-        <v>103.6107947827784</v>
+        <v>66.72422293708199</v>
       </c>
       <c r="H2">
-        <v>77.66944444444442</v>
+        <v>9.340000000000002</v>
       </c>
       <c r="I2">
-        <v>0.2429688145716846</v>
+        <v>0.8843113761068258</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8.623965141612203</v>
+        <v>5.054545454545456</v>
       </c>
       <c r="C3">
-        <v>159.2006318082788</v>
+        <v>45.89818181818183</v>
       </c>
       <c r="D3">
-        <v>12.61747327353139</v>
+        <v>6.774819688979318</v>
       </c>
       <c r="E3">
-        <v>0.3179943591466978</v>
+        <v>0.4543017725897102</v>
       </c>
       <c r="F3">
-        <v>0.3040758766803039</v>
+        <v>0.3936686362107891</v>
       </c>
       <c r="G3">
-        <v>18.73177856428489</v>
+        <v>7.829599500681778</v>
       </c>
       <c r="H3">
-        <v>6.327777777777783</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0.3179943591466978</v>
+        <v>0.4543017725897103</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>50.45969498910675</v>
+        <v>18.80636363636364</v>
       </c>
       <c r="C4">
-        <v>6717.559978213508</v>
+        <v>710.0305</v>
       </c>
       <c r="D4">
-        <v>81.96072216747183</v>
+        <v>26.64639750510376</v>
       </c>
       <c r="E4">
-        <v>0.3041163615888186</v>
+        <v>0.3103237277299765</v>
       </c>
       <c r="F4">
-        <v>0.289914654682468</v>
+        <v>0.2336930308110851</v>
       </c>
       <c r="G4">
-        <v>39.56422819156138</v>
+        <v>7.686864203472761</v>
       </c>
       <c r="H4">
-        <v>27.90555555555557</v>
+        <v>7.279999999999973</v>
       </c>
       <c r="I4">
-        <v>0.3041163615888186</v>
+        <v>0.3103237277299765</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>9.114596949891068</v>
+        <v>6.207272727272727</v>
       </c>
       <c r="C5">
-        <v>178.7987363834422</v>
+        <v>46.85527272727272</v>
       </c>
       <c r="D5">
-        <v>13.37156447030198</v>
+        <v>6.845091140903291</v>
       </c>
       <c r="E5">
-        <v>0.3809523796846417</v>
+        <v>0.9086814569892698</v>
       </c>
       <c r="F5">
-        <v>0.3683187547802467</v>
+        <v>0.8985349522102998</v>
       </c>
       <c r="G5">
-        <v>13.96807006717371</v>
+        <v>8.962857636830362</v>
       </c>
       <c r="H5">
-        <v>7.011111111111106</v>
+        <v>5.679999999999993</v>
       </c>
       <c r="I5">
-        <v>0.3809523796846418</v>
+        <v>0.9086814569892698</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>36.50209694989107</v>
+        <v>10.83068181818182</v>
       </c>
       <c r="C6">
-        <v>5239.274665958606</v>
+        <v>262.317825</v>
       </c>
       <c r="D6">
-        <v>56.46363727902722</v>
+        <v>13.99155594877365</v>
       </c>
       <c r="E6">
-        <v>0.3115079787479607</v>
+        <v>0.6394045833539457</v>
       </c>
       <c r="F6">
-        <v>0.2974571211713884</v>
+        <v>0.5993384259488284</v>
       </c>
       <c r="G6">
-        <v>43.96871790144958</v>
+        <v>22.80088606951673</v>
       </c>
       <c r="H6">
-        <v>29.72847222222222</v>
+        <v>6.324999999999992</v>
       </c>
       <c r="I6">
-        <v>0.3115079787479607</v>
+        <v>0.6394045833539457</v>
       </c>
     </row>
   </sheetData>
@@ -1279,176 +1252,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>82.56287306992496</v>
+        <v>13.97605639615074</v>
       </c>
       <c r="C2">
-        <v>14045.43264087969</v>
+        <v>307.3139954052415</v>
       </c>
       <c r="D2">
-        <v>118.5134281036528</v>
+        <v>17.53037351014637</v>
       </c>
       <c r="E2">
-        <v>0.2351328670021682</v>
+        <v>0.855762440193499</v>
       </c>
       <c r="F2">
-        <v>0.2195233336756819</v>
+        <v>0.8397360446594433</v>
       </c>
       <c r="G2">
-        <v>121.842746574698</v>
+        <v>74.29985338447671</v>
       </c>
       <c r="H2">
-        <v>77.21765353704339</v>
+        <v>11.52832196763556</v>
       </c>
       <c r="I2">
-        <v>0.2352455577393019</v>
+        <v>0.8577562203721193</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>9.753176602390061</v>
+        <v>4.934404165963904</v>
       </c>
       <c r="C3">
-        <v>165.7397800060362</v>
+        <v>50.13956699622341</v>
       </c>
       <c r="D3">
-        <v>12.87399627178896</v>
+        <v>7.08092981155889</v>
       </c>
       <c r="E3">
-        <v>0.2899810535046892</v>
+        <v>0.4038745817569633</v>
       </c>
       <c r="F3">
-        <v>0.2754908709231523</v>
+        <v>0.3376384241744037</v>
       </c>
       <c r="G3">
-        <v>20.98191451527865</v>
+        <v>7.834792686970203</v>
       </c>
       <c r="H3">
-        <v>7.618909586764914</v>
+        <v>3.76988516800661</v>
       </c>
       <c r="I3">
-        <v>0.2907411245997473</v>
+        <v>0.4059087374080069</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>57.24081157422639</v>
+        <v>18.26356283381114</v>
       </c>
       <c r="C4">
-        <v>6940.688328784092</v>
+        <v>749.1395120409427</v>
       </c>
       <c r="D4">
-        <v>83.31079359113134</v>
+        <v>27.37041307764541</v>
       </c>
       <c r="E4">
-        <v>0.2810021104423723</v>
+        <v>0.2723358418059763</v>
       </c>
       <c r="F4">
-        <v>0.2663286841248697</v>
+        <v>0.1914842686733069</v>
       </c>
       <c r="G4">
-        <v>49.80732105542366</v>
+        <v>7.586571264359497</v>
       </c>
       <c r="H4">
-        <v>32.77541666666662</v>
+        <v>12.47782523191063</v>
       </c>
       <c r="I4">
-        <v>0.2818732844134106</v>
+        <v>0.2727676461070295</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>10.94070680020846</v>
+        <v>7.053258139371438</v>
       </c>
       <c r="C5">
-        <v>201.9114168186741</v>
+        <v>60.48986365556152</v>
       </c>
       <c r="D5">
-        <v>14.20955371637949</v>
+        <v>7.777522976858475</v>
       </c>
       <c r="E5">
-        <v>0.3009302827059709</v>
+        <v>0.8821083328637127</v>
       </c>
       <c r="F5">
-        <v>0.2866635537816029</v>
+        <v>0.8690092587374586</v>
       </c>
       <c r="G5">
-        <v>17.31795197910997</v>
+        <v>11.73590033177454</v>
       </c>
       <c r="H5">
-        <v>7.802893910606699</v>
+        <v>6.578865728715712</v>
       </c>
       <c r="I5">
-        <v>0.3009497479487758</v>
+        <v>0.8843412218930139</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>40.12439201168747</v>
+        <v>11.0568203838243</v>
       </c>
       <c r="C6">
-        <v>5338.443041622122</v>
+        <v>291.7707345244923</v>
       </c>
       <c r="D6">
-        <v>57.22694292073815</v>
+        <v>14.93980984405228</v>
       </c>
       <c r="E6">
-        <v>0.2767615784138001</v>
+        <v>0.6035202991550379</v>
       </c>
       <c r="F6">
-        <v>0.2620016106263267</v>
+        <v>0.5594669990611532</v>
       </c>
       <c r="G6">
-        <v>52.48748353112757</v>
+        <v>25.36427941689524</v>
       </c>
       <c r="H6">
-        <v>31.3537184252704</v>
+        <v>8.588724524067128</v>
       </c>
       <c r="I6">
-        <v>0.2772024286753089</v>
+        <v>0.6051934564450424</v>
       </c>
     </row>
   </sheetData>
@@ -1463,176 +1436,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>77.81013071895418</v>
+        <v>9.563818181818187</v>
       </c>
       <c r="C2">
-        <v>13901.53931742919</v>
+        <v>191.5524752727271</v>
       </c>
       <c r="D2">
-        <v>117.9047892048037</v>
+        <v>13.8402483819015</v>
       </c>
       <c r="E2">
-        <v>0.2429688145716846</v>
+        <v>0.910095010245791</v>
       </c>
       <c r="F2">
-        <v>0.2275191985425353</v>
+        <v>0.9001055669397677</v>
       </c>
       <c r="G2">
-        <v>103.6107947827781</v>
+        <v>51.55576117821987</v>
       </c>
       <c r="H2">
-        <v>77.66944444444394</v>
+        <v>7.685000000000002</v>
       </c>
       <c r="I2">
-        <v>0.2429688145716845</v>
+        <v>0.910095010245791</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8.623965141612267</v>
+        <v>2.173727272727254</v>
       </c>
       <c r="C3">
-        <v>159.2006318082789</v>
+        <v>7.955941181818178</v>
       </c>
       <c r="D3">
-        <v>12.61747327353139</v>
+        <v>2.820627799235159</v>
       </c>
       <c r="E3">
-        <v>0.3179943591466978</v>
+        <v>0.9054092596195418</v>
       </c>
       <c r="F3">
-        <v>0.3040758766803039</v>
+        <v>0.8948991773550464</v>
       </c>
       <c r="G3">
-        <v>18.73177856428494</v>
+        <v>3.03819745829305</v>
       </c>
       <c r="H3">
-        <v>6.327777777777975</v>
+        <v>1.04549999999999</v>
       </c>
       <c r="I3">
-        <v>0.3179943591466978</v>
+        <v>0.9054092596195418</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>50.45969498910667</v>
+        <v>7.460636363636357</v>
       </c>
       <c r="C4">
-        <v>6717.559978213508</v>
+        <v>87.59577548863668</v>
       </c>
       <c r="D4">
-        <v>81.96072216747183</v>
+        <v>9.359261482010035</v>
       </c>
       <c r="E4">
-        <v>0.3041163615888186</v>
+        <v>0.9149153058838954</v>
       </c>
       <c r="F4">
-        <v>0.289914654682468</v>
+        <v>0.905461450982106</v>
       </c>
       <c r="G4">
-        <v>39.56422819156148</v>
+        <v>2.672558718613042</v>
       </c>
       <c r="H4">
-        <v>27.90555555555477</v>
+        <v>5.440999999999974</v>
       </c>
       <c r="I4">
-        <v>0.3041163615888186</v>
+        <v>0.9149153058838954</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>9.11459694989108</v>
+        <v>3.903545454545497</v>
       </c>
       <c r="C5">
-        <v>178.7987363834423</v>
+        <v>27.75628219318187</v>
       </c>
       <c r="D5">
-        <v>13.37156447030198</v>
+        <v>5.268423122071904</v>
       </c>
       <c r="E5">
-        <v>0.3809523796846416</v>
+        <v>0.9459044179717108</v>
       </c>
       <c r="F5">
-        <v>0.3683187547802464</v>
+        <v>0.9398937977463453</v>
       </c>
       <c r="G5">
-        <v>13.96807006717373</v>
+        <v>5.225556075985178</v>
       </c>
       <c r="H5">
-        <v>7.011111111111092</v>
+        <v>2.649999999999999</v>
       </c>
       <c r="I5">
-        <v>0.3809523796846418</v>
+        <v>0.9459044179717109</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>36.50209694989105</v>
+        <v>5.775431818181824</v>
       </c>
       <c r="C6">
-        <v>5239.274665958606</v>
+        <v>78.71511853409096</v>
       </c>
       <c r="D6">
-        <v>56.46363727902722</v>
+        <v>7.822140196304651</v>
       </c>
       <c r="E6">
-        <v>0.3115079787479607</v>
+        <v>0.9190809984302347</v>
       </c>
       <c r="F6">
-        <v>0.2974571211713884</v>
+        <v>0.9100899982558164</v>
       </c>
       <c r="G6">
-        <v>43.96871790144956</v>
+        <v>15.62301835777778</v>
       </c>
       <c r="H6">
-        <v>29.72847222222195</v>
+        <v>4.205374999999991</v>
       </c>
       <c r="I6">
-        <v>0.3115079787479607</v>
+        <v>0.9190809984302348</v>
       </c>
     </row>
   </sheetData>
@@ -1647,176 +1620,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>77.89653048617977</v>
+        <v>6.34328253830785</v>
       </c>
       <c r="C2">
-        <v>13901.58420726468</v>
+        <v>158.108541205525</v>
       </c>
       <c r="D2">
-        <v>117.9049795694172</v>
+        <v>12.57412188606127</v>
       </c>
       <c r="E2">
-        <v>0.2429663700218694</v>
+        <v>0.9257918919768743</v>
       </c>
       <c r="F2">
-        <v>0.2275167041039484</v>
+        <v>0.9175465466409715</v>
       </c>
       <c r="G2">
-        <v>104.1138467674524</v>
+        <v>33.8986182619173</v>
       </c>
       <c r="H2">
-        <v>77.64845281424189</v>
+        <v>0.1969198433984625</v>
       </c>
       <c r="I2">
-        <v>0.2429663700218694</v>
+        <v>0.9259447936407934</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8.668699654816473</v>
+        <v>1.044618748490738</v>
       </c>
       <c r="C3">
-        <v>159.2101874040501</v>
+        <v>5.025972571669175</v>
       </c>
       <c r="D3">
-        <v>12.61785193303718</v>
+        <v>2.241868098633185</v>
       </c>
       <c r="E3">
-        <v>0.317953423566583</v>
+        <v>0.9402445976130989</v>
       </c>
       <c r="F3">
-        <v>0.3040341056801867</v>
+        <v>0.9336051084589987</v>
       </c>
       <c r="G3">
-        <v>18.80314279426065</v>
+        <v>1.486280049618761</v>
       </c>
       <c r="H3">
-        <v>6.325916372930557</v>
+        <v>0.1194433504510215</v>
       </c>
       <c r="I3">
-        <v>0.317953423566583</v>
+        <v>0.9402688669004993</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>50.79944760426826</v>
+        <v>3.218205890881886</v>
       </c>
       <c r="C4">
-        <v>6718.140780302222</v>
+        <v>47.33994036641047</v>
       </c>
       <c r="D4">
-        <v>81.96426526421268</v>
+        <v>6.880402631126356</v>
       </c>
       <c r="E4">
-        <v>0.3040561952974863</v>
+        <v>0.9540171392617766</v>
       </c>
       <c r="F4">
-        <v>0.2898532605076392</v>
+        <v>0.948907932513085</v>
       </c>
       <c r="G4">
-        <v>39.77824053122271</v>
+        <v>1.184873424484606</v>
       </c>
       <c r="H4">
-        <v>27.91769726226602</v>
+        <v>0.3121006433261755</v>
       </c>
       <c r="I4">
-        <v>0.3040561952974864</v>
+        <v>0.9540447951779945</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>9.134311349273732</v>
+        <v>2.068824447867843</v>
       </c>
       <c r="C5">
-        <v>178.8013993988038</v>
+        <v>19.39439470836994</v>
       </c>
       <c r="D5">
-        <v>13.37166404748503</v>
+        <v>4.403906755185665</v>
       </c>
       <c r="E5">
-        <v>0.380943159634457</v>
+        <v>0.9622013113091435</v>
       </c>
       <c r="F5">
-        <v>0.3683093465657725</v>
+        <v>0.9580014570101595</v>
       </c>
       <c r="G5">
-        <v>13.99581943119564</v>
+        <v>2.375703031159464</v>
       </c>
       <c r="H5">
-        <v>7.006909547247147</v>
+        <v>0.1226353632516179</v>
       </c>
       <c r="I5">
-        <v>0.3809431596344569</v>
+        <v>0.9622728510127037</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>36.62474727363456</v>
+        <v>3.168732906387079</v>
       </c>
       <c r="C6">
-        <v>5239.434143592438</v>
+        <v>57.46721221299364</v>
       </c>
       <c r="D6">
-        <v>56.46469020353801</v>
+        <v>6.525074842751619</v>
       </c>
       <c r="E6">
-        <v>0.3114797871300989</v>
+        <v>0.9455637350402234</v>
       </c>
       <c r="F6">
-        <v>0.2974283542143867</v>
+        <v>0.9395152611558036</v>
       </c>
       <c r="G6">
-        <v>44.17276238103285</v>
+        <v>9.736368691795033</v>
       </c>
       <c r="H6">
-        <v>29.7247439991714</v>
+        <v>0.1877748001068194</v>
       </c>
       <c r="I6">
-        <v>0.3114797871300989</v>
+        <v>0.9456328266829976</v>
       </c>
     </row>
   </sheetData>
@@ -1831,176 +1804,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>82.46329647648534</v>
+        <v>6.444848484848484</v>
       </c>
       <c r="C2">
-        <v>14602.32195473957</v>
+        <v>157.4016080808081</v>
       </c>
       <c r="D2">
-        <v>120.8400676710319</v>
+        <v>12.54597975770757</v>
       </c>
       <c r="E2">
-        <v>0.2048065435787507</v>
+        <v>0.9261236904318099</v>
       </c>
       <c r="F2">
-        <v>0.1885781056926027</v>
+        <v>0.9179152115908998</v>
       </c>
       <c r="G2">
-        <v>126.006732705268</v>
+        <v>33.6225747820874</v>
       </c>
       <c r="H2">
-        <v>82.78421052631577</v>
+        <v>0.8333333333333357</v>
       </c>
       <c r="I2">
-        <v>0.2068887478140298</v>
+        <v>0.926172116574601</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>10.11245480010186</v>
+        <v>1.496969696969699</v>
       </c>
       <c r="C3">
-        <v>171.3694663172707</v>
+        <v>5.922828282828292</v>
       </c>
       <c r="D3">
-        <v>13.0908161058534</v>
+        <v>2.433686151258681</v>
       </c>
       <c r="E3">
-        <v>0.265863826224333</v>
+        <v>0.9295815919681029</v>
       </c>
       <c r="F3">
-        <v>0.2508814553309521</v>
+        <v>0.9217573244090032</v>
       </c>
       <c r="G3">
-        <v>20.59856626465658</v>
+        <v>2.047934623809187</v>
       </c>
       <c r="H3">
-        <v>8.75454545454545</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.2735791497997297</v>
+        <v>0.929739242839113</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>61.73881767841598</v>
+        <v>4.912727272727282</v>
       </c>
       <c r="C4">
-        <v>7379.495819912038</v>
+        <v>62.47425454545468</v>
       </c>
       <c r="D4">
-        <v>85.90399187413841</v>
+        <v>7.904065697187409</v>
       </c>
       <c r="E4">
-        <v>0.2355452846784725</v>
+        <v>0.9393166758501814</v>
       </c>
       <c r="F4">
-        <v>0.2199441680392576</v>
+        <v>0.9325740842779794</v>
       </c>
       <c r="G4">
-        <v>51.88991665359932</v>
+        <v>1.759629540987499</v>
       </c>
       <c r="H4">
-        <v>48.19756097560972</v>
+        <v>0.04000000000002046</v>
       </c>
       <c r="I4">
-        <v>0.2387805910901669</v>
+        <v>0.939820215035533</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>11.19073019843127</v>
+        <v>2.360606060606059</v>
       </c>
       <c r="C5">
-        <v>213.9552081512253</v>
+        <v>30.44010101010101</v>
       </c>
       <c r="D5">
-        <v>14.62720780433591</v>
+        <v>5.517254843679147</v>
       </c>
       <c r="E5">
-        <v>0.259231551972206</v>
+        <v>0.9406737916237996</v>
       </c>
       <c r="F5">
-        <v>0.2441138285430674</v>
+        <v>0.9340819906931107</v>
       </c>
       <c r="G5">
-        <v>15.385270440516</v>
+        <v>2.576699077377372</v>
       </c>
       <c r="H5">
-        <v>9.205882352941174</v>
+        <v>0.06666666666666288</v>
       </c>
       <c r="I5">
-        <v>0.3373059434297522</v>
+        <v>0.9451300843903921</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>41.37632478835862</v>
+        <v>3.803787878787881</v>
       </c>
       <c r="C6">
-        <v>5591.785612280027</v>
+        <v>64.05969797979802</v>
       </c>
       <c r="D6">
-        <v>58.6155208638399</v>
+        <v>7.100246612458202</v>
       </c>
       <c r="E6">
-        <v>0.2413618016134406</v>
+        <v>0.9339239374684735</v>
       </c>
       <c r="F6">
-        <v>0.22587938940147</v>
+        <v>0.9265821527427482</v>
       </c>
       <c r="G6">
-        <v>53.47012151600998</v>
+        <v>10.00170950606536</v>
       </c>
       <c r="H6">
-        <v>37.23554982735303</v>
+        <v>0.4850000000000048</v>
       </c>
       <c r="I6">
-        <v>0.2641386080334197</v>
+        <v>0.9352154147099099</v>
       </c>
     </row>
   </sheetData>
@@ -2015,57 +1988,57 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>103.3828835063437</v>
+        <v>36.81785123966942</v>
       </c>
       <c r="C2">
-        <v>18363.23203721646</v>
+        <v>2130.610056198347</v>
       </c>
       <c r="D2">
-        <v>135.5110033805981</v>
+        <v>46.15853178122488</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G2">
-        <v>246.2701631959676</v>
+        <v>182.0811323591802</v>
       </c>
       <c r="H2">
-        <v>100.3298039215686</v>
+        <v>34.12727272727273</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2073,86 +2046,86 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.51787773933103</v>
+        <v>7.600000000000003</v>
       </c>
       <c r="C3">
-        <v>233.4300807381776</v>
+        <v>84.10909090909091</v>
       </c>
       <c r="D3">
-        <v>15.27841879050897</v>
+        <v>9.171100855900065</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G3">
-        <v>26.35091689499544</v>
+        <v>11.75830913886914</v>
       </c>
       <c r="H3">
-        <v>11.98235294117647</v>
+        <v>6.199999999999989</v>
       </c>
       <c r="I3">
-        <v>-4.440892098500626E-16</v>
+        <v>-2.220446049250313E-16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>74.39008073817762</v>
+        <v>22.32727272727273</v>
       </c>
       <c r="C4">
-        <v>9653.280530565167</v>
+        <v>1029.512727272727</v>
       </c>
       <c r="D4">
-        <v>98.25110956404089</v>
+        <v>32.08602074537644</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G4">
-        <v>84.16034881762829</v>
+        <v>9.140243858576918</v>
       </c>
       <c r="H4">
-        <v>60.0529411764706</v>
+        <v>14.10000000000002</v>
       </c>
       <c r="I4">
-        <v>2.220446049250313E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.93425605536332</v>
+        <v>16.55702479338843</v>
       </c>
       <c r="C5">
-        <v>288.8287274125337</v>
+        <v>513.0970247933884</v>
       </c>
       <c r="D5">
-        <v>16.99496182439177</v>
+        <v>22.6516450791855</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G5">
-        <v>22.09499194193258</v>
+        <v>35.78654001617511</v>
       </c>
       <c r="H5">
-        <v>10.50980392156863</v>
+        <v>17.64545454545454</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2160,28 +2133,28 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>50.80627450980393</v>
+        <v>20.82553719008264</v>
       </c>
       <c r="C6">
-        <v>7134.692843983084</v>
+        <v>939.3322247933884</v>
       </c>
       <c r="D6">
-        <v>66.50887338988493</v>
+        <v>27.51682461542172</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G6">
-        <v>94.71910521263098</v>
+        <v>59.69155634320034</v>
       </c>
       <c r="H6">
-        <v>45.71872549019608</v>
+        <v>18.01818181818182</v>
       </c>
       <c r="I6">
         <v>-5.551115123125783E-17</v>
@@ -2199,176 +2172,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>83.43845791662018</v>
+        <v>10.12122424242424</v>
       </c>
       <c r="C2">
-        <v>14115.40888882113</v>
+        <v>211.945667877015</v>
       </c>
       <c r="D2">
-        <v>118.8082862801292</v>
+        <v>14.55835388624054</v>
       </c>
       <c r="E2">
-        <v>0.2313221953404679</v>
+        <v>0.9005234828116834</v>
       </c>
       <c r="F2">
-        <v>0.2156348932045592</v>
+        <v>0.889470536457426</v>
       </c>
       <c r="G2">
-        <v>124.3642892111376</v>
+        <v>43.46202850258808</v>
       </c>
       <c r="H2">
-        <v>78.29799928287855</v>
+        <v>5.6875</v>
       </c>
       <c r="I2">
-        <v>0.2315378632599916</v>
+        <v>0.9041274448355769</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>9.59310172719233</v>
+        <v>2.620575757575752</v>
       </c>
       <c r="C3">
-        <v>164.0535836608198</v>
+        <v>11.19873648242629</v>
       </c>
       <c r="D3">
-        <v>12.80834039447811</v>
+        <v>3.346451326767848</v>
       </c>
       <c r="E3">
-        <v>0.2972046141524178</v>
+        <v>0.8668546246144735</v>
       </c>
       <c r="F3">
-        <v>0.2828618511759365</v>
+        <v>0.8520606940160816</v>
       </c>
       <c r="G3">
-        <v>20.65842795799123</v>
+        <v>4.038850053088233</v>
       </c>
       <c r="H3">
-        <v>7.016579439849565</v>
+        <v>1.73670238095238</v>
       </c>
       <c r="I3">
-        <v>0.2985775558701912</v>
+        <v>0.8696476468732007</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>56.75821433992059</v>
+        <v>9.775651515151521</v>
       </c>
       <c r="C4">
-        <v>6894.457044874048</v>
+        <v>154.6198909587197</v>
       </c>
       <c r="D4">
-        <v>83.03286725673182</v>
+        <v>12.43462468105571</v>
       </c>
       <c r="E4">
-        <v>0.2857912889774478</v>
+        <v>0.8498125502845197</v>
       </c>
       <c r="F4">
-        <v>0.2712156009973957</v>
+        <v>0.8331250558716886</v>
       </c>
       <c r="G4">
-        <v>45.29794264117703</v>
+        <v>3.872868201305543</v>
       </c>
       <c r="H4">
-        <v>37.1104250017269</v>
+        <v>7.482500000000016</v>
       </c>
       <c r="I4">
-        <v>0.2858515894886996</v>
+        <v>0.8500671859412223</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>11.2837941750342</v>
+        <v>4.381283549783554</v>
       </c>
       <c r="C5">
-        <v>212.4033395474314</v>
+        <v>32.72350802293341</v>
       </c>
       <c r="D5">
-        <v>14.5740639338323</v>
+        <v>5.720446488075333</v>
       </c>
       <c r="E5">
-        <v>0.2646045237596604</v>
+        <v>0.9362235475130452</v>
       </c>
       <c r="F5">
-        <v>0.24959645281598</v>
+        <v>0.9291372750144946</v>
       </c>
       <c r="G5">
-        <v>18.01261971120906</v>
+        <v>7.837071084640885</v>
       </c>
       <c r="H5">
-        <v>7.808551613611982</v>
+        <v>3.143500000000003</v>
       </c>
       <c r="I5">
-        <v>0.2646084290705419</v>
+        <v>0.9405344463030664</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>40.26839203969183</v>
+        <v>6.724683766233768</v>
       </c>
       <c r="C6">
-        <v>5346.580714225858</v>
+        <v>102.6219508352736</v>
       </c>
       <c r="D6">
-        <v>57.30588946629285</v>
+        <v>9.014969095534857</v>
       </c>
       <c r="E6">
-        <v>0.2697306555574985</v>
+        <v>0.8883535513059304</v>
       </c>
       <c r="F6">
-        <v>0.2548271995484679</v>
+        <v>0.8759483903399227</v>
       </c>
       <c r="G6">
-        <v>52.08331988037873</v>
+        <v>14.80270446040569</v>
       </c>
       <c r="H6">
-        <v>32.55838883451675</v>
+        <v>4.5125505952381</v>
       </c>
       <c r="I6">
-        <v>0.2701438594223561</v>
+        <v>0.8910941809882665</v>
       </c>
     </row>
   </sheetData>
@@ -2383,176 +2356,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>85.54125490196081</v>
+        <v>5.170909090909091</v>
       </c>
       <c r="C2">
-        <v>19872.60872062745</v>
+        <v>174.6574545454546</v>
       </c>
       <c r="D2">
-        <v>140.9702405496545</v>
+        <v>13.21580321227032</v>
       </c>
       <c r="E2">
-        <v>-0.08219558955373252</v>
+        <v>0.91802467371383</v>
       </c>
       <c r="F2">
-        <v>-0.1042812138303393</v>
+        <v>0.9089163041264778</v>
       </c>
       <c r="G2">
-        <v>83.24724203352631</v>
+        <v>20.67319567921897</v>
       </c>
       <c r="H2">
-        <v>41.764</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1275145999421031</v>
+        <v>0.920379679964459</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>11.28549019607843</v>
+        <v>1.50909090909091</v>
       </c>
       <c r="C3">
-        <v>219.5694588235294</v>
+        <v>13.32727272727274</v>
       </c>
       <c r="D3">
-        <v>14.81787632636774</v>
+        <v>3.650653739711936</v>
       </c>
       <c r="E3">
-        <v>0.05937804532653457</v>
+        <v>0.841547773454388</v>
       </c>
       <c r="F3">
-        <v>0.04018167890462709</v>
+        <v>0.8239419705048756</v>
       </c>
       <c r="G3">
-        <v>25.58616781747041</v>
+        <v>1.996786661418645</v>
       </c>
       <c r="H3">
-        <v>8.799999999999997</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1308273432317499</v>
+        <v>0.8686239830208701</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>71.5835294117647</v>
+        <v>4.381818181818186</v>
       </c>
       <c r="C4">
-        <v>8554.127529411766</v>
+        <v>117.238181818182</v>
       </c>
       <c r="D4">
-        <v>92.48852647443231</v>
+        <v>10.82765818716965</v>
       </c>
       <c r="E4">
-        <v>0.113863157469956</v>
+        <v>0.8861226493734016</v>
       </c>
       <c r="F4">
-        <v>0.09577873211220012</v>
+        <v>0.8734696104148907</v>
       </c>
       <c r="G4">
-        <v>70.77748769846939</v>
+        <v>1.524355069777134</v>
       </c>
       <c r="H4">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.114021233426856</v>
+        <v>0.9047725699327869</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>13.16745098039216</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="C5">
-        <v>264.8544862745098</v>
+        <v>21.38909090909091</v>
       </c>
       <c r="D5">
-        <v>16.27435056383234</v>
+        <v>4.624834149360484</v>
       </c>
       <c r="E5">
-        <v>0.08300504369075956</v>
+        <v>0.9583137498844322</v>
       </c>
       <c r="F5">
-        <v>0.06429086090893832</v>
+        <v>0.9536819443160358</v>
       </c>
       <c r="G5">
-        <v>20.90362630823665</v>
+        <v>2.015603890018136</v>
       </c>
       <c r="H5">
-        <v>9.820000000000007</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.1022820360566972</v>
+        <v>0.9594502610464343</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>45.39443137254902</v>
+        <v>3.220000000000001</v>
       </c>
       <c r="C6">
-        <v>7227.790048784315</v>
+        <v>81.65300000000005</v>
       </c>
       <c r="D6">
-        <v>66.13774847857172</v>
+        <v>8.079737322128098</v>
       </c>
       <c r="E6">
-        <v>0.04351266423337941</v>
+        <v>0.9010022116065129</v>
       </c>
       <c r="F6">
-        <v>0.02399251452385656</v>
+        <v>0.89000245734057</v>
       </c>
       <c r="G6">
-        <v>50.12863096442569</v>
+        <v>6.552485325108222</v>
       </c>
       <c r="H6">
-        <v>28.971</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.1186613031643516</v>
+        <v>0.9133066234911374</v>
       </c>
     </row>
   </sheetData>
@@ -2567,176 +2540,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>105.3271895424837</v>
+        <v>5.170909090909091</v>
       </c>
       <c r="C2">
-        <v>27753.96435816994</v>
+        <v>174.6574545454546</v>
       </c>
       <c r="D2">
-        <v>166.5952110901449</v>
+        <v>13.21580321227032</v>
       </c>
       <c r="E2">
-        <v>-0.5113877721482492</v>
+        <v>0.91802467371383</v>
       </c>
       <c r="F2">
-        <v>-0.542232420559438</v>
+        <v>0.9089163041264778</v>
       </c>
       <c r="G2">
-        <v>75.70523535912056</v>
+        <v>20.67319567921897</v>
       </c>
       <c r="H2">
-        <v>53.72666666666667</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01036585755585528</v>
+        <v>0.920379679964459</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>13.33202614379085</v>
+        <v>1.50909090909091</v>
       </c>
       <c r="C3">
-        <v>330.7277559912854</v>
+        <v>13.32727272727274</v>
       </c>
       <c r="D3">
-        <v>18.18592191755165</v>
+        <v>3.650653739711936</v>
       </c>
       <c r="E3">
-        <v>-0.416817211155575</v>
+        <v>0.841547773454388</v>
       </c>
       <c r="F3">
-        <v>-0.4457318481179338</v>
+        <v>0.8239419705048756</v>
       </c>
       <c r="G3">
-        <v>31.25405899260044</v>
+        <v>1.996786661418645</v>
       </c>
       <c r="H3">
-        <v>10.53333333333333</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.05390071361195137</v>
+        <v>0.8686239830208701</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>62.99803921568628</v>
+        <v>4.381818181818186</v>
       </c>
       <c r="C4">
-        <v>8125.083420479303</v>
+        <v>117.238181818182</v>
       </c>
       <c r="D4">
-        <v>90.13924461897439</v>
+        <v>10.82765818716965</v>
       </c>
       <c r="E4">
-        <v>0.1583085776122569</v>
+        <v>0.8861226493734016</v>
       </c>
       <c r="F4">
-        <v>0.14113120164516</v>
+        <v>0.8734696104148907</v>
       </c>
       <c r="G4">
-        <v>60.4819264115517</v>
+        <v>1.524355069777134</v>
       </c>
       <c r="H4">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.2164244312181179</v>
+        <v>0.9047725699327869</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.47058823529412</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="C5">
-        <v>242.0894989106754</v>
+        <v>21.38909090909091</v>
       </c>
       <c r="D5">
-        <v>15.55922552412797</v>
+        <v>4.624834149360484</v>
       </c>
       <c r="E5">
-        <v>0.1618233370363492</v>
+        <v>0.9583137498844322</v>
       </c>
       <c r="F5">
-        <v>0.1447176908534176</v>
+        <v>0.9536819443160358</v>
       </c>
       <c r="G5">
-        <v>19.05461322223746</v>
+        <v>2.015603890018136</v>
       </c>
       <c r="H5">
-        <v>9.666666666666671</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.1731553985465476</v>
+        <v>0.9594502610464343</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>48.53196078431372</v>
+        <v>3.220000000000001</v>
       </c>
       <c r="C6">
-        <v>9112.9662583878</v>
+        <v>81.65300000000005</v>
       </c>
       <c r="D6">
-        <v>72.61990078769972</v>
+        <v>8.079737322128098</v>
       </c>
       <c r="E6">
-        <v>-0.1520182671638045</v>
+        <v>0.9010022116065129</v>
       </c>
       <c r="F6">
-        <v>-0.1755288440446985</v>
+        <v>0.89000245734057</v>
       </c>
       <c r="G6">
-        <v>46.62395849637755</v>
+        <v>6.552485325108222</v>
       </c>
       <c r="H6">
-        <v>28.60666666666667</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.113461600233118</v>
+        <v>0.9133066234911374</v>
       </c>
     </row>
   </sheetData>
@@ -2751,176 +2724,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>93.08675009937613</v>
+        <v>9.135099089440038</v>
       </c>
       <c r="C2">
-        <v>19356.36442252344</v>
+        <v>227.9373152924311</v>
       </c>
       <c r="D2">
-        <v>139.1271519960192</v>
+        <v>15.09759302976574</v>
       </c>
       <c r="E2">
-        <v>-0.05408265730641615</v>
+        <v>0.8930178168317011</v>
       </c>
       <c r="F2">
-        <v>-0.07559454827185319</v>
+        <v>0.8811309075907791</v>
       </c>
       <c r="G2">
-        <v>156.6209962855719</v>
+        <v>42.23687468370606</v>
       </c>
       <c r="H2">
-        <v>60.23849989630814</v>
+        <v>3.756718469895498</v>
       </c>
       <c r="I2">
-        <v>0.04195906017389828</v>
+        <v>0.9006139593466382</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>11.41822598968928</v>
+        <v>4.171119630410671</v>
       </c>
       <c r="C3">
-        <v>224.205083473497</v>
+        <v>60.37912349261862</v>
       </c>
       <c r="D3">
-        <v>14.97347933759876</v>
+        <v>7.770400471830176</v>
       </c>
       <c r="E3">
-        <v>0.0395193166001071</v>
+        <v>0.2821332053406778</v>
       </c>
       <c r="F3">
-        <v>0.01991767000010936</v>
+        <v>0.2023702281563087</v>
       </c>
       <c r="G3">
-        <v>25.79193139343494</v>
+        <v>6.932090168535715</v>
       </c>
       <c r="H3">
-        <v>8.000000299206974</v>
+        <v>1.354704521937407</v>
       </c>
       <c r="I3">
-        <v>0.09763435668346099</v>
+        <v>0.3064817405987508</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>68.86411940104585</v>
+        <v>15.62165657083344</v>
       </c>
       <c r="C4">
-        <v>9465.278869143707</v>
+        <v>929.6358678901887</v>
       </c>
       <c r="D4">
-        <v>97.28966476015685</v>
+        <v>30.48993059831702</v>
       </c>
       <c r="E4">
-        <v>0.01947541675870601</v>
+        <v>0.09701371992468866</v>
       </c>
       <c r="F4">
-        <v>-0.0005352890217285022</v>
+        <v>-0.003318088972568134</v>
       </c>
       <c r="G4">
-        <v>84.06345114102812</v>
+        <v>7.064922940042305</v>
       </c>
       <c r="H4">
-        <v>43.08202176006466</v>
+        <v>0.1403619432329037</v>
       </c>
       <c r="I4">
-        <v>0.06486970334497855</v>
+        <v>0.2039621979361006</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.07038452408274</v>
+        <v>3.712801038344377</v>
       </c>
       <c r="C5">
-        <v>311.7252541593797</v>
+        <v>34.10813695695931</v>
       </c>
       <c r="D5">
-        <v>17.65574280961805</v>
+        <v>5.840217201180048</v>
       </c>
       <c r="E5">
-        <v>-0.079273716821606</v>
+        <v>0.9335249761569094</v>
       </c>
       <c r="F5">
-        <v>-0.1012997110424552</v>
+        <v>0.9261388623965661</v>
       </c>
       <c r="G5">
-        <v>22.21796193116536</v>
+        <v>4.281677001951937</v>
       </c>
       <c r="H5">
-        <v>10.09981651181278</v>
+        <v>0.8063517488198499</v>
       </c>
       <c r="I5">
-        <v>-0.04043354842506308</v>
+        <v>0.9335409817172351</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>46.35987000354851</v>
+        <v>8.160169082257129</v>
       </c>
       <c r="C6">
-        <v>7339.393407325007</v>
+        <v>313.0151109080495</v>
       </c>
       <c r="D6">
-        <v>67.26150972584821</v>
+        <v>14.79953532527325</v>
       </c>
       <c r="E6">
-        <v>-0.01859041019230226</v>
+        <v>0.5514224295634942</v>
       </c>
       <c r="F6">
-        <v>-0.03937796958398188</v>
+        <v>0.5015804772927714</v>
       </c>
       <c r="G6">
-        <v>72.17358518780009</v>
+        <v>15.128891198559</v>
       </c>
       <c r="H6">
-        <v>30.35508461684814</v>
+        <v>1.514534170971415</v>
       </c>
       <c r="I6">
-        <v>0.04100739294431868</v>
+        <v>0.5861497198996812</v>
       </c>
     </row>
   </sheetData>
@@ -2935,72 +2908,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>117.9047892048037</v>
+        <v>12.54597975770757</v>
       </c>
       <c r="D2">
-        <v>0.2429688145716846</v>
+        <v>0.9261236904318099</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>12.61747327351583</v>
+        <v>2.231636211036968</v>
       </c>
       <c r="D3">
-        <v>0.3179943591483801</v>
+        <v>0.9407888002999073</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>81.96072216747183</v>
+        <v>6.846584112358198</v>
       </c>
       <c r="D4">
-        <v>0.3041163615888186</v>
+        <v>0.9544680577851876</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>13.37156447030198</v>
+        <v>4.389801766206672</v>
       </c>
       <c r="D5">
-        <v>0.3809523796846417</v>
+        <v>0.9624430495297631</v>
       </c>
     </row>
   </sheetData>
@@ -3015,176 +2988,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>77.81018150339462</v>
+        <v>9.464835827635261</v>
       </c>
       <c r="C2">
-        <v>13901.53931799675</v>
+        <v>191.043576306493</v>
       </c>
       <c r="D2">
-        <v>117.9047892072105</v>
+        <v>13.82185140661312</v>
       </c>
       <c r="E2">
-        <v>0.2429688145407776</v>
+        <v>0.9103338615385246</v>
       </c>
       <c r="F2">
-        <v>0.2275191985109976</v>
+        <v>0.9003709572650274</v>
       </c>
       <c r="G2">
-        <v>103.6110864192689</v>
+        <v>56.71946161767452</v>
       </c>
       <c r="H2">
-        <v>77.66944250929788</v>
+        <v>5.160384664613204</v>
       </c>
       <c r="I2">
-        <v>0.2429688145409071</v>
+        <v>0.9103347316036985</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8.623969217286845</v>
+        <v>1.047657967859604</v>
       </c>
       <c r="C3">
-        <v>159.2006318078862</v>
+        <v>4.980200178411433</v>
       </c>
       <c r="D3">
-        <v>12.61747327351583</v>
+        <v>2.231636211036968</v>
       </c>
       <c r="E3">
-        <v>0.3179943591483801</v>
+        <v>0.9407888002999073</v>
       </c>
       <c r="F3">
-        <v>0.3040758766820205</v>
+        <v>0.9342097781110081</v>
       </c>
       <c r="G3">
-        <v>18.73178607624857</v>
+        <v>1.47476981178906</v>
       </c>
       <c r="H3">
-        <v>6.327777749308567</v>
+        <v>0.07849850665577662</v>
       </c>
       <c r="I3">
-        <v>0.317994359148384</v>
+        <v>0.9407888740429461</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>50.45969533586576</v>
+        <v>3.042098970418687</v>
       </c>
       <c r="C4">
-        <v>6717.55997821351</v>
+        <v>46.8757140075957</v>
       </c>
       <c r="D4">
-        <v>81.96072216747184</v>
+        <v>6.846584112358198</v>
       </c>
       <c r="E4">
-        <v>0.3041163615888185</v>
+        <v>0.9544680577851876</v>
       </c>
       <c r="F4">
-        <v>0.2899146546824678</v>
+        <v>0.9494089530946529</v>
       </c>
       <c r="G4">
-        <v>39.56422857153029</v>
+        <v>1.108844511258337</v>
       </c>
       <c r="H4">
-        <v>27.90555632743536</v>
+        <v>0.1376522039631141</v>
       </c>
       <c r="I4">
-        <v>0.3041163615888187</v>
+        <v>0.95446806816635</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>9.114599726559888</v>
+        <v>2.162045222697159</v>
       </c>
       <c r="C5">
-        <v>178.7987363955133</v>
+        <v>19.27035954659121</v>
       </c>
       <c r="D5">
-        <v>13.37156447075335</v>
+        <v>4.389801766206672</v>
       </c>
       <c r="E5">
-        <v>0.3809523796428488</v>
+        <v>0.9624430495297631</v>
       </c>
       <c r="F5">
-        <v>0.3683187547376008</v>
+        <v>0.9582700550330702</v>
       </c>
       <c r="G5">
-        <v>13.96807589870407</v>
+        <v>2.60141634216883</v>
       </c>
       <c r="H5">
-        <v>7.011111131763741</v>
+        <v>0.119654179702934</v>
       </c>
       <c r="I5">
-        <v>0.380952379642849</v>
+        <v>0.9624432272390576</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>36.50211144577678</v>
+        <v>3.929159497152678</v>
       </c>
       <c r="C6">
-        <v>5239.274666103413</v>
+        <v>65.54246250977285</v>
       </c>
       <c r="D6">
-        <v>56.46363727973788</v>
+        <v>6.822468374053738</v>
       </c>
       <c r="E6">
-        <v>0.3115079787302062</v>
+        <v>0.9420084422883457</v>
       </c>
       <c r="F6">
-        <v>0.2974571211532717</v>
+        <v>0.9355649358759397</v>
       </c>
       <c r="G6">
-        <v>43.96879424143795</v>
+        <v>15.47612307072269</v>
       </c>
       <c r="H6">
-        <v>29.72847192945139</v>
+        <v>1.374047388733757</v>
       </c>
       <c r="I6">
-        <v>0.3115079787302397</v>
+        <v>0.942008725263013</v>
       </c>
     </row>
   </sheetData>
@@ -3199,176 +3172,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>77.76265625822779</v>
+        <v>22.47874861283736</v>
       </c>
       <c r="C2">
-        <v>13904.58582873972</v>
+        <v>864.0970897764774</v>
       </c>
       <c r="D2">
-        <v>117.9177078675621</v>
+        <v>29.3955283976403</v>
       </c>
       <c r="E2">
-        <v>0.2428029117881033</v>
+        <v>0.5944367730441074</v>
       </c>
       <c r="F2">
-        <v>0.2273499099878605</v>
+        <v>0.5493741922712304</v>
       </c>
       <c r="G2">
-        <v>103.2850370261531</v>
+        <v>106.3009167342963</v>
       </c>
       <c r="H2">
-        <v>75.65267944335938</v>
+        <v>19.81992416381836</v>
       </c>
       <c r="I2">
-        <v>0.2429146161171736</v>
+        <v>0.598205973018451</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8.710901432411344</v>
+        <v>4.924207097833807</v>
       </c>
       <c r="C3">
-        <v>159.2417370207818</v>
+        <v>41.70204206730366</v>
       </c>
       <c r="D3">
-        <v>12.61910206872034</v>
+        <v>6.457711829069462</v>
       </c>
       <c r="E3">
-        <v>0.3178182669636639</v>
+        <v>0.5041910260048204</v>
       </c>
       <c r="F3">
-        <v>0.3038961907792489</v>
+        <v>0.4491011400053559</v>
       </c>
       <c r="G3">
-        <v>18.8812564209679</v>
+        <v>7.764184798383268</v>
       </c>
       <c r="H3">
-        <v>6.312732696533203</v>
+        <v>4.405749511718753</v>
       </c>
       <c r="I3">
-        <v>0.3178192039247441</v>
+        <v>0.5093799775864472</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>51.05114629782883</v>
+        <v>16.75351534756748</v>
       </c>
       <c r="C4">
-        <v>6719.274806897892</v>
+        <v>586.2686375711496</v>
       </c>
       <c r="D4">
-        <v>81.97118278332876</v>
+        <v>24.21298489594271</v>
       </c>
       <c r="E4">
-        <v>0.3039387195241386</v>
+        <v>0.4305377466053981</v>
       </c>
       <c r="F4">
-        <v>0.2897333872695292</v>
+        <v>0.3672641628948868</v>
       </c>
       <c r="G4">
-        <v>40.03445658192646</v>
+        <v>6.900530507952373</v>
       </c>
       <c r="H4">
-        <v>27.94454956054688</v>
+        <v>12.94874267578126</v>
       </c>
       <c r="I4">
-        <v>0.3039387342075709</v>
+        <v>0.4368591516329008</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>9.204164766797833</v>
+        <v>10.20883095481179</v>
       </c>
       <c r="C5">
-        <v>178.8807381076493</v>
+        <v>196.3698471258346</v>
       </c>
       <c r="D5">
-        <v>13.37463039144071</v>
+        <v>14.01320260061327</v>
       </c>
       <c r="E5">
-        <v>0.3806684684375102</v>
+        <v>0.6172851573152116</v>
       </c>
       <c r="F5">
-        <v>0.3680290494260309</v>
+        <v>0.5747612859057907</v>
       </c>
       <c r="G5">
-        <v>14.04028729856523</v>
+        <v>22.26113678591969</v>
       </c>
       <c r="H5">
-        <v>6.784683227539062</v>
+        <v>9.317398071289062</v>
       </c>
       <c r="I5">
-        <v>0.3808241689233319</v>
+        <v>0.6204738373261833</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>36.68221718881645</v>
+        <v>13.59132550326261</v>
       </c>
       <c r="C6">
-        <v>5240.49577769151</v>
+        <v>422.1094041351914</v>
       </c>
       <c r="D6">
-        <v>56.47065577776298</v>
+        <v>18.51985693081643</v>
       </c>
       <c r="E6">
-        <v>0.311307091678354</v>
+        <v>0.5366126757423844</v>
       </c>
       <c r="F6">
-        <v>0.2972521343656674</v>
+        <v>0.485125195269316</v>
       </c>
       <c r="G6">
-        <v>44.06025933190316</v>
+        <v>35.8066922066379</v>
       </c>
       <c r="H6">
-        <v>29.17366123199463</v>
+        <v>11.62295360565186</v>
       </c>
       <c r="I6">
-        <v>0.3113741807932051</v>
+        <v>0.5412297348909956</v>
       </c>
     </row>
   </sheetData>
@@ -3383,57 +3356,57 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>103.3828835128335</v>
+        <v>36.81785126725504</v>
       </c>
       <c r="C2">
-        <v>18363.23203721646</v>
+        <v>2130.610056198347</v>
       </c>
       <c r="D2">
-        <v>135.5110033805981</v>
+        <v>46.15853178122488</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G2">
-        <v>246.2701632404246</v>
+        <v>182.0811326658558</v>
       </c>
       <c r="H2">
-        <v>100.329803943634</v>
+        <v>34.1272727879611</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3441,86 +3414,86 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.51787774373091</v>
+        <v>7.599999981084148</v>
       </c>
       <c r="C3">
-        <v>233.4300807381776</v>
+        <v>84.10909090909094</v>
       </c>
       <c r="D3">
-        <v>15.27841879050897</v>
+        <v>9.171100855900066</v>
       </c>
       <c r="E3">
+        <v>-4.440892098500626E-16</v>
+      </c>
+      <c r="F3">
+        <v>-0.1111111111111116</v>
+      </c>
+      <c r="G3">
+        <v>11.75830912354077</v>
+      </c>
+      <c r="H3">
+        <v>6.200000069358126</v>
+      </c>
+      <c r="I3">
         <v>-2.220446049250313E-16</v>
-      </c>
-      <c r="F3">
-        <v>-0.02040816326530637</v>
-      </c>
-      <c r="G3">
-        <v>26.35091688262225</v>
-      </c>
-      <c r="H3">
-        <v>11.98235298605526</v>
-      </c>
-      <c r="I3">
-        <v>-4.440892098500626E-16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>74.39008081957542</v>
+        <v>22.32727280293615</v>
       </c>
       <c r="C4">
-        <v>9653.280530565165</v>
+        <v>1029.512727272728</v>
       </c>
       <c r="D4">
-        <v>98.25110956404087</v>
+        <v>32.08602074537645</v>
       </c>
       <c r="E4">
-        <v>1.110223024625157E-16</v>
+        <v>-4.440892098500626E-16</v>
       </c>
       <c r="F4">
-        <v>-0.02040816326530592</v>
+        <v>-0.1111111111111116</v>
       </c>
       <c r="G4">
-        <v>84.16034875700822</v>
+        <v>9.140243858427112</v>
       </c>
       <c r="H4">
-        <v>60.05294145322313</v>
+        <v>14.09999916770244</v>
       </c>
       <c r="I4">
-        <v>2.220446049250313E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.93425605536332</v>
+        <v>16.55702473033558</v>
       </c>
       <c r="C5">
-        <v>288.8287274125337</v>
+        <v>513.0970247933884</v>
       </c>
       <c r="D5">
-        <v>16.99496182439177</v>
+        <v>22.6516450791855</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G5">
-        <v>22.09499194193258</v>
+        <v>35.78653999883794</v>
       </c>
       <c r="H5">
-        <v>10.50980392156863</v>
+        <v>17.64545440673828</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3528,215 +3501,31 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>50.8062745328758</v>
+        <v>20.82553719540273</v>
       </c>
       <c r="C6">
-        <v>7134.692843983083</v>
+        <v>939.3322247933886</v>
       </c>
       <c r="D6">
-        <v>66.50887338988493</v>
+        <v>27.51682461542173</v>
       </c>
       <c r="E6">
-        <v>-2.775557561562891E-17</v>
+        <v>-2.220446049250313E-16</v>
       </c>
       <c r="F6">
-        <v>-0.02040816326530615</v>
+        <v>-0.1111111111111114</v>
       </c>
       <c r="G6">
-        <v>94.7191052054969</v>
+        <v>59.69155641166542</v>
       </c>
       <c r="H6">
-        <v>45.71872557612026</v>
+        <v>18.01818160793999</v>
       </c>
       <c r="I6">
         <v>-5.551115123125783E-17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2">
-        <v>78.43587014564805</v>
-      </c>
-      <c r="C2">
-        <v>13903.7584111244</v>
-      </c>
-      <c r="D2">
-        <v>117.914199361758</v>
-      </c>
-      <c r="E2">
-        <v>0.2428479701750822</v>
-      </c>
-      <c r="F2">
-        <v>0.2273958879337574</v>
-      </c>
-      <c r="G2">
-        <v>106.5435159473219</v>
-      </c>
-      <c r="H2">
-        <v>77.5958885216848</v>
-      </c>
-      <c r="I2">
-        <v>0.2428480037515979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3">
-        <v>8.819405554201415</v>
-      </c>
-      <c r="C3">
-        <v>159.3836398411521</v>
-      </c>
-      <c r="D3">
-        <v>12.62472335701468</v>
-      </c>
-      <c r="E3">
-        <v>0.3172103640750492</v>
-      </c>
-      <c r="F3">
-        <v>0.3032758817092339</v>
-      </c>
-      <c r="G3">
-        <v>19.0557280300236</v>
-      </c>
-      <c r="H3">
-        <v>6.3514897433977</v>
-      </c>
-      <c r="I3">
-        <v>0.3172103645224323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4">
-        <v>51.76136689593978</v>
-      </c>
-      <c r="C4">
-        <v>6726.144752708734</v>
-      </c>
-      <c r="D4">
-        <v>82.01307671773284</v>
-      </c>
-      <c r="E4">
-        <v>0.3032270499741769</v>
-      </c>
-      <c r="F4">
-        <v>0.2890071938512009</v>
-      </c>
-      <c r="G4">
-        <v>40.40101371595181</v>
-      </c>
-      <c r="H4">
-        <v>28.05340447759244</v>
-      </c>
-      <c r="I4">
-        <v>0.3032272420329404</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5">
-        <v>9.293284388227931</v>
-      </c>
-      <c r="C5">
-        <v>178.9545123558075</v>
-      </c>
-      <c r="D5">
-        <v>13.37738809916972</v>
-      </c>
-      <c r="E5">
-        <v>0.3804130428473376</v>
-      </c>
-      <c r="F5">
-        <v>0.3677684110687118</v>
-      </c>
-      <c r="G5">
-        <v>14.20819471335664</v>
-      </c>
-      <c r="H5">
-        <v>7.033953355155091</v>
-      </c>
-      <c r="I5">
-        <v>0.3804130916550036</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6">
-        <v>37.0774817460043</v>
-      </c>
-      <c r="C6">
-        <v>5242.060329007524</v>
-      </c>
-      <c r="D6">
-        <v>56.4823468839188</v>
-      </c>
-      <c r="E6">
-        <v>0.3109246067679114</v>
-      </c>
-      <c r="F6">
-        <v>0.296861843640726</v>
-      </c>
-      <c r="G6">
-        <v>45.0521131016635</v>
-      </c>
-      <c r="H6">
-        <v>29.75868402445751</v>
-      </c>
-      <c r="I6">
-        <v>0.3109246754904935</v>
       </c>
     </row>
   </sheetData>
@@ -3751,176 +3540,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>100.5991041010139</v>
+        <v>19.7635110550352</v>
       </c>
       <c r="C2">
-        <v>17379.08227684107</v>
+        <v>543.2657012332552</v>
       </c>
       <c r="D2">
-        <v>131.8297473138785</v>
+        <v>23.30806086385685</v>
       </c>
       <c r="E2">
-        <v>0.05359349369331234</v>
+        <v>0.7450187097104922</v>
       </c>
       <c r="F2">
-        <v>0.03427907519725759</v>
+        <v>0.7166874552338802</v>
       </c>
       <c r="G2">
-        <v>238.7666581408387</v>
+        <v>110.3975298333543</v>
       </c>
       <c r="H2">
-        <v>100.0378372710054</v>
+        <v>18.09499225443398</v>
       </c>
       <c r="I2">
-        <v>0.05359349369331234</v>
+        <v>0.7450187097104922</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.12410483549724</v>
+        <v>5.748835003635675</v>
       </c>
       <c r="C3">
-        <v>223.6937809029339</v>
+        <v>69.15334401522092</v>
       </c>
       <c r="D3">
-        <v>14.95639598643115</v>
+        <v>8.315848965392584</v>
       </c>
       <c r="E3">
-        <v>0.04170970512649663</v>
+        <v>0.1778136790235297</v>
       </c>
       <c r="F3">
-        <v>0.02215276033315983</v>
+        <v>0.08645964335947753</v>
       </c>
       <c r="G3">
-        <v>25.51073889482632</v>
+        <v>9.049075970963221</v>
       </c>
       <c r="H3">
-        <v>10.76753489029105</v>
+        <v>3.272726123107091</v>
       </c>
       <c r="I3">
-        <v>0.04170970512649652</v>
+        <v>0.1778136790235297</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>65.84982486633585</v>
+        <v>22.07833674866333</v>
       </c>
       <c r="C4">
-        <v>8129.864549907176</v>
+        <v>1029.211924236676</v>
       </c>
       <c r="D4">
-        <v>90.16576151681511</v>
+        <v>32.08133295604589</v>
       </c>
       <c r="E4">
-        <v>0.1578132921584948</v>
+        <v>0.0002921800071846725</v>
       </c>
       <c r="F4">
-        <v>0.1406258083249947</v>
+        <v>-0.1107864666586837</v>
       </c>
       <c r="G4">
-        <v>50.04804571545817</v>
+        <v>9.054636362132088</v>
       </c>
       <c r="H4">
-        <v>47.69542868656839</v>
+        <v>13.5783406046811</v>
       </c>
       <c r="I4">
-        <v>0.1578132921584948</v>
+        <v>0.0002921800071845615</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.97177929324432</v>
+        <v>9.456866537717602</v>
       </c>
       <c r="C5">
-        <v>288.767627710486</v>
+        <v>106.0086085284574</v>
       </c>
       <c r="D5">
-        <v>16.99316414651745</v>
+        <v>10.29604819959859</v>
       </c>
       <c r="E5">
-        <v>0.000211543022728522</v>
+        <v>0.7933946146517913</v>
       </c>
       <c r="F5">
-        <v>-0.02019230303803221</v>
+        <v>0.7704384607242125</v>
       </c>
       <c r="G5">
-        <v>22.14270322625135</v>
+        <v>12.6364705484913</v>
       </c>
       <c r="H5">
-        <v>11.03400008039232</v>
+        <v>9.739072428946287</v>
       </c>
       <c r="I5">
-        <v>0.000211543022728522</v>
+        <v>0.7933946146517913</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>47.88620327402283</v>
+        <v>14.26188733626295</v>
       </c>
       <c r="C6">
-        <v>6505.352058840415</v>
+        <v>436.9098945034024</v>
       </c>
       <c r="D6">
-        <v>63.48626724091056</v>
+        <v>18.50032274622348</v>
       </c>
       <c r="E6">
-        <v>0.06333200850025808</v>
+        <v>0.4291297958482495</v>
       </c>
       <c r="F6">
-        <v>0.04421633520434498</v>
+        <v>0.3656997731647216</v>
       </c>
       <c r="G6">
-        <v>84.11703649434362</v>
+        <v>35.28442817873522</v>
       </c>
       <c r="H6">
-        <v>42.3837002320643</v>
+        <v>11.17128285279211</v>
       </c>
       <c r="I6">
-        <v>0.06333200850025805</v>
+        <v>0.4291297958482495</v>
       </c>
     </row>
   </sheetData>
@@ -3935,176 +3724,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>100.5713187095467</v>
+        <v>36.78211700867913</v>
       </c>
       <c r="C2">
-        <v>17379.44623755126</v>
+        <v>2125.848940524359</v>
       </c>
       <c r="D2">
-        <v>131.8311277261606</v>
+        <v>46.10692941982104</v>
       </c>
       <c r="E2">
-        <v>0.05357367361428389</v>
+        <v>0.002234625552497205</v>
       </c>
       <c r="F2">
-        <v>0.03425885062682033</v>
+        <v>-0.1086281938305587</v>
       </c>
       <c r="G2">
-        <v>238.6305438639394</v>
+        <v>181.9432490525538</v>
       </c>
       <c r="H2">
-        <v>100.2288441711482</v>
+        <v>34.1191200286468</v>
       </c>
       <c r="I2">
-        <v>0.05357367361428378</v>
+        <v>0.002234625552497538</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.13006706395132</v>
+        <v>7.597221702551052</v>
       </c>
       <c r="C3">
-        <v>223.6973816055357</v>
+        <v>84.06423231194414</v>
       </c>
       <c r="D3">
-        <v>14.95651635928419</v>
+        <v>9.168654880185214</v>
       </c>
       <c r="E3">
-        <v>0.04169427993968944</v>
+        <v>0.0005333382713081924</v>
       </c>
       <c r="F3">
-        <v>0.02213702034662179</v>
+        <v>-0.1105185130318798</v>
       </c>
       <c r="G3">
-        <v>25.52412458970145</v>
+        <v>11.75424302071447</v>
       </c>
       <c r="H3">
-        <v>10.74926781660898</v>
+        <v>6.191568329721036</v>
       </c>
       <c r="I3">
-        <v>0.04169427993968955</v>
+        <v>0.0005333382713086365</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>65.98682694780348</v>
+        <v>22.32689911487422</v>
       </c>
       <c r="C4">
-        <v>8130.427943391148</v>
+        <v>1029.511825037465</v>
       </c>
       <c r="D4">
-        <v>90.16888567233792</v>
+        <v>32.08600668574176</v>
       </c>
       <c r="E4">
-        <v>0.15775492925459</v>
+        <v>8.763711591974754E-07</v>
       </c>
       <c r="F4">
-        <v>0.1405662543414185</v>
+        <v>-0.1111101373653787</v>
       </c>
       <c r="G4">
-        <v>50.69354982725588</v>
+        <v>9.140115375654295</v>
       </c>
       <c r="H4">
-        <v>47.93307315752804</v>
+        <v>14.09792241870076</v>
       </c>
       <c r="I4">
-        <v>0.15775492925459</v>
+        <v>8.7637115941952E-07</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.97105769251584</v>
+        <v>16.53892834965514</v>
       </c>
       <c r="C5">
-        <v>288.7676503065296</v>
+        <v>511.8759948175576</v>
       </c>
       <c r="D5">
-        <v>16.9931648113743</v>
+        <v>22.62467667874079</v>
       </c>
       <c r="E5">
-        <v>0.0002114647893624033</v>
+        <v>0.002379725308916947</v>
       </c>
       <c r="F5">
-        <v>-0.02019238286799752</v>
+        <v>-0.1084669718789812</v>
       </c>
       <c r="G5">
-        <v>22.14178570155291</v>
+        <v>35.74214863162645</v>
       </c>
       <c r="H5">
-        <v>11.02391938503033</v>
+        <v>17.64132587532872</v>
       </c>
       <c r="I5">
-        <v>0.0002114647893622923</v>
+        <v>0.002379725308917169</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>47.91481760345432</v>
+        <v>20.81129154393988</v>
       </c>
       <c r="C6">
-        <v>6505.584803213618</v>
+        <v>937.8252481728314</v>
       </c>
       <c r="D6">
-        <v>63.48742364228924</v>
+        <v>27.49656691612221</v>
       </c>
       <c r="E6">
-        <v>0.06330858689948143</v>
+        <v>0.001287141375970385</v>
       </c>
       <c r="F6">
-        <v>0.04419243561171576</v>
+        <v>-0.1096809540266996</v>
       </c>
       <c r="G6">
-        <v>84.2475009956124</v>
+        <v>59.64493902013724</v>
       </c>
       <c r="H6">
-        <v>42.48377613257889</v>
+        <v>18.01248416309933</v>
       </c>
       <c r="I6">
-        <v>0.06330858689948141</v>
+        <v>0.001287141375970691</v>
       </c>
     </row>
   </sheetData>
@@ -4119,176 +3908,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>100.5990580446904</v>
+        <v>20.30291548360422</v>
       </c>
       <c r="C2">
-        <v>17379.08227784106</v>
+        <v>547.5601892220443</v>
       </c>
       <c r="D2">
-        <v>131.8297473176713</v>
+        <v>23.40000404320573</v>
       </c>
       <c r="E2">
-        <v>0.0535934936388559</v>
+        <v>0.7430030954612796</v>
       </c>
       <c r="F2">
-        <v>0.0342790751416896</v>
+        <v>0.7144478838458663</v>
       </c>
       <c r="G2">
-        <v>238.7664325214447</v>
+        <v>112.9618060876235</v>
       </c>
       <c r="H2">
-        <v>100.0381538789472</v>
+        <v>18.19078762878262</v>
       </c>
       <c r="I2">
-        <v>0.0535934936388559</v>
+        <v>0.7430030954612796</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.12420419627597</v>
+        <v>6.740800970913425</v>
       </c>
       <c r="C3">
-        <v>223.6937819029338</v>
+        <v>73.44783200401024</v>
       </c>
       <c r="D3">
-        <v>14.95639601986166</v>
+        <v>8.570171060370395</v>
       </c>
       <c r="E3">
-        <v>0.04170970084255876</v>
+        <v>0.1267551318157019</v>
       </c>
       <c r="F3">
-        <v>0.02215275596179456</v>
+        <v>0.02972792423966863</v>
       </c>
       <c r="G3">
-        <v>25.51096196797369</v>
+        <v>10.50084666955623</v>
       </c>
       <c r="H3">
-        <v>10.7672304687681</v>
+        <v>4.638210684642331</v>
       </c>
       <c r="I3">
-        <v>0.04170970084255876</v>
+        <v>0.1267551318157019</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>65.85000739087288</v>
+        <v>22.32727272727273</v>
       </c>
       <c r="C4">
-        <v>8129.864550907178</v>
+        <v>1029.512727272727</v>
       </c>
       <c r="D4">
-        <v>90.16576152236046</v>
+        <v>32.08602074537644</v>
       </c>
       <c r="E4">
-        <v>0.157813292054903</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.1406258082192888</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G4">
-        <v>50.04890570486778</v>
+        <v>9.140243858576918</v>
       </c>
       <c r="H4">
-        <v>47.69574529451023</v>
+        <v>14.10000000000002</v>
       </c>
       <c r="I4">
-        <v>0.1578132920549029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.9716274901024</v>
+        <v>9.892623508815397</v>
       </c>
       <c r="C5">
-        <v>288.767628710486</v>
+        <v>110.3030965172467</v>
       </c>
       <c r="D5">
-        <v>16.99316417594104</v>
+        <v>10.50252810123575</v>
       </c>
       <c r="E5">
-        <v>0.0002115395604691539</v>
+        <v>0.7850248760228866</v>
       </c>
       <c r="F5">
-        <v>-0.02019230657094973</v>
+        <v>0.7611387511365407</v>
       </c>
       <c r="G5">
-        <v>22.14251020658477</v>
+        <v>14.42569213865134</v>
       </c>
       <c r="H5">
-        <v>11.0318794045555</v>
+        <v>9.712320302425553</v>
       </c>
       <c r="I5">
-        <v>0.0002115395604690429</v>
+        <v>0.7850248760228866</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>47.8862242804854</v>
+        <v>14.81590317265144</v>
       </c>
       <c r="C6">
-        <v>6505.352059840414</v>
+        <v>440.2059612540071</v>
       </c>
       <c r="D6">
-        <v>63.48626725895862</v>
+        <v>18.63968098754708</v>
       </c>
       <c r="E6">
-        <v>0.06333200652419671</v>
+        <v>0.413695775824967</v>
       </c>
       <c r="F6">
-        <v>0.04421633318795581</v>
+        <v>0.3485508620277411</v>
       </c>
       <c r="G6">
-        <v>84.11720260021775</v>
+        <v>36.757147188602</v>
       </c>
       <c r="H6">
-        <v>42.38325226169527</v>
+        <v>11.66032965396263</v>
       </c>
       <c r="I6">
-        <v>0.06333200652419665</v>
+        <v>0.413695775824967</v>
       </c>
     </row>
   </sheetData>
@@ -4303,176 +4092,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>100.5983590252119</v>
+        <v>30.43195933703567</v>
       </c>
       <c r="C2">
-        <v>17379.08253855231</v>
+        <v>1393.321033472063</v>
       </c>
       <c r="D2">
-        <v>131.8297483064893</v>
+        <v>37.32721572086596</v>
       </c>
       <c r="E2">
-        <v>0.05359347944139636</v>
+        <v>0.3460459695951265</v>
       </c>
       <c r="F2">
-        <v>0.03427906065448616</v>
+        <v>0.2733844106612516</v>
       </c>
       <c r="G2">
-        <v>238.7630081849203</v>
+        <v>157.4406723046976</v>
       </c>
       <c r="H2">
-        <v>100.0429591934188</v>
+        <v>28.92409632082919</v>
       </c>
       <c r="I2">
-        <v>0.05359347944139636</v>
+        <v>0.3460459695951265</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.12430943152839</v>
+        <v>7.295685019884015</v>
       </c>
       <c r="C3">
-        <v>223.69378514292</v>
+        <v>79.59607907796027</v>
       </c>
       <c r="D3">
-        <v>14.95639612817607</v>
+        <v>8.921663470337819</v>
       </c>
       <c r="E3">
-        <v>0.04170968696265875</v>
+        <v>0.05365664736536646</v>
       </c>
       <c r="F3">
-        <v>0.02215274179863136</v>
+        <v>-0.05149261403848171</v>
       </c>
       <c r="G3">
-        <v>25.51119822979927</v>
+        <v>11.31293542056737</v>
       </c>
       <c r="H3">
-        <v>10.76690804903447</v>
+        <v>5.276454691972276</v>
       </c>
       <c r="I3">
-        <v>0.04170968696265887</v>
+        <v>0.05365664736536657</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>65.8534763569772</v>
+        <v>22.32727272727273</v>
       </c>
       <c r="C4">
-        <v>8129.864950126333</v>
+        <v>1029.512727272727</v>
       </c>
       <c r="D4">
-        <v>90.16576373616725</v>
+        <v>32.08602074537644</v>
       </c>
       <c r="E4">
-        <v>0.1578132506991012</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.1406257660194911</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="G4">
-        <v>50.06525021482001</v>
+        <v>9.140243858576918</v>
       </c>
       <c r="H4">
-        <v>47.70176257983763</v>
+        <v>14.10000000000002</v>
       </c>
       <c r="I4">
-        <v>0.1578132506991012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.97168467736236</v>
+        <v>13.95438742210717</v>
       </c>
       <c r="C5">
-        <v>288.7676280989641</v>
+        <v>330.5418475770354</v>
       </c>
       <c r="D5">
-        <v>16.99316415794787</v>
+        <v>18.18080987131859</v>
       </c>
       <c r="E5">
-        <v>0.0002115416777166423</v>
+        <v>0.355790753785531</v>
       </c>
       <c r="F5">
-        <v>-0.02019230441049324</v>
+        <v>0.2842119486505901</v>
       </c>
       <c r="G5">
-        <v>22.14258292092857</v>
+        <v>28.81650008990628</v>
       </c>
       <c r="H5">
-        <v>11.03267830528205</v>
+        <v>16.06385980220439</v>
       </c>
       <c r="I5">
-        <v>0.0002115416777167534</v>
+        <v>0.3557907537855312</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>47.88695737276996</v>
+        <v>18.5023261265749</v>
       </c>
       <c r="C6">
-        <v>6505.352225480131</v>
+        <v>708.2429218499466</v>
       </c>
       <c r="D6">
-        <v>63.4862680821951</v>
+        <v>24.1289274519747</v>
       </c>
       <c r="E6">
-        <v>0.06333198969521825</v>
+        <v>0.188873342686506</v>
       </c>
       <c r="F6">
-        <v>0.04421631601552883</v>
+        <v>0.09874815854056221</v>
       </c>
       <c r="G6">
-        <v>84.12050988761703</v>
+        <v>51.67758791843703</v>
       </c>
       <c r="H6">
-        <v>42.38607703189324</v>
+        <v>16.09110270375147</v>
       </c>
       <c r="I6">
-        <v>0.0633319896952183</v>
+        <v>0.188873342686506</v>
       </c>
     </row>
   </sheetData>
@@ -4487,176 +4276,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>98.0011711905231</v>
+        <v>9.679664420775948</v>
       </c>
       <c r="C2">
-        <v>16648.61023394446</v>
+        <v>192.9259532024618</v>
       </c>
       <c r="D2">
-        <v>129.0294936591803</v>
+        <v>13.88977873122757</v>
       </c>
       <c r="E2">
-        <v>0.09337255009341516</v>
+        <v>0.909450369559083</v>
       </c>
       <c r="F2">
-        <v>0.03550271286533535</v>
+        <v>0.8706433850844042</v>
       </c>
       <c r="G2">
-        <v>213.6849963897367</v>
+        <v>57.28434970245569</v>
       </c>
       <c r="H2">
-        <v>93.54565298408323</v>
+        <v>5.380836973151546</v>
       </c>
       <c r="I2">
-        <v>0.09337255009341516</v>
+        <v>0.909450369559083</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>11.38770890916648</v>
+        <v>5.203277552552851</v>
       </c>
       <c r="C3">
-        <v>204.2943931298636</v>
+        <v>55.53384829555377</v>
       </c>
       <c r="D3">
-        <v>14.29315896258989</v>
+        <v>7.452103615460119</v>
       </c>
       <c r="E3">
-        <v>0.1248154801479654</v>
+        <v>0.3397402385958803</v>
       </c>
       <c r="F3">
-        <v>0.06895263845528243</v>
+        <v>0.05677176942268614</v>
       </c>
       <c r="G3">
-        <v>23.80112464621239</v>
+        <v>8.071023979749192</v>
       </c>
       <c r="H3">
-        <v>9.562943564177765</v>
+        <v>3.729422866570246</v>
       </c>
       <c r="I3">
-        <v>0.1248154801479656</v>
+        <v>0.3397402385958803</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>61.28425258735685</v>
+        <v>19.12760877208812</v>
       </c>
       <c r="C4">
-        <v>7390.526516485918</v>
+        <v>790.3465745211633</v>
       </c>
       <c r="D4">
-        <v>85.96817153159603</v>
+        <v>28.11310325313026</v>
       </c>
       <c r="E4">
-        <v>0.2344025957719446</v>
+        <v>0.2323100496145754</v>
       </c>
       <c r="F4">
-        <v>0.1855346763531325</v>
+        <v>-0.09669992912203518</v>
       </c>
       <c r="G4">
-        <v>44.39473256806328</v>
+        <v>7.916017389382368</v>
       </c>
       <c r="H4">
-        <v>41.88854091358417</v>
+        <v>14.52657702577102</v>
       </c>
       <c r="I4">
-        <v>0.2344025957719446</v>
+        <v>0.2323100496145754</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>13.05927605951512</v>
+        <v>4.738503544002092</v>
       </c>
       <c r="C5">
-        <v>274.7378375731138</v>
+        <v>36.32458708689315</v>
       </c>
       <c r="D5">
-        <v>16.5752175724216</v>
+        <v>6.026988226875273</v>
       </c>
       <c r="E5">
-        <v>0.04878631694863877</v>
+        <v>0.9292052276048177</v>
       </c>
       <c r="F5">
-        <v>-0.01192945005463963</v>
+        <v>0.8988646108640254</v>
       </c>
       <c r="G5">
-        <v>21.50162752972338</v>
+        <v>5.570944700574753</v>
       </c>
       <c r="H5">
-        <v>11.01726866315143</v>
+        <v>3.710741840657093</v>
       </c>
       <c r="I5">
-        <v>0.04878631694863866</v>
+        <v>0.9292052276048177</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>45.93310218664039</v>
+        <v>9.687263572354752</v>
       </c>
       <c r="C6">
-        <v>6129.542245283339</v>
+        <v>268.782740776518</v>
       </c>
       <c r="D6">
-        <v>61.46651043144696</v>
+        <v>13.87049345667331</v>
       </c>
       <c r="E6">
-        <v>0.125344235740491</v>
+        <v>0.602676471343589</v>
       </c>
       <c r="F6">
-        <v>0.06951514440477766</v>
+        <v>0.4323949590622701</v>
       </c>
       <c r="G6">
-        <v>75.84562028343396</v>
+        <v>19.7105839430405</v>
       </c>
       <c r="H6">
-        <v>39.00360153124915</v>
+        <v>6.836894676537476</v>
       </c>
       <c r="I6">
-        <v>0.125344235740491</v>
+        <v>0.602676471343589</v>
       </c>
     </row>
   </sheetData>
@@ -4671,176 +4460,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>97.69659342730803</v>
+        <v>10.97532918431244</v>
       </c>
       <c r="C2">
-        <v>16771.24329095106</v>
+        <v>205.8764612832678</v>
       </c>
       <c r="D2">
-        <v>129.5038350434112</v>
+        <v>14.34839577385806</v>
       </c>
       <c r="E2">
-        <v>0.08669436529685759</v>
+        <v>0.9033720597139142</v>
       </c>
       <c r="F2">
-        <v>0.0283982609541038</v>
+        <v>0.8619600853055918</v>
       </c>
       <c r="G2">
-        <v>219.733384529777</v>
+        <v>64.46696153173846</v>
       </c>
       <c r="H2">
-        <v>94.60852155871873</v>
+        <v>7.398118893620961</v>
       </c>
       <c r="I2">
-        <v>0.08669436529685748</v>
+        <v>0.9033720597139142</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>11.49671166722123</v>
+        <v>4.994018362771272</v>
       </c>
       <c r="C3">
-        <v>206.7033719449706</v>
+        <v>55.96507327401947</v>
       </c>
       <c r="D3">
-        <v>14.37718233677832</v>
+        <v>7.48098076952611</v>
       </c>
       <c r="E3">
-        <v>0.1144955641907371</v>
+        <v>0.3346132663054321</v>
       </c>
       <c r="F3">
-        <v>0.05797400445823098</v>
+        <v>0.04944752329347435</v>
       </c>
       <c r="G3">
-        <v>24.1162773342043</v>
+        <v>7.784361275801394</v>
       </c>
       <c r="H3">
-        <v>9.699320437368513</v>
+        <v>2.996973266739474</v>
       </c>
       <c r="I3">
-        <v>0.1144955641907371</v>
+        <v>0.3346132663054322</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>61.20460266314026</v>
+        <v>19.42398341187271</v>
       </c>
       <c r="C4">
-        <v>7469.666247559385</v>
+        <v>797.5028909343688</v>
       </c>
       <c r="D4">
-        <v>86.42723093770496</v>
+        <v>28.24009367786107</v>
       </c>
       <c r="E4">
-        <v>0.2262043743670152</v>
+        <v>0.2253588811407642</v>
       </c>
       <c r="F4">
-        <v>0.176813164220229</v>
+        <v>-0.1066301697989083</v>
       </c>
       <c r="G4">
-        <v>45.34318420283291</v>
+        <v>8.03096150021592</v>
       </c>
       <c r="H4">
-        <v>40.69001563330357</v>
+        <v>14.96293719606138</v>
       </c>
       <c r="I4">
-        <v>0.2262043743670152</v>
+        <v>0.2253588811407643</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>12.93685089400243</v>
+        <v>5.364599564185789</v>
       </c>
       <c r="C5">
-        <v>277.0932031605188</v>
+        <v>39.18517578839717</v>
       </c>
       <c r="D5">
-        <v>16.64611675918798</v>
+        <v>6.259806369880555</v>
       </c>
       <c r="E5">
-        <v>0.04063143011135795</v>
+        <v>0.9236300857441611</v>
       </c>
       <c r="F5">
-        <v>-0.02060486158366182</v>
+        <v>0.8909001224916586</v>
       </c>
       <c r="G5">
-        <v>21.6553306536923</v>
+        <v>6.770742743450725</v>
       </c>
       <c r="H5">
-        <v>10.77601537661963</v>
+        <v>5.196405557302697</v>
       </c>
       <c r="I5">
-        <v>0.04063143011135806</v>
+        <v>0.9236300857441611</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>45.83368966291799</v>
+        <v>10.18948263078555</v>
       </c>
       <c r="C6">
-        <v>6181.176528403983</v>
+        <v>274.6324003200133</v>
       </c>
       <c r="D6">
-        <v>61.73859126927061</v>
+        <v>14.08231914778145</v>
       </c>
       <c r="E6">
-        <v>0.117006433491492</v>
+        <v>0.596743573226068</v>
       </c>
       <c r="F6">
-        <v>0.06064514201222548</v>
+        <v>0.4239193903229541</v>
       </c>
       <c r="G6">
-        <v>77.71204418012663</v>
+        <v>21.76325676280162</v>
       </c>
       <c r="H6">
-        <v>38.94346825150261</v>
+        <v>7.638608728431127</v>
       </c>
       <c r="I6">
-        <v>0.117006433491492</v>
+        <v>0.596743573226068</v>
       </c>
     </row>
   </sheetData>
@@ -4855,176 +4644,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>101.2242018229437</v>
+        <v>27.95454351267378</v>
       </c>
       <c r="C2">
-        <v>25324.84588178204</v>
+        <v>1610.280151835785</v>
       </c>
       <c r="D2">
-        <v>159.1378204003751</v>
+        <v>40.12829614917365</v>
       </c>
       <c r="E2">
-        <v>-0.3791061306885732</v>
+        <v>0.2442163937266814</v>
       </c>
       <c r="F2">
-        <v>-0.4072511537638501</v>
+        <v>0.1602404374740903</v>
       </c>
       <c r="G2">
-        <v>95.1141812935045</v>
+        <v>63.918622322872</v>
       </c>
       <c r="H2">
-        <v>46.65146630736417</v>
+        <v>14.63290969418151</v>
       </c>
       <c r="I2">
-        <v>0.02420975511320989</v>
+        <v>0.4842733401901038</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>12.54941715435306</v>
+        <v>10.02085702383019</v>
       </c>
       <c r="C3">
-        <v>230.1110174532339</v>
+        <v>129.7829336994978</v>
       </c>
       <c r="D3">
-        <v>15.16941058358016</v>
+        <v>11.3922312871315</v>
       </c>
       <c r="E3">
-        <v>0.01421866142721517</v>
+        <v>-0.5430309886451312</v>
       </c>
       <c r="F3">
-        <v>-0.005899325074270267</v>
+        <v>-0.7144788762723679</v>
       </c>
       <c r="G3">
-        <v>25.12786540144864</v>
+        <v>14.05213124338457</v>
       </c>
       <c r="H3">
-        <v>11.11623770630729</v>
+        <v>11.06076556000318</v>
       </c>
       <c r="I3">
-        <v>0.0386637314452879</v>
+        <v>0.1266927301389354</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>173.6366971566488</v>
+        <v>206.7809556805961</v>
       </c>
       <c r="C4">
-        <v>37949.8765829827</v>
+        <v>43787.87645329037</v>
       </c>
       <c r="D4">
-        <v>194.8072806210864</v>
+        <v>209.2555290865462</v>
       </c>
       <c r="E4">
-        <v>-2.931293249255739</v>
+        <v>-41.53262275765005</v>
       </c>
       <c r="F4">
-        <v>-3.011523723730345</v>
+        <v>-46.25846973072228</v>
       </c>
       <c r="G4">
-        <v>65.4373518109233</v>
+        <v>75.01223567975612</v>
       </c>
       <c r="H4">
-        <v>193.9120720321577</v>
+        <v>209.6810146886268</v>
       </c>
       <c r="I4">
-        <v>0.07840237060330679</v>
+        <v>-9.114703036772198E-08</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>15.16638485203424</v>
+        <v>17.2052965685299</v>
       </c>
       <c r="C5">
-        <v>325.3743559938584</v>
+        <v>420.1208981291327</v>
       </c>
       <c r="D5">
-        <v>18.03813615631777</v>
+        <v>20.49685093201228</v>
       </c>
       <c r="E5">
-        <v>-0.1265304490613453</v>
+        <v>0.1812057411591793</v>
       </c>
       <c r="F5">
-        <v>-0.1495208663891279</v>
+        <v>0.09022860128797694</v>
       </c>
       <c r="G5">
-        <v>23.28045217523622</v>
+        <v>19.74295354983274</v>
       </c>
       <c r="H5">
-        <v>13.38155251822839</v>
+        <v>14.15877479478122</v>
       </c>
       <c r="I5">
-        <v>-0.00154966522770561</v>
+        <v>0.7069957253830426</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>75.64417524649492</v>
+        <v>65.49041319640749</v>
       </c>
       <c r="C6">
-        <v>15957.55195955295</v>
+        <v>11487.0151092387</v>
       </c>
       <c r="D6">
-        <v>96.78816194033985</v>
+        <v>70.31822686371589</v>
       </c>
       <c r="E6">
-        <v>-0.8556777918946106</v>
+        <v>-10.41255790285233</v>
       </c>
       <c r="F6">
-        <v>-0.8935487672393984</v>
+        <v>-11.68061989205815</v>
       </c>
       <c r="G6">
-        <v>52.23996267027817</v>
+        <v>43.18148569896135</v>
       </c>
       <c r="H6">
-        <v>66.26533214101437</v>
+        <v>62.38336618439817</v>
       </c>
       <c r="I6">
-        <v>0.03493154798352474</v>
+        <v>0.3294904261412629</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/models/tables/all_model_metrics.xlsx
+++ b/outputs/models/tables/all_model_metrics.xlsx
@@ -27,15 +27,13 @@
     <sheet name="metrics__K Nearest Neighbors Th" sheetId="18" r:id="rId18"/>
     <sheet name="metrics__Support Vector Regress" sheetId="19" r:id="rId19"/>
     <sheet name="metrics__Gaussian Process Regre" sheetId="20" r:id="rId20"/>
-    <sheet name="metrics__Extreme Gradient Boost" sheetId="21" r:id="rId21"/>
-    <sheet name="metrics__Light Gradient Boostin" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="42">
   <si>
     <t>model</t>
   </si>
@@ -70,28 +68,19 @@
     <t>Extra Trees</t>
   </si>
   <si>
-    <t>K Nearest Neighbors Five</t>
-  </si>
-  <si>
-    <t>K Nearest Neighbors Three</t>
+    <t>Decision Tree</t>
   </si>
   <si>
     <t>Bagging Regressor</t>
   </si>
   <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
     <t>Polynomial Regression Degree 3</t>
   </si>
   <si>
-    <t>Decision Tree</t>
-  </si>
-  <si>
-    <t>Polynomial Ridge Degree 3</t>
-  </si>
-  <si>
     <t>Support Vector Regression</t>
-  </si>
-  <si>
-    <t>Random Forest</t>
   </si>
   <si>
     <t>Polynomial Regression Degree 2</t>
@@ -103,9 +92,6 @@
     <t>Linear Regression</t>
   </si>
   <si>
-    <t>Extreme Gradient Boosting</t>
-  </si>
-  <si>
     <t>Lasso Regression</t>
   </si>
   <si>
@@ -115,10 +101,16 @@
     <t>Ridge Regression</t>
   </si>
   <si>
-    <t>Histogram Gradient Boosting</t>
+    <t>K Nearest Neighbors Five</t>
   </si>
   <si>
-    <t>Light Gradient Boosting</t>
+    <t>K Nearest Neighbors Three</t>
+  </si>
+  <si>
+    <t>Polynomial Ridge Degree 3</t>
+  </si>
+  <si>
+    <t>Histogram Gradient Boosting</t>
   </si>
   <si>
     <t>Stochastic Gradient Regression</t>
@@ -524,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -555,19 +547,19 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>3.168732906387079</v>
+        <v>3.352380071380857</v>
       </c>
       <c r="C2">
-        <v>6.525074842751619</v>
+        <v>7.490347085127204</v>
       </c>
       <c r="D2">
-        <v>0.9455637350402234</v>
+        <v>0.9186481118372842</v>
       </c>
       <c r="E2">
-        <v>0.9395152611558036</v>
+        <v>0.9118687878237246</v>
       </c>
       <c r="F2">
-        <v>9.736368691795033</v>
+        <v>10.33248135795984</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -578,19 +570,19 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>3.929159497152678</v>
+        <v>4.52130048637139</v>
       </c>
       <c r="C3">
-        <v>6.822468374053738</v>
+        <v>7.848740004166213</v>
       </c>
       <c r="D3">
-        <v>0.9420084422883457</v>
+        <v>0.9143535482814524</v>
       </c>
       <c r="E3">
-        <v>0.9355649358759397</v>
+        <v>0.9072163439715735</v>
       </c>
       <c r="F3">
-        <v>15.47612307072269</v>
+        <v>17.81413203485885</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -601,19 +593,19 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.803787878787881</v>
+        <v>4.994553571428572</v>
       </c>
       <c r="C4">
-        <v>7.100246612458202</v>
+        <v>8.350237732030237</v>
       </c>
       <c r="D4">
-        <v>0.9339239374684735</v>
+        <v>0.9086560452830199</v>
       </c>
       <c r="E4">
-        <v>0.9265821527427482</v>
+        <v>0.901044049056605</v>
       </c>
       <c r="F4">
-        <v>10.00170950606536</v>
+        <v>10.7317434073068</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -624,19 +616,19 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>5.775431818181824</v>
+        <v>7.27885211640207</v>
       </c>
       <c r="C5">
-        <v>7.822140196304651</v>
+        <v>9.598162906480946</v>
       </c>
       <c r="D5">
-        <v>0.9190809984302347</v>
+        <v>0.8870326089380014</v>
       </c>
       <c r="E5">
-        <v>0.9100899982558164</v>
+        <v>0.8776186596828348</v>
       </c>
       <c r="F5">
-        <v>15.62301835777778</v>
+        <v>18.61605578615462</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -647,19 +639,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>3.220000000000001</v>
+        <v>9.405833333333334</v>
       </c>
       <c r="C6">
-        <v>8.079737322128098</v>
+        <v>11.90708057405086</v>
       </c>
       <c r="D6">
-        <v>0.9010022116065129</v>
+        <v>0.8395422978097675</v>
       </c>
       <c r="E6">
-        <v>0.89000245734057</v>
+        <v>0.8261708226272482</v>
       </c>
       <c r="F6">
-        <v>6.552485325108222</v>
+        <v>20.84090261367143</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -670,19 +662,19 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>3.220000000000001</v>
+        <v>9.945483482142858</v>
       </c>
       <c r="C7">
-        <v>8.079737322128098</v>
+        <v>12.89428456536625</v>
       </c>
       <c r="D7">
-        <v>0.9010022116065129</v>
+        <v>0.81358447085416</v>
       </c>
       <c r="E7">
-        <v>0.89000245734057</v>
+        <v>0.79804984342534</v>
       </c>
       <c r="F7">
-        <v>6.552485325108222</v>
+        <v>20.89000868207015</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -693,19 +685,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>6.724683766233768</v>
+        <v>10.64943109565036</v>
       </c>
       <c r="C8">
-        <v>9.014969095534857</v>
+        <v>14.20191255247596</v>
       </c>
       <c r="D8">
-        <v>0.8883535513059304</v>
+        <v>0.7741271154704554</v>
       </c>
       <c r="E8">
-        <v>0.8759483903399227</v>
+        <v>0.7553043750929934</v>
       </c>
       <c r="F8">
-        <v>14.80270446040569</v>
+        <v>22.24528501761244</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -716,19 +708,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>9.687263572354752</v>
+        <v>14.48011672793636</v>
       </c>
       <c r="C9">
-        <v>13.87049345667331</v>
+        <v>20.33457760275129</v>
       </c>
       <c r="D9">
-        <v>0.602676471343589</v>
+        <v>0.4762210209648448</v>
       </c>
       <c r="E9">
-        <v>0.4323949590622701</v>
+        <v>0.3190873272542982</v>
       </c>
       <c r="F9">
-        <v>19.7105839430405</v>
+        <v>25.58396066056122</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -739,19 +731,19 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>10.83068181818182</v>
+        <v>12.31186742106223</v>
       </c>
       <c r="C10">
-        <v>13.99155594877365</v>
+        <v>21.76376782966211</v>
       </c>
       <c r="D10">
-        <v>0.6394045833539457</v>
+        <v>0.4112792158705586</v>
       </c>
       <c r="E10">
-        <v>0.5993384259488284</v>
+        <v>0.3622191505264385</v>
       </c>
       <c r="F10">
-        <v>22.80088606951673</v>
+        <v>25.70818259397801</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -762,19 +754,19 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>10.18948263078555</v>
+        <v>17.07534542753056</v>
       </c>
       <c r="C11">
-        <v>14.08231914778145</v>
+        <v>22.50055028561906</v>
       </c>
       <c r="D11">
-        <v>0.596743573226068</v>
+        <v>0.4019472518502805</v>
       </c>
       <c r="E11">
-        <v>0.4239193903229541</v>
+        <v>0.2932103885503314</v>
       </c>
       <c r="F11">
-        <v>21.76325676280162</v>
+        <v>33.89866841714797</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -785,19 +777,19 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>8.160169082257129</v>
+        <v>17.07526361925966</v>
       </c>
       <c r="C12">
-        <v>14.79953532527325</v>
+        <v>22.50055028743339</v>
       </c>
       <c r="D12">
-        <v>0.5514224295634942</v>
+        <v>0.4019472517571439</v>
       </c>
       <c r="E12">
-        <v>0.5015804772927714</v>
+        <v>0.2932103884402609</v>
       </c>
       <c r="F12">
-        <v>15.128891198559</v>
+        <v>33.89861337410156</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -808,19 +800,19 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>11.0568203838243</v>
+        <v>17.58637526846502</v>
       </c>
       <c r="C13">
-        <v>14.93980984405228</v>
+        <v>24.02370698363448</v>
       </c>
       <c r="D13">
-        <v>0.6035202991550379</v>
+        <v>0.3321183132319596</v>
       </c>
       <c r="E13">
-        <v>0.5594669990611532</v>
+        <v>0.2764615060012896</v>
       </c>
       <c r="F13">
-        <v>25.36427941689524</v>
+        <v>37.86706591949187</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -831,19 +823,19 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>13.70488226603412</v>
+        <v>17.58637565411988</v>
       </c>
       <c r="C14">
-        <v>16.96819961741376</v>
+        <v>24.02370698363722</v>
       </c>
       <c r="D14">
-        <v>0.5068381739464329</v>
+        <v>0.332118313231722</v>
       </c>
       <c r="E14">
-        <v>0.3835477174330411</v>
+        <v>0.2764615060010323</v>
       </c>
       <c r="F14">
-        <v>31.19930956978714</v>
+        <v>37.86706986545299</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -854,19 +846,19 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>13.29933925905086</v>
+        <v>17.58638342629325</v>
       </c>
       <c r="C15">
-        <v>17.11935361275002</v>
+        <v>24.02370698396665</v>
       </c>
       <c r="D15">
-        <v>0.4991561221423056</v>
+        <v>0.3321183132199413</v>
       </c>
       <c r="E15">
-        <v>0.3739451526778821</v>
+        <v>0.2764615059882699</v>
       </c>
       <c r="F15">
-        <v>31.17984184084805</v>
+        <v>37.86711074396536</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -877,19 +869,19 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>14.26188733626295</v>
+        <v>17.58638523634016</v>
       </c>
       <c r="C16">
-        <v>18.50032274622348</v>
+        <v>24.02370698411692</v>
       </c>
       <c r="D16">
-        <v>0.4291297958482495</v>
+        <v>0.3321183132150149</v>
       </c>
       <c r="E16">
-        <v>0.3656997731647216</v>
+        <v>0.2764615059829329</v>
       </c>
       <c r="F16">
-        <v>35.28442817873522</v>
+        <v>37.86711925484783</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -900,19 +892,19 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>13.59132550326261</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C17">
-        <v>18.51985693081643</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="D17">
-        <v>0.5366126757423844</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="E17">
-        <v>0.485125195269316</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="F17">
-        <v>35.8066922066379</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -923,19 +915,19 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>14.81590317265144</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C18">
-        <v>18.63968098754708</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="D18">
-        <v>0.413695775824967</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="E18">
-        <v>0.3485508620277411</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="F18">
-        <v>36.757147188602</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -946,19 +938,19 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>18.5023261265749</v>
+        <v>21.08132541145396</v>
       </c>
       <c r="C19">
-        <v>24.1289274519747</v>
+        <v>29.78566177295085</v>
       </c>
       <c r="D19">
-        <v>0.188873342686506</v>
+        <v>0.06338891693132301</v>
       </c>
       <c r="E19">
-        <v>0.09874815854056221</v>
+        <v>-0.2175944079892801</v>
       </c>
       <c r="F19">
-        <v>51.67758791843703</v>
+        <v>49.73564455388451</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -969,19 +961,19 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>20.81129154393988</v>
+        <v>21.80005102040816</v>
       </c>
       <c r="C20">
-        <v>27.49656691612221</v>
+        <v>30.8200775199298</v>
       </c>
       <c r="D20">
-        <v>0.001287141375970385</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.1096809540266996</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="F20">
-        <v>59.64493902013724</v>
+        <v>51.86540618403083</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -992,68 +984,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>20.82553719008264</v>
+        <v>56.87433699333061</v>
       </c>
       <c r="C21">
-        <v>27.51682461542172</v>
+        <v>62.66107261418601</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>-3.36311947070695</v>
       </c>
       <c r="E21">
-        <v>-0.1111111111111112</v>
+        <v>-3.726712759932529</v>
       </c>
       <c r="F21">
-        <v>59.69155634320034</v>
+        <v>48.04105268799751</v>
       </c>
       <c r="G21">
         <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22">
-        <v>20.82553719540273</v>
-      </c>
-      <c r="C22">
-        <v>27.51682461542173</v>
-      </c>
-      <c r="D22">
-        <v>-2.220446049250313E-16</v>
-      </c>
-      <c r="E22">
-        <v>-0.1111111111111114</v>
-      </c>
-      <c r="F22">
-        <v>59.69155641166542</v>
-      </c>
-      <c r="G22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23">
-        <v>65.49041319640749</v>
-      </c>
-      <c r="C23">
-        <v>70.31822686371589</v>
-      </c>
-      <c r="D23">
-        <v>-10.41255790285233</v>
-      </c>
-      <c r="E23">
-        <v>-11.68061989205815</v>
-      </c>
-      <c r="F23">
-        <v>43.18148569896135</v>
-      </c>
-      <c r="G23">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1068,176 +1014,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>13.25454545454546</v>
+        <v>11.18523809523809</v>
       </c>
       <c r="C2">
-        <v>246.4873454545454</v>
+        <v>201.3859261904761</v>
       </c>
       <c r="D2">
-        <v>15.69991546010823</v>
+        <v>14.19105091917002</v>
       </c>
       <c r="E2">
-        <v>0.8843113761068258</v>
+        <v>0.8803477478228072</v>
       </c>
       <c r="F2">
-        <v>0.8714570845631397</v>
+        <v>0.8703767268080411</v>
       </c>
       <c r="G2">
-        <v>66.72422293708199</v>
+        <v>58.07192754245103</v>
       </c>
       <c r="H2">
-        <v>9.340000000000002</v>
+        <v>9.435833333333328</v>
       </c>
       <c r="I2">
-        <v>0.8843113761068258</v>
+        <v>0.8803477478228072</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>5.054545454545456</v>
+        <v>4.207142857142858</v>
       </c>
       <c r="C3">
-        <v>45.89818181818183</v>
+        <v>23.39107142857144</v>
       </c>
       <c r="D3">
-        <v>6.774819688979318</v>
+        <v>4.83643168343888</v>
       </c>
       <c r="E3">
-        <v>0.4543017725897102</v>
+        <v>0.8531707765440903</v>
       </c>
       <c r="F3">
-        <v>0.3936686362107891</v>
+        <v>0.8409350079227645</v>
       </c>
       <c r="G3">
-        <v>7.829599500681778</v>
+        <v>7.268140300799806</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.524999999999999</v>
       </c>
       <c r="I3">
-        <v>0.4543017725897103</v>
+        <v>0.8531707765440903</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>18.80636363636364</v>
+        <v>15.00714285714286</v>
       </c>
       <c r="C4">
-        <v>710.0305</v>
+        <v>336.815773809524</v>
       </c>
       <c r="D4">
-        <v>26.64639750510376</v>
+        <v>18.35254134471638</v>
       </c>
       <c r="E4">
-        <v>0.3103237277299765</v>
+        <v>0.8556964367356024</v>
       </c>
       <c r="F4">
-        <v>0.2336930308110851</v>
+        <v>0.8436711397969026</v>
       </c>
       <c r="G4">
-        <v>7.686864203472761</v>
+        <v>6.80814351818554</v>
       </c>
       <c r="H4">
-        <v>7.279999999999973</v>
+        <v>15.44583333333333</v>
       </c>
       <c r="I4">
-        <v>0.3103237277299765</v>
+        <v>0.8556964367356024</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>6.207272727272727</v>
+        <v>7.223809523809522</v>
       </c>
       <c r="C5">
-        <v>46.85527272727272</v>
+        <v>105.027619047619</v>
       </c>
       <c r="D5">
-        <v>6.845091140903291</v>
+        <v>10.24829834887817</v>
       </c>
       <c r="E5">
-        <v>0.9086814569892698</v>
+        <v>0.7689542301365704</v>
       </c>
       <c r="F5">
-        <v>0.8985349522102998</v>
+        <v>0.7497004159812846</v>
       </c>
       <c r="G5">
-        <v>8.962857636830362</v>
+        <v>11.21539909324933</v>
       </c>
       <c r="H5">
-        <v>5.679999999999993</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>0.9086814569892698</v>
+        <v>0.7689542301365704</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>10.83068181818182</v>
+        <v>9.405833333333334</v>
       </c>
       <c r="C6">
-        <v>262.317825</v>
+        <v>166.6550976190477</v>
       </c>
       <c r="D6">
-        <v>13.99155594877365</v>
+        <v>11.90708057405086</v>
       </c>
       <c r="E6">
-        <v>0.6394045833539457</v>
+        <v>0.8395422978097675</v>
       </c>
       <c r="F6">
-        <v>0.5993384259488284</v>
+        <v>0.8261708226272482</v>
       </c>
       <c r="G6">
-        <v>22.80088606951673</v>
+        <v>20.84090261367143</v>
       </c>
       <c r="H6">
-        <v>6.324999999999992</v>
+        <v>8.351666666666663</v>
       </c>
       <c r="I6">
-        <v>0.6394045833539457</v>
+        <v>0.8395422978097675</v>
       </c>
     </row>
   </sheetData>
@@ -1252,176 +1198,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>13.97605639615074</v>
+        <v>11.20179695011338</v>
       </c>
       <c r="C2">
-        <v>307.3139954052415</v>
+        <v>224.7096343972572</v>
       </c>
       <c r="D2">
-        <v>17.53037351014637</v>
+        <v>14.99031802188523</v>
       </c>
       <c r="E2">
-        <v>0.855762440193499</v>
+        <v>0.8664901050924733</v>
       </c>
       <c r="F2">
-        <v>0.8397360446594433</v>
+        <v>0.855364280516846</v>
       </c>
       <c r="G2">
-        <v>74.29985338447671</v>
+        <v>58.90464254253096</v>
       </c>
       <c r="H2">
-        <v>11.52832196763556</v>
+        <v>8.386608544973544</v>
       </c>
       <c r="I2">
-        <v>0.8577562203721193</v>
+        <v>0.8678324828815218</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>4.934404165963904</v>
+        <v>4.73816678004534</v>
       </c>
       <c r="C3">
-        <v>50.13956699622341</v>
+        <v>42.66476898952453</v>
       </c>
       <c r="D3">
-        <v>7.08092981155889</v>
+        <v>6.531827385159878</v>
       </c>
       <c r="E3">
-        <v>0.4038745817569633</v>
+        <v>0.7321869193214529</v>
       </c>
       <c r="F3">
-        <v>0.3376384241744037</v>
+        <v>0.7098691625982405</v>
       </c>
       <c r="G3">
-        <v>7.834792686970203</v>
+        <v>8.831622888899272</v>
       </c>
       <c r="H3">
-        <v>3.76988516800661</v>
+        <v>3.799534920634933</v>
       </c>
       <c r="I3">
-        <v>0.4059087374080069</v>
+        <v>0.7323021588655974</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>18.26356283381114</v>
+        <v>19.56376118154327</v>
       </c>
       <c r="C4">
-        <v>749.1395120409427</v>
+        <v>621.5268394215173</v>
       </c>
       <c r="D4">
-        <v>27.37041307764541</v>
+        <v>24.93044001660455</v>
       </c>
       <c r="E4">
-        <v>0.2723358418059763</v>
+        <v>0.7337163382267701</v>
       </c>
       <c r="F4">
-        <v>0.1914842686733069</v>
+        <v>0.711526033079001</v>
       </c>
       <c r="G4">
-        <v>7.586571264359497</v>
+        <v>9.410596220698149</v>
       </c>
       <c r="H4">
-        <v>12.47782523191063</v>
+        <v>17.369032539682</v>
       </c>
       <c r="I4">
-        <v>0.2727676461070295</v>
+        <v>0.7337254489870485</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>7.053258139371438</v>
+        <v>7.093999470899462</v>
       </c>
       <c r="C5">
-        <v>60.48986365556152</v>
+        <v>107.2273667275214</v>
       </c>
       <c r="D5">
-        <v>7.777522976858475</v>
+        <v>10.35506478625418</v>
       </c>
       <c r="E5">
-        <v>0.8821083328637127</v>
+        <v>0.7641150992411256</v>
       </c>
       <c r="F5">
-        <v>0.8690092587374586</v>
+        <v>0.7444580241778862</v>
       </c>
       <c r="G5">
-        <v>11.73590033177454</v>
+        <v>11.83427841832139</v>
       </c>
       <c r="H5">
-        <v>6.578865728715712</v>
+        <v>4.789012433862396</v>
       </c>
       <c r="I5">
-        <v>0.8843412218930139</v>
+        <v>0.76548862857474</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>11.0568203838243</v>
+        <v>10.64943109565036</v>
       </c>
       <c r="C6">
-        <v>291.7707345244923</v>
+        <v>249.0321523839551</v>
       </c>
       <c r="D6">
-        <v>14.93980984405228</v>
+        <v>14.20191255247596</v>
       </c>
       <c r="E6">
-        <v>0.6035202991550379</v>
+        <v>0.7741271154704554</v>
       </c>
       <c r="F6">
-        <v>0.5594669990611532</v>
+        <v>0.7553043750929934</v>
       </c>
       <c r="G6">
-        <v>25.36427941689524</v>
+        <v>22.24528501761244</v>
       </c>
       <c r="H6">
-        <v>8.588724524067128</v>
+        <v>8.586047109788218</v>
       </c>
       <c r="I6">
-        <v>0.6051934564450424</v>
+        <v>0.7748371798272269</v>
       </c>
     </row>
   </sheetData>
@@ -1436,176 +1382,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>9.563818181818187</v>
+        <v>9.744504761904759</v>
       </c>
       <c r="C2">
-        <v>191.5524752727271</v>
+        <v>174.6017692153439</v>
       </c>
       <c r="D2">
-        <v>13.8402483819015</v>
+        <v>13.21369627376624</v>
       </c>
       <c r="E2">
-        <v>0.910095010245791</v>
+        <v>0.8962613956400378</v>
       </c>
       <c r="F2">
-        <v>0.9001055669397677</v>
+        <v>0.8876165119433743</v>
       </c>
       <c r="G2">
-        <v>51.55576117821987</v>
+        <v>56.14016639137427</v>
       </c>
       <c r="H2">
-        <v>7.685000000000002</v>
+        <v>8.945161111110981</v>
       </c>
       <c r="I2">
-        <v>0.910095010245791</v>
+        <v>0.8962613956400378</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>2.173727272727254</v>
+        <v>2.996882539682586</v>
       </c>
       <c r="C3">
-        <v>7.955941181818178</v>
+        <v>12.10389356684306</v>
       </c>
       <c r="D3">
-        <v>2.820627799235159</v>
+        <v>3.479065042054123</v>
       </c>
       <c r="E3">
-        <v>0.9054092596195418</v>
+        <v>0.9240220654859893</v>
       </c>
       <c r="F3">
-        <v>0.8948991773550464</v>
+        <v>0.9176905709431551</v>
       </c>
       <c r="G3">
-        <v>3.03819745829305</v>
+        <v>4.85607386447903</v>
       </c>
       <c r="H3">
-        <v>1.04549999999999</v>
+        <v>3.131877777777873</v>
       </c>
       <c r="I3">
-        <v>0.9054092596195418</v>
+        <v>0.9240220654859893</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>7.460636363636357</v>
+        <v>10.21884021164004</v>
       </c>
       <c r="C4">
-        <v>87.59577548863668</v>
+        <v>141.4562546553184</v>
       </c>
       <c r="D4">
-        <v>9.359261482010035</v>
+        <v>11.89353835724754</v>
       </c>
       <c r="E4">
-        <v>0.9149153058838954</v>
+        <v>0.9393952327056326</v>
       </c>
       <c r="F4">
-        <v>0.905461450982106</v>
+        <v>0.934344835431102</v>
       </c>
       <c r="G4">
-        <v>2.672558718613042</v>
+        <v>4.368872825302105</v>
       </c>
       <c r="H4">
-        <v>5.440999999999974</v>
+        <v>10.70506666666506</v>
       </c>
       <c r="I4">
-        <v>0.9149153058838954</v>
+        <v>0.9393952327056326</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>3.903545454545497</v>
+        <v>6.1551809523809</v>
       </c>
       <c r="C5">
-        <v>27.75628219318187</v>
+        <v>96.16453862328039</v>
       </c>
       <c r="D5">
-        <v>5.268423122071904</v>
+        <v>9.806351952855882</v>
       </c>
       <c r="E5">
-        <v>0.9459044179717108</v>
+        <v>0.7884517419203456</v>
       </c>
       <c r="F5">
-        <v>0.9398937977463453</v>
+        <v>0.7708227204137078</v>
       </c>
       <c r="G5">
-        <v>5.225556075985178</v>
+        <v>9.099110063463067</v>
       </c>
       <c r="H5">
-        <v>2.649999999999999</v>
+        <v>4.25</v>
       </c>
       <c r="I5">
-        <v>0.9459044179717109</v>
+        <v>0.7884517419203456</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>5.775431818181824</v>
+        <v>7.27885211640207</v>
       </c>
       <c r="C6">
-        <v>78.71511853409096</v>
+        <v>106.0816140151965</v>
       </c>
       <c r="D6">
-        <v>7.822140196304651</v>
+        <v>9.598162906480946</v>
       </c>
       <c r="E6">
-        <v>0.9190809984302347</v>
+        <v>0.8870326089380014</v>
       </c>
       <c r="F6">
-        <v>0.9100899982558164</v>
+        <v>0.8776186596828348</v>
       </c>
       <c r="G6">
-        <v>15.62301835777778</v>
+        <v>18.61605578615462</v>
       </c>
       <c r="H6">
-        <v>4.205374999999991</v>
+        <v>6.758026388888479</v>
       </c>
       <c r="I6">
-        <v>0.9190809984302348</v>
+        <v>0.8870326089380014</v>
       </c>
     </row>
   </sheetData>
@@ -1620,176 +1566,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>6.34328253830785</v>
+        <v>5.547003887826607</v>
       </c>
       <c r="C2">
-        <v>158.108541205525</v>
+        <v>141.3121283968491</v>
       </c>
       <c r="D2">
-        <v>12.57412188606127</v>
+        <v>11.88747779795399</v>
       </c>
       <c r="E2">
-        <v>0.9257918919768743</v>
+        <v>0.9160402380519714</v>
       </c>
       <c r="F2">
-        <v>0.9175465466409715</v>
+        <v>0.9090435912229691</v>
       </c>
       <c r="G2">
-        <v>33.8986182619173</v>
+        <v>32.57685910751209</v>
       </c>
       <c r="H2">
-        <v>0.1969198433984625</v>
+        <v>0.01996302596227473</v>
       </c>
       <c r="I2">
-        <v>0.9259447936407934</v>
+        <v>0.9188843216893332</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>1.044618748490738</v>
+        <v>1.103320129706783</v>
       </c>
       <c r="C3">
-        <v>5.025972571669175</v>
+        <v>4.993944690047625</v>
       </c>
       <c r="D3">
-        <v>2.241868098633185</v>
+        <v>2.234713558836484</v>
       </c>
       <c r="E3">
-        <v>0.9402445976130989</v>
+        <v>0.9686522687487583</v>
       </c>
       <c r="F3">
-        <v>0.9336051084589987</v>
+        <v>0.9660399578111548</v>
       </c>
       <c r="G3">
-        <v>1.486280049618761</v>
+        <v>1.556304175908757</v>
       </c>
       <c r="H3">
-        <v>0.1194433504510215</v>
+        <v>0.004925863845340217</v>
       </c>
       <c r="I3">
-        <v>0.9402688669004993</v>
+        <v>0.9687861808663898</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>3.218205890881886</v>
+        <v>2.964023435646182</v>
       </c>
       <c r="C4">
-        <v>47.33994036641047</v>
+        <v>42.20397466564071</v>
       </c>
       <c r="D4">
-        <v>6.880402631126356</v>
+        <v>6.496458624946419</v>
       </c>
       <c r="E4">
-        <v>0.9540171392617766</v>
+        <v>0.9819183529937157</v>
       </c>
       <c r="F4">
-        <v>0.948907932513085</v>
+        <v>0.9804115490765253</v>
       </c>
       <c r="G4">
-        <v>1.184873424484606</v>
+        <v>1.066088054274457</v>
       </c>
       <c r="H4">
-        <v>0.3121006433261755</v>
+        <v>0.007191736280468319</v>
       </c>
       <c r="I4">
-        <v>0.9540447951779945</v>
+        <v>0.9821539730635134</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>2.068824447867843</v>
+        <v>3.795172832343855</v>
       </c>
       <c r="C5">
-        <v>19.39439470836994</v>
+        <v>87.28676004046827</v>
       </c>
       <c r="D5">
-        <v>4.403906755185665</v>
+        <v>9.342738358771921</v>
       </c>
       <c r="E5">
-        <v>0.9622013113091435</v>
+        <v>0.8079815875546916</v>
       </c>
       <c r="F5">
-        <v>0.9580014570101595</v>
+        <v>0.7919800531842492</v>
       </c>
       <c r="G5">
-        <v>2.375703031159464</v>
+        <v>6.130674094144062</v>
       </c>
       <c r="H5">
-        <v>0.1226353632516179</v>
+        <v>0.007198414576095047</v>
       </c>
       <c r="I5">
-        <v>0.9622728510127037</v>
+        <v>0.8105557421850719</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>3.168732906387079</v>
+        <v>3.352380071380857</v>
       </c>
       <c r="C6">
-        <v>57.46721221299364</v>
+        <v>68.94920194825141</v>
       </c>
       <c r="D6">
-        <v>6.525074842751619</v>
+        <v>7.490347085127204</v>
       </c>
       <c r="E6">
-        <v>0.9455637350402234</v>
+        <v>0.9186481118372842</v>
       </c>
       <c r="F6">
-        <v>0.9395152611558036</v>
+        <v>0.9118687878237246</v>
       </c>
       <c r="G6">
-        <v>9.736368691795033</v>
+        <v>10.33248135795984</v>
       </c>
       <c r="H6">
-        <v>0.1877748001068194</v>
+        <v>0.009819760166044578</v>
       </c>
       <c r="I6">
-        <v>0.9456328266829976</v>
+        <v>0.9200950544510771</v>
       </c>
     </row>
   </sheetData>
@@ -1804,176 +1750,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>6.444848484848484</v>
+        <v>6.385833333333335</v>
       </c>
       <c r="C2">
-        <v>157.4016080808081</v>
+        <v>139.9965470238095</v>
       </c>
       <c r="D2">
-        <v>12.54597975770757</v>
+        <v>11.83201365042356</v>
       </c>
       <c r="E2">
-        <v>0.9261236904318099</v>
+        <v>0.9168218829125843</v>
       </c>
       <c r="F2">
-        <v>0.9179152115908998</v>
+        <v>0.9098903731552996</v>
       </c>
       <c r="G2">
-        <v>33.6225747820874</v>
+        <v>30.71379985486174</v>
       </c>
       <c r="H2">
         <v>0.8333333333333357</v>
       </c>
       <c r="I2">
-        <v>0.926172116574601</v>
+        <v>0.9173606543729681</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>1.496969696969699</v>
+        <v>1.738095238095237</v>
       </c>
       <c r="C3">
-        <v>5.922828282828292</v>
+        <v>7.060634920634918</v>
       </c>
       <c r="D3">
-        <v>2.433686151258681</v>
+        <v>2.657185526197769</v>
       </c>
       <c r="E3">
-        <v>0.9295815919681029</v>
+        <v>0.9556793477516298</v>
       </c>
       <c r="F3">
-        <v>0.9217573244090032</v>
+        <v>0.9519859600642656</v>
       </c>
       <c r="G3">
-        <v>2.047934623809187</v>
+        <v>2.401144235243257</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.7499999999999929</v>
       </c>
       <c r="I3">
-        <v>0.929739242839113</v>
+        <v>0.9558958453142707</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>4.912727272727282</v>
+        <v>6.759285714285718</v>
       </c>
       <c r="C4">
-        <v>62.47425454545468</v>
+        <v>87.81028650793662</v>
       </c>
       <c r="D4">
-        <v>7.904065697187409</v>
+        <v>9.370714300838364</v>
       </c>
       <c r="E4">
-        <v>0.9393166758501814</v>
+        <v>0.9623790266974587</v>
       </c>
       <c r="F4">
-        <v>0.9325740842779794</v>
+        <v>0.9592439455889136</v>
       </c>
       <c r="G4">
-        <v>1.759629540987499</v>
+        <v>2.454784806808297</v>
       </c>
       <c r="H4">
-        <v>0.04000000000002046</v>
+        <v>5.683333333333337</v>
       </c>
       <c r="I4">
-        <v>0.939820215035533</v>
+        <v>0.9625806183610094</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>2.360606060606059</v>
+        <v>5.094999999999998</v>
       </c>
       <c r="C5">
-        <v>30.44010101010101</v>
+        <v>91.03139563492061</v>
       </c>
       <c r="D5">
-        <v>5.517254843679147</v>
+        <v>9.541037450661255</v>
       </c>
       <c r="E5">
-        <v>0.9406737916237996</v>
+        <v>0.7997439237704067</v>
       </c>
       <c r="F5">
-        <v>0.9340819906931107</v>
+        <v>0.7830559174179406</v>
       </c>
       <c r="G5">
-        <v>2.576699077377372</v>
+        <v>7.357244732313917</v>
       </c>
       <c r="H5">
-        <v>0.06666666666666288</v>
+        <v>0.62083333333333</v>
       </c>
       <c r="I5">
-        <v>0.9451300843903921</v>
+        <v>0.799940969249874</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>3.803787878787881</v>
+        <v>4.994553571428572</v>
       </c>
       <c r="C6">
-        <v>64.05969797979802</v>
+        <v>81.47471602182542</v>
       </c>
       <c r="D6">
-        <v>7.100246612458202</v>
+        <v>8.350237732030237</v>
       </c>
       <c r="E6">
-        <v>0.9339239374684735</v>
+        <v>0.9086560452830199</v>
       </c>
       <c r="F6">
-        <v>0.9265821527427482</v>
+        <v>0.901044049056605</v>
       </c>
       <c r="G6">
-        <v>10.00170950606536</v>
+        <v>10.7317434073068</v>
       </c>
       <c r="H6">
-        <v>0.4850000000000048</v>
+        <v>1.971874999999999</v>
       </c>
       <c r="I6">
-        <v>0.9352154147099099</v>
+        <v>0.9089445218245306</v>
       </c>
     </row>
   </sheetData>
@@ -1988,57 +1934,57 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>36.81785123966942</v>
+        <v>29.58285714285715</v>
       </c>
       <c r="C2">
-        <v>2130.610056198347</v>
+        <v>1683.093485714286</v>
       </c>
       <c r="D2">
-        <v>46.15853178122488</v>
+        <v>41.02552236979178</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>-0.1111111111111112</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="G2">
-        <v>182.0811323591802</v>
+        <v>140.2043443286067</v>
       </c>
       <c r="H2">
-        <v>34.12727272727273</v>
+        <v>21.79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2046,57 +1992,57 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>7.600000000000003</v>
+        <v>9.354081632653058</v>
       </c>
       <c r="C3">
-        <v>84.10909090909091</v>
+        <v>159.3080102040817</v>
       </c>
       <c r="D3">
-        <v>9.171100855900065</v>
+        <v>12.62172770281793</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>-0.1111111111111112</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="G3">
-        <v>11.75830913886914</v>
+        <v>17.74311782890865</v>
       </c>
       <c r="H3">
-        <v>6.199999999999989</v>
+        <v>7.064285714285703</v>
       </c>
       <c r="I3">
-        <v>-2.220446049250313E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>22.32727272727273</v>
+        <v>32.10306122448979</v>
       </c>
       <c r="C4">
-        <v>1029.512727272727</v>
+        <v>2334.078010204082</v>
       </c>
       <c r="D4">
-        <v>32.08602074537644</v>
+        <v>48.31229667697534</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>-0.1111111111111112</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="G4">
-        <v>9.140243858576918</v>
+        <v>16.6410616884347</v>
       </c>
       <c r="H4">
-        <v>14.10000000000002</v>
+        <v>22.53571428571428</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2104,57 +2050,57 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>16.55702479338843</v>
+        <v>16.16020408163265</v>
       </c>
       <c r="C5">
-        <v>513.0970247933884</v>
+        <v>454.5749489795918</v>
       </c>
       <c r="D5">
-        <v>22.6516450791855</v>
+        <v>21.32076333013412</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>-0.1111111111111112</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="G5">
-        <v>35.78654001617511</v>
+        <v>32.8731008901733</v>
       </c>
       <c r="H5">
-        <v>17.64545454545454</v>
+        <v>13.29285714285713</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-2.220446049250313E-16</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>20.82553719008264</v>
+        <v>21.80005102040816</v>
       </c>
       <c r="C6">
-        <v>939.3322247933884</v>
+        <v>1157.76361377551</v>
       </c>
       <c r="D6">
-        <v>27.51682461542172</v>
+        <v>30.8200775199298</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>-0.1111111111111112</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="G6">
-        <v>59.69155634320034</v>
+        <v>51.86540618403083</v>
       </c>
       <c r="H6">
-        <v>18.01818181818182</v>
+        <v>16.17071428571428</v>
       </c>
       <c r="I6">
         <v>-5.551115123125783E-17</v>
@@ -2172,176 +2118,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>10.12122424242424</v>
+        <v>11.30476428571428</v>
       </c>
       <c r="C2">
-        <v>211.945667877015</v>
+        <v>225.6083918291567</v>
       </c>
       <c r="D2">
-        <v>14.55835388624054</v>
+        <v>15.02026603722972</v>
       </c>
       <c r="E2">
-        <v>0.9005234828116834</v>
+        <v>0.865956113701307</v>
       </c>
       <c r="F2">
-        <v>0.889470536457426</v>
+        <v>0.8547857898430826</v>
       </c>
       <c r="G2">
-        <v>43.46202850258808</v>
+        <v>55.43836192495155</v>
       </c>
       <c r="H2">
-        <v>5.6875</v>
+        <v>8.551895833333329</v>
       </c>
       <c r="I2">
-        <v>0.9041274448355769</v>
+        <v>0.870053822148988</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>2.620575757575752</v>
+        <v>4.348476190476187</v>
       </c>
       <c r="C3">
-        <v>11.19873648242629</v>
+        <v>30.45792862003967</v>
       </c>
       <c r="D3">
-        <v>3.346451326767848</v>
+        <v>5.518870230404016</v>
       </c>
       <c r="E3">
-        <v>0.8668546246144735</v>
+        <v>0.8088110661791487</v>
       </c>
       <c r="F3">
-        <v>0.8520606940160816</v>
+        <v>0.7928786550274111</v>
       </c>
       <c r="G3">
-        <v>4.038850053088233</v>
+        <v>7.648256241692383</v>
       </c>
       <c r="H3">
-        <v>1.73670238095238</v>
+        <v>3.654999999999987</v>
       </c>
       <c r="I3">
-        <v>0.8696476468732007</v>
+        <v>0.8097421870952792</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>9.775651515151521</v>
+        <v>17.01513988095239</v>
       </c>
       <c r="C4">
-        <v>154.6198909587197</v>
+        <v>425.9112810809776</v>
       </c>
       <c r="D4">
-        <v>12.43462468105571</v>
+        <v>20.63761810580324</v>
       </c>
       <c r="E4">
-        <v>0.8498125502845197</v>
+        <v>0.8175248302674606</v>
       </c>
       <c r="F4">
-        <v>0.8331250558716886</v>
+        <v>0.8023185661230823</v>
       </c>
       <c r="G4">
-        <v>3.872868201305543</v>
+        <v>7.808682415642464</v>
       </c>
       <c r="H4">
-        <v>7.482500000000016</v>
+        <v>15.90499999999994</v>
       </c>
       <c r="I4">
-        <v>0.8500671859412223</v>
+        <v>0.8177246363479393</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>4.381283549783554</v>
+        <v>7.113553571428571</v>
       </c>
       <c r="C5">
-        <v>32.72350802293341</v>
+        <v>108.1679850183531</v>
       </c>
       <c r="D5">
-        <v>5.720446488075333</v>
+        <v>10.40038388802803</v>
       </c>
       <c r="E5">
-        <v>0.9362235475130452</v>
+        <v>0.7620458732687239</v>
       </c>
       <c r="F5">
-        <v>0.9291372750144946</v>
+        <v>0.7422163627077842</v>
       </c>
       <c r="G5">
-        <v>7.837071084640885</v>
+        <v>12.66473414599422</v>
       </c>
       <c r="H5">
-        <v>3.143500000000003</v>
+        <v>5.110416666666669</v>
       </c>
       <c r="I5">
-        <v>0.9405344463030664</v>
+        <v>0.7673903392117379</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>6.724683766233768</v>
+        <v>9.945483482142858</v>
       </c>
       <c r="C6">
-        <v>102.6219508352736</v>
+        <v>197.5363966371318</v>
       </c>
       <c r="D6">
-        <v>9.014969095534857</v>
+        <v>12.89428456536625</v>
       </c>
       <c r="E6">
-        <v>0.8883535513059304</v>
+        <v>0.81358447085416</v>
       </c>
       <c r="F6">
-        <v>0.8759483903399227</v>
+        <v>0.79804984342534</v>
       </c>
       <c r="G6">
-        <v>14.80270446040569</v>
+        <v>20.89000868207015</v>
       </c>
       <c r="H6">
-        <v>4.5125505952381</v>
+        <v>8.305578124999982</v>
       </c>
       <c r="I6">
-        <v>0.8910941809882665</v>
+        <v>0.8162277462009861</v>
       </c>
     </row>
   </sheetData>
@@ -2356,176 +2302,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>5.170909090909091</v>
+        <v>23.82523809523809</v>
       </c>
       <c r="C2">
-        <v>174.6574545454546</v>
+        <v>1358.989868430335</v>
       </c>
       <c r="D2">
-        <v>13.21580321227032</v>
+        <v>36.8644797661697</v>
       </c>
       <c r="E2">
-        <v>0.91802467371383</v>
+        <v>0.192564239618814</v>
       </c>
       <c r="F2">
-        <v>0.9089163041264778</v>
+        <v>0.1252779262537151</v>
       </c>
       <c r="G2">
-        <v>20.67319567921897</v>
+        <v>89.51563936683232</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="I2">
-        <v>0.920379679964459</v>
+        <v>0.250581756450024</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>1.50909090909091</v>
+        <v>9.28809523809524</v>
       </c>
       <c r="C3">
-        <v>13.32727272727274</v>
+        <v>153.5173985890652</v>
       </c>
       <c r="D3">
-        <v>3.650653739711936</v>
+        <v>12.39021382337953</v>
       </c>
       <c r="E3">
-        <v>0.841547773454388</v>
+        <v>0.03634852765782681</v>
       </c>
       <c r="F3">
-        <v>0.8239419705048756</v>
+        <v>-0.04395576170402093</v>
       </c>
       <c r="G3">
-        <v>1.996786661418645</v>
+        <v>17.46387395743525</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7.044444444444444</v>
       </c>
       <c r="I3">
-        <v>0.8686239830208701</v>
+        <v>0.0368868892004296</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>4.381818181818186</v>
+        <v>35.8015873015873</v>
       </c>
       <c r="C4">
-        <v>117.238181818182</v>
+        <v>2324.184144620812</v>
       </c>
       <c r="D4">
-        <v>10.82765818716965</v>
+        <v>48.20979303648598</v>
       </c>
       <c r="E4">
-        <v>0.8861226493734016</v>
+        <v>0.004238875281809995</v>
       </c>
       <c r="F4">
-        <v>0.8734696104148907</v>
+        <v>-0.07874121844470583</v>
       </c>
       <c r="G4">
-        <v>1.524355069777134</v>
+        <v>17.42832607359704</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>31.50555555555555</v>
       </c>
       <c r="I4">
-        <v>0.9047725699327869</v>
+        <v>0.02928593934982482</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>1.818181818181818</v>
+        <v>13.31746031746031</v>
       </c>
       <c r="C5">
-        <v>21.38909090909091</v>
+        <v>386.5201940035274</v>
       </c>
       <c r="D5">
-        <v>4.624834149360484</v>
+        <v>19.66011683595821</v>
       </c>
       <c r="E5">
-        <v>0.9583137498844322</v>
+        <v>0.1497107465530833</v>
       </c>
       <c r="F5">
-        <v>0.9536819443160358</v>
+        <v>0.07885330876584018</v>
       </c>
       <c r="G5">
-        <v>2.015603890018136</v>
+        <v>29.86622669604085</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>8.049999999999997</v>
       </c>
       <c r="I5">
-        <v>0.9594502610464343</v>
+        <v>0.215911185649081</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>3.220000000000001</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C6">
-        <v>81.65300000000005</v>
+        <v>1055.802901410935</v>
       </c>
       <c r="D6">
-        <v>8.079737322128098</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="E6">
-        <v>0.9010022116065129</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="F6">
-        <v>0.89000245734057</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="G6">
-        <v>6.552485325108222</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>15.12222222222222</v>
       </c>
       <c r="I6">
-        <v>0.9133066234911374</v>
+        <v>0.1331664426623398</v>
       </c>
     </row>
   </sheetData>
@@ -2540,176 +2486,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>5.170909090909091</v>
+        <v>23.82523809523809</v>
       </c>
       <c r="C2">
-        <v>174.6574545454546</v>
+        <v>1358.989868430335</v>
       </c>
       <c r="D2">
-        <v>13.21580321227032</v>
+        <v>36.8644797661697</v>
       </c>
       <c r="E2">
-        <v>0.91802467371383</v>
+        <v>0.192564239618814</v>
       </c>
       <c r="F2">
-        <v>0.9089163041264778</v>
+        <v>0.1252779262537151</v>
       </c>
       <c r="G2">
-        <v>20.67319567921897</v>
+        <v>89.51563936683232</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="I2">
-        <v>0.920379679964459</v>
+        <v>0.250581756450024</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>1.50909090909091</v>
+        <v>9.28809523809524</v>
       </c>
       <c r="C3">
-        <v>13.32727272727274</v>
+        <v>153.5173985890652</v>
       </c>
       <c r="D3">
-        <v>3.650653739711936</v>
+        <v>12.39021382337953</v>
       </c>
       <c r="E3">
-        <v>0.841547773454388</v>
+        <v>0.03634852765782681</v>
       </c>
       <c r="F3">
-        <v>0.8239419705048756</v>
+        <v>-0.04395576170402093</v>
       </c>
       <c r="G3">
-        <v>1.996786661418645</v>
+        <v>17.46387395743525</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7.044444444444444</v>
       </c>
       <c r="I3">
-        <v>0.8686239830208701</v>
+        <v>0.0368868892004296</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>4.381818181818186</v>
+        <v>35.8015873015873</v>
       </c>
       <c r="C4">
-        <v>117.238181818182</v>
+        <v>2324.184144620812</v>
       </c>
       <c r="D4">
-        <v>10.82765818716965</v>
+        <v>48.20979303648598</v>
       </c>
       <c r="E4">
-        <v>0.8861226493734016</v>
+        <v>0.004238875281809995</v>
       </c>
       <c r="F4">
-        <v>0.8734696104148907</v>
+        <v>-0.07874121844470583</v>
       </c>
       <c r="G4">
-        <v>1.524355069777134</v>
+        <v>17.42832607359704</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>31.50555555555555</v>
       </c>
       <c r="I4">
-        <v>0.9047725699327869</v>
+        <v>0.02928593934982482</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>1.818181818181818</v>
+        <v>13.31746031746031</v>
       </c>
       <c r="C5">
-        <v>21.38909090909091</v>
+        <v>386.5201940035274</v>
       </c>
       <c r="D5">
-        <v>4.624834149360484</v>
+        <v>19.66011683595821</v>
       </c>
       <c r="E5">
-        <v>0.9583137498844322</v>
+        <v>0.1497107465530833</v>
       </c>
       <c r="F5">
-        <v>0.9536819443160358</v>
+        <v>0.07885330876584018</v>
       </c>
       <c r="G5">
-        <v>2.015603890018136</v>
+        <v>29.86622669604085</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>8.049999999999997</v>
       </c>
       <c r="I5">
-        <v>0.9594502610464343</v>
+        <v>0.215911185649081</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>3.220000000000001</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C6">
-        <v>81.65300000000005</v>
+        <v>1055.802901410935</v>
       </c>
       <c r="D6">
-        <v>8.079737322128098</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="E6">
-        <v>0.9010022116065129</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="F6">
-        <v>0.89000245734057</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="G6">
-        <v>6.552485325108222</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>15.12222222222222</v>
       </c>
       <c r="I6">
-        <v>0.9133066234911374</v>
+        <v>0.1331664426623398</v>
       </c>
     </row>
   </sheetData>
@@ -2724,176 +2670,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>9.135099089440038</v>
+        <v>9.446195671540888</v>
       </c>
       <c r="C2">
-        <v>227.9373152924311</v>
+        <v>192.4685111243765</v>
       </c>
       <c r="D2">
-        <v>15.09759302976574</v>
+        <v>13.87330209879308</v>
       </c>
       <c r="E2">
-        <v>0.8930178168317011</v>
+        <v>0.8856459770309817</v>
       </c>
       <c r="F2">
-        <v>0.8811309075907791</v>
+        <v>0.8761164751168968</v>
       </c>
       <c r="G2">
-        <v>42.23687468370606</v>
+        <v>63.97577783465798</v>
       </c>
       <c r="H2">
-        <v>3.756718469895498</v>
+        <v>5.117490080971982</v>
       </c>
       <c r="I2">
-        <v>0.9006139593466382</v>
+        <v>0.8875182305539248</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>4.171119630410671</v>
+        <v>6.703953457269698</v>
       </c>
       <c r="C3">
-        <v>60.37912349261862</v>
+        <v>142.6746175357007</v>
       </c>
       <c r="D3">
-        <v>7.770400471830176</v>
+        <v>11.94464807081819</v>
       </c>
       <c r="E3">
-        <v>0.2821332053406778</v>
+        <v>0.1044102719447233</v>
       </c>
       <c r="F3">
-        <v>0.2023702281563087</v>
+        <v>0.02977779460678354</v>
       </c>
       <c r="G3">
-        <v>6.932090168535715</v>
+        <v>14.26744988320347</v>
       </c>
       <c r="H3">
-        <v>1.354704521937407</v>
+        <v>2.823378514546043</v>
       </c>
       <c r="I3">
-        <v>0.3064817405987508</v>
+        <v>0.1237868851464625</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>15.62165657083344</v>
+        <v>26.73518541278025</v>
       </c>
       <c r="C4">
-        <v>929.6358678901887</v>
+        <v>2598.207069926513</v>
       </c>
       <c r="D4">
-        <v>30.48993059831702</v>
+        <v>50.97261097811759</v>
       </c>
       <c r="E4">
-        <v>0.09701371992468866</v>
+        <v>-0.1131620530966473</v>
       </c>
       <c r="F4">
-        <v>-0.003318088972568134</v>
+        <v>-0.2059255575213679</v>
       </c>
       <c r="G4">
-        <v>7.064922940042305</v>
+        <v>15.88588951691986</v>
       </c>
       <c r="H4">
-        <v>0.1403619432329037</v>
+        <v>10.09913308669061</v>
       </c>
       <c r="I4">
-        <v>0.2039621979361006</v>
+        <v>0.08419040624466256</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>3.712801038344377</v>
+        <v>6.362135142658091</v>
       </c>
       <c r="C5">
-        <v>34.10813695695931</v>
+        <v>105.3601690489118</v>
       </c>
       <c r="D5">
-        <v>5.840217201180048</v>
+        <v>10.2645101709196</v>
       </c>
       <c r="E5">
-        <v>0.9335249761569094</v>
+        <v>0.7682226676031767</v>
       </c>
       <c r="F5">
-        <v>0.9261388623965661</v>
+        <v>0.7489078899034414</v>
       </c>
       <c r="G5">
-        <v>4.281677001951937</v>
+        <v>8.703613141130717</v>
       </c>
       <c r="H5">
-        <v>0.8063517488198499</v>
+        <v>3.207255368886877</v>
       </c>
       <c r="I5">
-        <v>0.9335409817172351</v>
+        <v>0.7708767769947198</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>8.160169082257129</v>
+        <v>12.31186742106223</v>
       </c>
       <c r="C6">
-        <v>313.0151109080495</v>
+        <v>759.6775919088756</v>
       </c>
       <c r="D6">
-        <v>14.79953532527325</v>
+        <v>21.76376782966211</v>
       </c>
       <c r="E6">
-        <v>0.5514224295634942</v>
+        <v>0.4112792158705586</v>
       </c>
       <c r="F6">
-        <v>0.5015804772927714</v>
+        <v>0.3622191505264385</v>
       </c>
       <c r="G6">
-        <v>15.128891198559</v>
+        <v>25.70818259397801</v>
       </c>
       <c r="H6">
-        <v>1.514534170971415</v>
+        <v>5.311814262773879</v>
       </c>
       <c r="I6">
-        <v>0.5861497198996812</v>
+        <v>0.4665930747349424</v>
       </c>
     </row>
   </sheetData>
@@ -2908,72 +2854,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12.54597975770757</v>
+        <v>11.83201365042356</v>
       </c>
       <c r="D2">
-        <v>0.9261236904318099</v>
+        <v>0.9168218829125843</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.231636211036968</v>
+        <v>2.217968823452416</v>
       </c>
       <c r="D3">
-        <v>0.9407888002999073</v>
+        <v>0.9691202865725025</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>6.846584112358198</v>
+        <v>6.34826935136047</v>
       </c>
       <c r="D4">
-        <v>0.9544680577851876</v>
+        <v>0.9827338574026928</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>4.389801766206672</v>
+        <v>9.112072159657277</v>
       </c>
       <c r="D5">
-        <v>0.9624430495297631</v>
+        <v>0.8173461621033391</v>
       </c>
     </row>
   </sheetData>
@@ -2988,544 +2934,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>9.464835827635261</v>
+        <v>10.08782696009768</v>
       </c>
       <c r="C2">
-        <v>191.043576306493</v>
+        <v>188.1464785040516</v>
       </c>
       <c r="D2">
-        <v>13.82185140661312</v>
+        <v>13.71664968219469</v>
       </c>
       <c r="E2">
-        <v>0.9103338615385246</v>
+        <v>0.8882138870472757</v>
       </c>
       <c r="F2">
-        <v>0.9003709572650274</v>
+        <v>0.8788983776345486</v>
       </c>
       <c r="G2">
-        <v>56.71946161767452</v>
+        <v>62.53985981558836</v>
       </c>
       <c r="H2">
-        <v>5.160384664613204</v>
+        <v>6.959710172616424</v>
       </c>
       <c r="I2">
-        <v>0.9103347316036985</v>
+        <v>0.8882140212639021</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>1.047657967859604</v>
+        <v>1.136230829833945</v>
       </c>
       <c r="C3">
-        <v>4.980200178411433</v>
+        <v>4.919385701806893</v>
       </c>
       <c r="D3">
-        <v>2.231636211036968</v>
+        <v>2.217968823452416</v>
       </c>
       <c r="E3">
-        <v>0.9407888002999073</v>
+        <v>0.9691202865725025</v>
       </c>
       <c r="F3">
-        <v>0.9342097781110081</v>
+        <v>0.966546977120211</v>
       </c>
       <c r="G3">
-        <v>1.47476981178906</v>
+        <v>1.610548460655721</v>
       </c>
       <c r="H3">
-        <v>0.07849850665577662</v>
+        <v>0.05879704116281204</v>
       </c>
       <c r="I3">
-        <v>0.9407888740429461</v>
+        <v>0.969120368791204</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>3.042098970418687</v>
+        <v>2.983787378796376</v>
       </c>
       <c r="C4">
-        <v>46.8757140075957</v>
+        <v>40.30052375742268</v>
       </c>
       <c r="D4">
-        <v>6.846584112358198</v>
+        <v>6.34826935136047</v>
       </c>
       <c r="E4">
-        <v>0.9544680577851876</v>
+        <v>0.9827338574026928</v>
       </c>
       <c r="F4">
-        <v>0.9494089530946529</v>
+        <v>0.9812950121862506</v>
       </c>
       <c r="G4">
-        <v>1.108844511258337</v>
+        <v>1.104173214734122</v>
       </c>
       <c r="H4">
-        <v>0.1376522039631141</v>
+        <v>0.1963008158346895</v>
       </c>
       <c r="I4">
-        <v>0.95446806816635</v>
+        <v>0.982733954291013</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>2.162045222697159</v>
+        <v>3.877356776757563</v>
       </c>
       <c r="C5">
-        <v>19.27035954659121</v>
+        <v>83.02985904280125</v>
       </c>
       <c r="D5">
-        <v>4.389801766206672</v>
+        <v>9.112072159657277</v>
       </c>
       <c r="E5">
-        <v>0.9624430495297631</v>
+        <v>0.8173461621033391</v>
       </c>
       <c r="F5">
-        <v>0.9582700550330702</v>
+        <v>0.802125008945284</v>
       </c>
       <c r="G5">
-        <v>2.60141634216883</v>
+        <v>6.001946648457192</v>
       </c>
       <c r="H5">
-        <v>0.119654179702934</v>
+        <v>0.104826742414744</v>
       </c>
       <c r="I5">
-        <v>0.9624432272390576</v>
+        <v>0.8173461647405856</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>3.929159497152678</v>
+        <v>4.52130048637139</v>
       </c>
       <c r="C6">
-        <v>65.54246250977285</v>
+        <v>79.09906175152062</v>
       </c>
       <c r="D6">
-        <v>6.822468374053738</v>
+        <v>7.848740004166213</v>
       </c>
       <c r="E6">
-        <v>0.9420084422883457</v>
+        <v>0.9143535482814524</v>
       </c>
       <c r="F6">
-        <v>0.9355649358759397</v>
+        <v>0.9072163439715735</v>
       </c>
       <c r="G6">
-        <v>15.47612307072269</v>
+        <v>17.81413203485885</v>
       </c>
       <c r="H6">
-        <v>1.374047388733757</v>
+        <v>1.829908693007167</v>
       </c>
       <c r="I6">
-        <v>0.942008725263013</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2">
-        <v>22.47874861283736</v>
-      </c>
-      <c r="C2">
-        <v>864.0970897764774</v>
-      </c>
-      <c r="D2">
-        <v>29.3955283976403</v>
-      </c>
-      <c r="E2">
-        <v>0.5944367730441074</v>
-      </c>
-      <c r="F2">
-        <v>0.5493741922712304</v>
-      </c>
-      <c r="G2">
-        <v>106.3009167342963</v>
-      </c>
-      <c r="H2">
-        <v>19.81992416381836</v>
-      </c>
-      <c r="I2">
-        <v>0.598205973018451</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3">
-        <v>4.924207097833807</v>
-      </c>
-      <c r="C3">
-        <v>41.70204206730366</v>
-      </c>
-      <c r="D3">
-        <v>6.457711829069462</v>
-      </c>
-      <c r="E3">
-        <v>0.5041910260048204</v>
-      </c>
-      <c r="F3">
-        <v>0.4491011400053559</v>
-      </c>
-      <c r="G3">
-        <v>7.764184798383268</v>
-      </c>
-      <c r="H3">
-        <v>4.405749511718753</v>
-      </c>
-      <c r="I3">
-        <v>0.5093799775864472</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4">
-        <v>16.75351534756748</v>
-      </c>
-      <c r="C4">
-        <v>586.2686375711496</v>
-      </c>
-      <c r="D4">
-        <v>24.21298489594271</v>
-      </c>
-      <c r="E4">
-        <v>0.4305377466053981</v>
-      </c>
-      <c r="F4">
-        <v>0.3672641628948868</v>
-      </c>
-      <c r="G4">
-        <v>6.900530507952373</v>
-      </c>
-      <c r="H4">
-        <v>12.94874267578126</v>
-      </c>
-      <c r="I4">
-        <v>0.4368591516329008</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5">
-        <v>10.20883095481179</v>
-      </c>
-      <c r="C5">
-        <v>196.3698471258346</v>
-      </c>
-      <c r="D5">
-        <v>14.01320260061327</v>
-      </c>
-      <c r="E5">
-        <v>0.6172851573152116</v>
-      </c>
-      <c r="F5">
-        <v>0.5747612859057907</v>
-      </c>
-      <c r="G5">
-        <v>22.26113678591969</v>
-      </c>
-      <c r="H5">
-        <v>9.317398071289062</v>
-      </c>
-      <c r="I5">
-        <v>0.6204738373261833</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6">
-        <v>13.59132550326261</v>
-      </c>
-      <c r="C6">
-        <v>422.1094041351914</v>
-      </c>
-      <c r="D6">
-        <v>18.51985693081643</v>
-      </c>
-      <c r="E6">
-        <v>0.5366126757423844</v>
-      </c>
-      <c r="F6">
-        <v>0.485125195269316</v>
-      </c>
-      <c r="G6">
-        <v>35.8066922066379</v>
-      </c>
-      <c r="H6">
-        <v>11.62295360565186</v>
-      </c>
-      <c r="I6">
-        <v>0.5412297348909956</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2">
-        <v>36.81785126725504</v>
-      </c>
-      <c r="C2">
-        <v>2130.610056198347</v>
-      </c>
-      <c r="D2">
-        <v>46.15853178122488</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>-0.1111111111111112</v>
-      </c>
-      <c r="G2">
-        <v>182.0811326658558</v>
-      </c>
-      <c r="H2">
-        <v>34.1272727879611</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3">
-        <v>7.599999981084148</v>
-      </c>
-      <c r="C3">
-        <v>84.10909090909094</v>
-      </c>
-      <c r="D3">
-        <v>9.171100855900066</v>
-      </c>
-      <c r="E3">
-        <v>-4.440892098500626E-16</v>
-      </c>
-      <c r="F3">
-        <v>-0.1111111111111116</v>
-      </c>
-      <c r="G3">
-        <v>11.75830912354077</v>
-      </c>
-      <c r="H3">
-        <v>6.200000069358126</v>
-      </c>
-      <c r="I3">
-        <v>-2.220446049250313E-16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4">
-        <v>22.32727280293615</v>
-      </c>
-      <c r="C4">
-        <v>1029.512727272728</v>
-      </c>
-      <c r="D4">
-        <v>32.08602074537645</v>
-      </c>
-      <c r="E4">
-        <v>-4.440892098500626E-16</v>
-      </c>
-      <c r="F4">
-        <v>-0.1111111111111116</v>
-      </c>
-      <c r="G4">
-        <v>9.140243858427112</v>
-      </c>
-      <c r="H4">
-        <v>14.09999916770244</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5">
-        <v>16.55702473033558</v>
-      </c>
-      <c r="C5">
-        <v>513.0970247933884</v>
-      </c>
-      <c r="D5">
-        <v>22.6516450791855</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>-0.1111111111111112</v>
-      </c>
-      <c r="G5">
-        <v>35.78653999883794</v>
-      </c>
-      <c r="H5">
-        <v>17.64545440673828</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6">
-        <v>20.82553719540273</v>
-      </c>
-      <c r="C6">
-        <v>939.3322247933886</v>
-      </c>
-      <c r="D6">
-        <v>27.51682461542173</v>
-      </c>
-      <c r="E6">
-        <v>-2.220446049250313E-16</v>
-      </c>
-      <c r="F6">
-        <v>-0.1111111111111114</v>
-      </c>
-      <c r="G6">
-        <v>59.69155641166542</v>
-      </c>
-      <c r="H6">
-        <v>18.01818160793999</v>
-      </c>
-      <c r="I6">
-        <v>-5.551115123125783E-17</v>
+        <v>0.9143536272716762</v>
       </c>
     </row>
   </sheetData>
@@ -3540,176 +3118,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>19.7635110550352</v>
+        <v>17.95974911175558</v>
       </c>
       <c r="C2">
-        <v>543.2657012332552</v>
+        <v>469.5435433409056</v>
       </c>
       <c r="D2">
-        <v>23.30806086385685</v>
+        <v>21.66895344360003</v>
       </c>
       <c r="E2">
-        <v>0.7450187097104922</v>
+        <v>0.7210234919650725</v>
       </c>
       <c r="F2">
-        <v>0.7166874552338802</v>
+        <v>0.6977754496288286</v>
       </c>
       <c r="G2">
-        <v>110.3975298333543</v>
+        <v>101.9665922988225</v>
       </c>
       <c r="H2">
-        <v>18.09499225443398</v>
+        <v>16.16582408389939</v>
       </c>
       <c r="I2">
-        <v>0.7450187097104922</v>
+        <v>0.7210234919650725</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>5.748835003635675</v>
+        <v>8.696079553061745</v>
       </c>
       <c r="C3">
-        <v>69.15334401522092</v>
+        <v>156.0043864640514</v>
       </c>
       <c r="D3">
-        <v>8.315848965392584</v>
+        <v>12.49017159465999</v>
       </c>
       <c r="E3">
-        <v>0.1778136790235297</v>
+        <v>0.02073733603098893</v>
       </c>
       <c r="F3">
-        <v>0.08645964335947753</v>
+        <v>-0.06086788596642867</v>
       </c>
       <c r="G3">
-        <v>9.049075970963221</v>
+        <v>16.85921674715309</v>
       </c>
       <c r="H3">
-        <v>3.272726123107091</v>
+        <v>6.160207037573471</v>
       </c>
       <c r="I3">
-        <v>0.1778136790235297</v>
+        <v>0.02073733603098926</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>22.07833674866333</v>
+        <v>33.11990447568959</v>
       </c>
       <c r="C4">
-        <v>1029.211924236676</v>
+        <v>2309.015001017982</v>
       </c>
       <c r="D4">
-        <v>32.08133295604589</v>
+        <v>48.05221119800817</v>
       </c>
       <c r="E4">
-        <v>0.0002921800071846725</v>
+        <v>0.01073786269204813</v>
       </c>
       <c r="F4">
-        <v>-0.1107864666586837</v>
+        <v>-0.07170064875028115</v>
       </c>
       <c r="G4">
-        <v>9.054636362132088</v>
+        <v>16.89591127308343</v>
       </c>
       <c r="H4">
-        <v>13.5783406046811</v>
+        <v>25.13420128265699</v>
       </c>
       <c r="I4">
-        <v>0.0002921800071845615</v>
+        <v>0.01073786269204813</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>9.456866537717602</v>
+        <v>10.56976793335318</v>
       </c>
       <c r="C5">
-        <v>106.0086085284574</v>
+        <v>192.7513417359244</v>
       </c>
       <c r="D5">
-        <v>10.29604819959859</v>
+        <v>13.88349169826973</v>
       </c>
       <c r="E5">
-        <v>0.7933946146517913</v>
+        <v>0.5759745622397288</v>
       </c>
       <c r="F5">
-        <v>0.7704384607242125</v>
+        <v>0.5406391090930396</v>
       </c>
       <c r="G5">
-        <v>12.6364705484913</v>
+        <v>15.7465433589085</v>
       </c>
       <c r="H5">
-        <v>9.739072428946287</v>
+        <v>9.925735630136252</v>
       </c>
       <c r="I5">
-        <v>0.7933946146517913</v>
+        <v>0.5759745622397288</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>14.26188733626295</v>
+        <v>17.58637526846502</v>
       </c>
       <c r="C6">
-        <v>436.9098945034024</v>
+        <v>781.8285681397159</v>
       </c>
       <c r="D6">
-        <v>18.50032274622348</v>
+        <v>24.02370698363448</v>
       </c>
       <c r="E6">
-        <v>0.4291297958482495</v>
+        <v>0.3321183132319596</v>
       </c>
       <c r="F6">
-        <v>0.3656997731647216</v>
+        <v>0.2764615060012896</v>
       </c>
       <c r="G6">
-        <v>35.28442817873522</v>
+        <v>37.86706591949187</v>
       </c>
       <c r="H6">
-        <v>11.17128285279211</v>
+        <v>14.34649200856653</v>
       </c>
       <c r="I6">
-        <v>0.4291297958482495</v>
+        <v>0.3321183132319597</v>
       </c>
     </row>
   </sheetData>
@@ -3724,176 +3302,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>36.78211700867913</v>
+        <v>17.95978215412796</v>
       </c>
       <c r="C2">
-        <v>2125.848940524359</v>
+        <v>469.5435434028204</v>
       </c>
       <c r="D2">
-        <v>46.10692941982104</v>
+        <v>21.66895344502868</v>
       </c>
       <c r="E2">
-        <v>0.002234625552497205</v>
+        <v>0.7210234919282862</v>
       </c>
       <c r="F2">
-        <v>-0.1086281938305587</v>
+        <v>0.6977754495889767</v>
       </c>
       <c r="G2">
-        <v>181.9432490525538</v>
+        <v>101.96670866629</v>
       </c>
       <c r="H2">
-        <v>34.1191200286468</v>
+        <v>16.16596396987104</v>
       </c>
       <c r="I2">
-        <v>0.002234625552497538</v>
+        <v>0.7210234919282862</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>7.597221702551052</v>
+        <v>8.696083677245394</v>
       </c>
       <c r="C3">
-        <v>84.06423231194414</v>
+        <v>156.00438646422</v>
       </c>
       <c r="D3">
-        <v>9.168654880185214</v>
+        <v>12.49017159466674</v>
       </c>
       <c r="E3">
-        <v>0.0005333382713081924</v>
+        <v>0.02073733602993055</v>
       </c>
       <c r="F3">
-        <v>-0.1105185130318798</v>
+        <v>-0.06086788596757509</v>
       </c>
       <c r="G3">
-        <v>11.75424302071447</v>
+        <v>16.85922221392592</v>
       </c>
       <c r="H3">
-        <v>6.191568329721036</v>
+        <v>6.160204923864832</v>
       </c>
       <c r="I3">
-        <v>0.0005333382713086365</v>
+        <v>0.02073733602993044</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>22.32689911487422</v>
+        <v>33.11988792692743</v>
       </c>
       <c r="C4">
-        <v>1029.511825037465</v>
+        <v>2309.01500101926</v>
       </c>
       <c r="D4">
-        <v>32.08600668574176</v>
+        <v>48.05221119802147</v>
       </c>
       <c r="E4">
-        <v>8.763711591974754E-07</v>
+        <v>0.01073786269150045</v>
       </c>
       <c r="F4">
-        <v>-0.1111101373653787</v>
+        <v>-0.07170064875087445</v>
       </c>
       <c r="G4">
-        <v>9.140115375654295</v>
+        <v>16.8959059864024</v>
       </c>
       <c r="H4">
-        <v>14.09792241870076</v>
+        <v>25.13418272216819</v>
       </c>
       <c r="I4">
-        <v>8.7637115941952E-07</v>
+        <v>0.01073786269150045</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>16.53892834965514</v>
+        <v>10.56978718705986</v>
       </c>
       <c r="C5">
-        <v>511.8759948175576</v>
+        <v>192.7513417492826</v>
       </c>
       <c r="D5">
-        <v>22.62467667874079</v>
+        <v>13.88349169875081</v>
       </c>
       <c r="E5">
-        <v>0.002379725308916947</v>
+        <v>0.5759745622103426</v>
       </c>
       <c r="F5">
-        <v>-0.1084669718789812</v>
+        <v>0.5406391090612044</v>
       </c>
       <c r="G5">
-        <v>35.74214863162645</v>
+        <v>15.74664015277305</v>
       </c>
       <c r="H5">
-        <v>17.64132587532872</v>
+        <v>9.925798354025567</v>
       </c>
       <c r="I5">
-        <v>0.002379725308917169</v>
+        <v>0.5759745622103425</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>20.81129154393988</v>
+        <v>17.58638523634016</v>
       </c>
       <c r="C6">
-        <v>937.8252481728314</v>
+        <v>781.8285681588959</v>
       </c>
       <c r="D6">
-        <v>27.49656691612221</v>
+        <v>24.02370698411692</v>
       </c>
       <c r="E6">
-        <v>0.001287141375970385</v>
+        <v>0.3321183132150149</v>
       </c>
       <c r="F6">
-        <v>-0.1096809540266996</v>
+        <v>0.2764615059829329</v>
       </c>
       <c r="G6">
-        <v>59.64493902013724</v>
+        <v>37.86711925484783</v>
       </c>
       <c r="H6">
-        <v>18.01248416309933</v>
+        <v>14.34653749248241</v>
       </c>
       <c r="I6">
-        <v>0.001287141375970691</v>
+        <v>0.3321183132150149</v>
       </c>
     </row>
   </sheetData>
@@ -3908,176 +3486,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>20.30291548360422</v>
+        <v>17.95975043968054</v>
       </c>
       <c r="C2">
-        <v>547.5601892220443</v>
+        <v>469.5435433410056</v>
       </c>
       <c r="D2">
-        <v>23.40000404320573</v>
+        <v>21.66895344360234</v>
       </c>
       <c r="E2">
-        <v>0.7430030954612796</v>
+        <v>0.7210234919650131</v>
       </c>
       <c r="F2">
-        <v>0.7144478838458663</v>
+        <v>0.6977754496287643</v>
       </c>
       <c r="G2">
-        <v>112.9618060876235</v>
+        <v>101.966596975462</v>
       </c>
       <c r="H2">
-        <v>18.19078762878262</v>
+        <v>16.16582970571343</v>
       </c>
       <c r="I2">
-        <v>0.7430030954612796</v>
+        <v>0.7210234919650131</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>6.740800970913425</v>
+        <v>8.696082729744493</v>
       </c>
       <c r="C3">
-        <v>73.44783200401024</v>
+        <v>156.0043864641514</v>
       </c>
       <c r="D3">
-        <v>8.570171060370395</v>
+        <v>12.490171594664</v>
       </c>
       <c r="E3">
-        <v>0.1267551318157019</v>
+        <v>0.02073733603036099</v>
       </c>
       <c r="F3">
-        <v>0.02972792423966863</v>
+        <v>-0.06086788596710879</v>
       </c>
       <c r="G3">
-        <v>10.50084666955623</v>
+        <v>16.85922095797502</v>
       </c>
       <c r="H3">
-        <v>4.638210684642331</v>
+        <v>6.160205409473868</v>
       </c>
       <c r="I3">
-        <v>0.1267551318157019</v>
+        <v>0.0207373360303611</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>22.32727272727273</v>
+        <v>33.11989984783138</v>
       </c>
       <c r="C4">
-        <v>1029.512727272727</v>
+        <v>2309.015001018081</v>
       </c>
       <c r="D4">
-        <v>32.08602074537644</v>
+        <v>48.0522111980092</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.0107378626920055</v>
       </c>
       <c r="F4">
-        <v>-0.1111111111111112</v>
+        <v>-0.07170064875032733</v>
       </c>
       <c r="G4">
-        <v>9.140243858576918</v>
+        <v>16.89590979466407</v>
       </c>
       <c r="H4">
-        <v>14.10000000000002</v>
+        <v>25.13419609221981</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.0107378626920055</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>9.892623508815397</v>
+        <v>10.56976959922311</v>
       </c>
       <c r="C5">
-        <v>110.3030965172467</v>
+        <v>192.7513417360246</v>
       </c>
       <c r="D5">
-        <v>10.50252810123575</v>
+        <v>13.88349169827333</v>
       </c>
       <c r="E5">
-        <v>0.7850248760228866</v>
+        <v>0.5759745622395085</v>
       </c>
       <c r="F5">
-        <v>0.7611387511365407</v>
+        <v>0.5406391090928009</v>
       </c>
       <c r="G5">
-        <v>14.42569213865134</v>
+        <v>15.74655173371086</v>
       </c>
       <c r="H5">
-        <v>9.712320302425553</v>
+        <v>9.92574105713495</v>
       </c>
       <c r="I5">
-        <v>0.7850248760228866</v>
+        <v>0.5759745622395085</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>14.81590317265144</v>
+        <v>17.58637565411988</v>
       </c>
       <c r="C6">
-        <v>440.2059612540071</v>
+        <v>781.8285681398157</v>
       </c>
       <c r="D6">
-        <v>18.63968098754708</v>
+        <v>24.02370698363722</v>
       </c>
       <c r="E6">
-        <v>0.413695775824967</v>
+        <v>0.332118313231722</v>
       </c>
       <c r="F6">
-        <v>0.3485508620277411</v>
+        <v>0.2764615060010323</v>
       </c>
       <c r="G6">
-        <v>36.757147188602</v>
+        <v>37.86706986545299</v>
       </c>
       <c r="H6">
-        <v>11.66032965396263</v>
+        <v>14.34649306613551</v>
       </c>
       <c r="I6">
-        <v>0.413695775824967</v>
+        <v>0.332118313231722</v>
       </c>
     </row>
   </sheetData>
@@ -4092,176 +3670,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>30.43195933703567</v>
+        <v>17.95977618491867</v>
       </c>
       <c r="C2">
-        <v>1393.321033472063</v>
+        <v>469.5435433824708</v>
       </c>
       <c r="D2">
-        <v>37.32721572086596</v>
+        <v>21.66895344455913</v>
       </c>
       <c r="E2">
-        <v>0.3460459695951265</v>
+        <v>0.7210234919403768</v>
       </c>
       <c r="F2">
-        <v>0.2733844106612516</v>
+        <v>0.6977754496020749</v>
       </c>
       <c r="G2">
-        <v>157.4406723046976</v>
+        <v>101.9666876441382</v>
       </c>
       <c r="H2">
-        <v>28.92409632082919</v>
+        <v>16.16593869902695</v>
       </c>
       <c r="I2">
-        <v>0.3460459695951265</v>
+        <v>0.7210234919403767</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>7.295685019884015</v>
+        <v>8.696084810296183</v>
       </c>
       <c r="C3">
-        <v>79.59607907796027</v>
+        <v>156.0043864643253</v>
       </c>
       <c r="D3">
-        <v>8.921663470337819</v>
+        <v>12.49017159467096</v>
       </c>
       <c r="E3">
-        <v>0.05365664736536646</v>
+        <v>0.02073733602926975</v>
       </c>
       <c r="F3">
-        <v>-0.05149261403848171</v>
+        <v>-0.06086788596829096</v>
       </c>
       <c r="G3">
-        <v>11.31293542056737</v>
+        <v>16.85922371583073</v>
       </c>
       <c r="H3">
-        <v>5.276454691972276</v>
+        <v>6.160204343158576</v>
       </c>
       <c r="I3">
-        <v>0.05365664736536657</v>
+        <v>0.02073733602926975</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>22.32727272727273</v>
+        <v>33.11988844469191</v>
       </c>
       <c r="C4">
-        <v>1029.512727272727</v>
+        <v>2309.015001019181</v>
       </c>
       <c r="D4">
-        <v>32.08602074537644</v>
+        <v>48.05221119802065</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.01073786269153432</v>
       </c>
       <c r="F4">
-        <v>-0.1111111111111112</v>
+        <v>-0.07170064875083781</v>
       </c>
       <c r="G4">
-        <v>9.140243858576918</v>
+        <v>16.89590615180786</v>
       </c>
       <c r="H4">
-        <v>14.10000000000002</v>
+        <v>25.13418330287394</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.01073786269153432</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>13.95438742210717</v>
+        <v>10.56978426526622</v>
       </c>
       <c r="C5">
-        <v>330.5418475770354</v>
+        <v>192.751341745536</v>
       </c>
       <c r="D5">
-        <v>18.18080987131859</v>
+        <v>13.88349169861588</v>
       </c>
       <c r="E5">
-        <v>0.355790753785531</v>
+        <v>0.5759745622185846</v>
       </c>
       <c r="F5">
-        <v>0.2842119486505901</v>
+        <v>0.5406391090701332</v>
       </c>
       <c r="G5">
-        <v>28.81650008990628</v>
+        <v>15.74662546408464</v>
       </c>
       <c r="H5">
-        <v>16.06385980220439</v>
+        <v>9.925788835533147</v>
       </c>
       <c r="I5">
-        <v>0.3557907537855312</v>
+        <v>0.5759745622185846</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>18.5023261265749</v>
+        <v>17.58638342629325</v>
       </c>
       <c r="C6">
-        <v>708.2429218499466</v>
+        <v>781.8285681528783</v>
       </c>
       <c r="D6">
-        <v>24.1289274519747</v>
+        <v>24.02370698396665</v>
       </c>
       <c r="E6">
-        <v>0.188873342686506</v>
+        <v>0.3321183132199413</v>
       </c>
       <c r="F6">
-        <v>0.09874815854056221</v>
+        <v>0.2764615059882699</v>
       </c>
       <c r="G6">
-        <v>51.67758791843703</v>
+        <v>37.86711074396536</v>
       </c>
       <c r="H6">
-        <v>16.09110270375147</v>
+        <v>14.34652879514815</v>
       </c>
       <c r="I6">
-        <v>0.188873342686506</v>
+        <v>0.3321183132199413</v>
       </c>
     </row>
   </sheetData>
@@ -4276,176 +3854,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>9.679664420775948</v>
+        <v>10.18400410812769</v>
       </c>
       <c r="C2">
-        <v>192.9259532024618</v>
+        <v>189.9897117553252</v>
       </c>
       <c r="D2">
-        <v>13.88977873122757</v>
+        <v>13.78367555317976</v>
       </c>
       <c r="E2">
-        <v>0.909450369559083</v>
+        <v>0.8871187409565098</v>
       </c>
       <c r="F2">
-        <v>0.8706433850844042</v>
+        <v>0.8532543632434627</v>
       </c>
       <c r="G2">
-        <v>57.28434970245569</v>
+        <v>61.13097625092665</v>
       </c>
       <c r="H2">
-        <v>5.380836973151546</v>
+        <v>7.830349026907371</v>
       </c>
       <c r="I2">
-        <v>0.909450369559083</v>
+        <v>0.8871187409565098</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>5.203277552552851</v>
+        <v>7.668926701638179</v>
       </c>
       <c r="C3">
-        <v>55.53384829555377</v>
+        <v>137.1628170144274</v>
       </c>
       <c r="D3">
-        <v>7.452103615460119</v>
+        <v>11.71165304363254</v>
       </c>
       <c r="E3">
-        <v>0.3397402385958803</v>
+        <v>0.139008661028941</v>
       </c>
       <c r="F3">
-        <v>0.05677176942268614</v>
+        <v>-0.1192887406623766</v>
       </c>
       <c r="G3">
-        <v>8.071023979749192</v>
+        <v>15.07332819570342</v>
       </c>
       <c r="H3">
-        <v>3.729422866570246</v>
+        <v>4.656081911799802</v>
       </c>
       <c r="I3">
-        <v>0.3397402385958803</v>
+        <v>0.1390086610289412</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>19.12760877208812</v>
+        <v>33.34258327838067</v>
       </c>
       <c r="C4">
-        <v>790.3465745211633</v>
+        <v>2086.174194799422</v>
       </c>
       <c r="D4">
-        <v>28.11310325313026</v>
+        <v>45.67465593520571</v>
       </c>
       <c r="E4">
-        <v>0.2323100496145754</v>
+        <v>0.1062105954988986</v>
       </c>
       <c r="F4">
-        <v>-0.09669992912203518</v>
+        <v>-0.1619262258514318</v>
       </c>
       <c r="G4">
-        <v>7.916017389382368</v>
+        <v>16.7996861714309</v>
       </c>
       <c r="H4">
-        <v>14.52657702577102</v>
+        <v>22.61631116938514</v>
       </c>
       <c r="I4">
-        <v>0.2323100496145754</v>
+        <v>0.1062105954988986</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>4.738503544002092</v>
+        <v>6.724952823598907</v>
       </c>
       <c r="C5">
-        <v>36.32458708689315</v>
+        <v>103.3948511812794</v>
       </c>
       <c r="D5">
-        <v>6.026988226875273</v>
+        <v>10.16832587898713</v>
       </c>
       <c r="E5">
-        <v>0.9292052276048177</v>
+        <v>0.7725460863750298</v>
       </c>
       <c r="F5">
-        <v>0.8988646108640254</v>
+        <v>0.7043099122875387</v>
       </c>
       <c r="G5">
-        <v>5.570944700574753</v>
+        <v>9.331852024183938</v>
       </c>
       <c r="H5">
-        <v>3.710741840657093</v>
+        <v>3.850313105553319</v>
       </c>
       <c r="I5">
-        <v>0.9292052276048177</v>
+        <v>0.7725460863750298</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>9.687263572354752</v>
+        <v>14.48011672793636</v>
       </c>
       <c r="C6">
-        <v>268.782740776518</v>
+        <v>629.1803936876136</v>
       </c>
       <c r="D6">
-        <v>13.87049345667331</v>
+        <v>20.33457760275129</v>
       </c>
       <c r="E6">
-        <v>0.602676471343589</v>
+        <v>0.4762210209648448</v>
       </c>
       <c r="F6">
-        <v>0.4323949590622701</v>
+        <v>0.3190873272542982</v>
       </c>
       <c r="G6">
-        <v>19.7105839430405</v>
+        <v>25.58396066056122</v>
       </c>
       <c r="H6">
-        <v>6.836894676537476</v>
+        <v>9.738263803411408</v>
       </c>
       <c r="I6">
-        <v>0.602676471343589</v>
+        <v>0.4762210209648448</v>
       </c>
     </row>
   </sheetData>
@@ -4460,176 +4038,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>10.97532918431244</v>
+        <v>27.70739324299376</v>
       </c>
       <c r="C2">
-        <v>205.8764612832678</v>
+        <v>1454.16764252894</v>
       </c>
       <c r="D2">
-        <v>14.34839577385806</v>
+        <v>38.1335500908182</v>
       </c>
       <c r="E2">
-        <v>0.9033720597139142</v>
+        <v>0.1360149303222999</v>
       </c>
       <c r="F2">
-        <v>0.8619600853055918</v>
+        <v>-0.1231805905810099</v>
       </c>
       <c r="G2">
-        <v>64.46696153173846</v>
+        <v>133.9881443826817</v>
       </c>
       <c r="H2">
-        <v>7.398118893620961</v>
+        <v>21.87642648980349</v>
       </c>
       <c r="I2">
-        <v>0.9033720597139142</v>
+        <v>0.1360149303223001</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>4.994018362771272</v>
+        <v>9.230217882112072</v>
       </c>
       <c r="C3">
-        <v>55.96507327401947</v>
+        <v>157.7967482820635</v>
       </c>
       <c r="D3">
-        <v>7.48098076952611</v>
+        <v>12.56171756894986</v>
       </c>
       <c r="E3">
-        <v>0.3346132663054321</v>
+        <v>0.009486415153149741</v>
       </c>
       <c r="F3">
-        <v>0.04944752329347435</v>
+        <v>-0.2876676603009054</v>
       </c>
       <c r="G3">
-        <v>7.784361275801394</v>
+        <v>17.56462955776416</v>
       </c>
       <c r="H3">
-        <v>2.996973266739474</v>
+        <v>6.969089569453757</v>
       </c>
       <c r="I3">
-        <v>0.3346132663054322</v>
+        <v>0.00948641515314963</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>19.42398341187271</v>
+        <v>32.09597830566354</v>
       </c>
       <c r="C4">
-        <v>797.5028909343688</v>
+        <v>2333.922165194635</v>
       </c>
       <c r="D4">
-        <v>28.24009367786107</v>
+        <v>48.31068375830169</v>
       </c>
       <c r="E4">
-        <v>0.2253588811407642</v>
+        <v>6.676940906247264E-05</v>
       </c>
       <c r="F4">
-        <v>-0.1066301697989083</v>
+        <v>-0.2999131997682187</v>
       </c>
       <c r="G4">
-        <v>8.03096150021592</v>
+        <v>16.63859364620697</v>
       </c>
       <c r="H4">
-        <v>14.96293719606138</v>
+        <v>22.53272535000156</v>
       </c>
       <c r="I4">
-        <v>0.2253588811407643</v>
+        <v>6.676940906247264E-05</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>5.364599564185789</v>
+        <v>15.29171221504644</v>
       </c>
       <c r="C5">
-        <v>39.18517578839717</v>
+        <v>405.4865126565633</v>
       </c>
       <c r="D5">
-        <v>6.259806369880555</v>
+        <v>20.13669567373364</v>
       </c>
       <c r="E5">
-        <v>0.9236300857441611</v>
+        <v>0.1079875528407799</v>
       </c>
       <c r="F5">
-        <v>0.8909001224916586</v>
+        <v>-0.1596161813069863</v>
       </c>
       <c r="G5">
-        <v>6.770742743450725</v>
+        <v>30.75121062888524</v>
       </c>
       <c r="H5">
-        <v>5.196405557302697</v>
+        <v>12.7769672298138</v>
       </c>
       <c r="I5">
-        <v>0.9236300857441611</v>
+        <v>0.10798755284078</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>10.18948263078555</v>
+        <v>21.08132541145396</v>
       </c>
       <c r="C6">
-        <v>274.6324003200133</v>
+        <v>1087.843267165551</v>
       </c>
       <c r="D6">
-        <v>14.08231914778145</v>
+        <v>29.78566177295085</v>
       </c>
       <c r="E6">
-        <v>0.596743573226068</v>
+        <v>0.06338891693132301</v>
       </c>
       <c r="F6">
-        <v>0.4239193903229541</v>
+        <v>-0.2175944079892801</v>
       </c>
       <c r="G6">
-        <v>21.76325676280162</v>
+        <v>49.73564455388451</v>
       </c>
       <c r="H6">
-        <v>7.638608728431127</v>
+        <v>16.03880215976815</v>
       </c>
       <c r="I6">
-        <v>0.596743573226068</v>
+        <v>0.06338891693132304</v>
       </c>
     </row>
   </sheetData>
@@ -4644,176 +4222,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>27.95454351267378</v>
+        <v>24.10753027245121</v>
       </c>
       <c r="C2">
-        <v>1610.280151835785</v>
+        <v>1136.101462228707</v>
       </c>
       <c r="D2">
-        <v>40.12829614917365</v>
+        <v>33.70610422799863</v>
       </c>
       <c r="E2">
-        <v>0.2442163937266814</v>
+        <v>0.3249920626087158</v>
       </c>
       <c r="F2">
-        <v>0.1602404374740903</v>
+        <v>0.2687414011594421</v>
       </c>
       <c r="G2">
-        <v>63.918622322872</v>
+        <v>91.66700786904762</v>
       </c>
       <c r="H2">
-        <v>14.63290969418151</v>
+        <v>15.17144749610551</v>
       </c>
       <c r="I2">
-        <v>0.4842733401901038</v>
+        <v>0.3894790409600025</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>10.02085702383019</v>
+        <v>8.859216086972451</v>
       </c>
       <c r="C3">
-        <v>129.7829336994978</v>
+        <v>158.0302394259915</v>
       </c>
       <c r="D3">
-        <v>11.3922312871315</v>
+        <v>12.57100789220942</v>
       </c>
       <c r="E3">
-        <v>-0.5430309886451312</v>
+        <v>0.008020756623934089</v>
       </c>
       <c r="F3">
-        <v>-0.7144788762723679</v>
+        <v>-0.07464418032407139</v>
       </c>
       <c r="G3">
-        <v>14.05213124338457</v>
+        <v>16.91965977373152</v>
       </c>
       <c r="H3">
-        <v>11.06076556000318</v>
+        <v>7.26766547681919</v>
       </c>
       <c r="I3">
-        <v>0.1266927301389354</v>
+        <v>0.01422470829512235</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
-        <v>206.7809556805961</v>
+        <v>182.298092612082</v>
       </c>
       <c r="C4">
-        <v>43787.87645329037</v>
+        <v>35566.65742346342</v>
       </c>
       <c r="D4">
-        <v>209.2555290865462</v>
+        <v>188.5912442916251</v>
       </c>
       <c r="E4">
-        <v>-41.53262275765005</v>
+        <v>-14.23799001917405</v>
       </c>
       <c r="F4">
-        <v>-46.25846973072228</v>
+        <v>-15.50782252077188</v>
       </c>
       <c r="G4">
-        <v>75.01223567975612</v>
+        <v>67.54990255135532</v>
       </c>
       <c r="H4">
-        <v>209.6810146886268</v>
+        <v>192.8329852518807</v>
       </c>
       <c r="I4">
-        <v>-9.114703036772198E-08</v>
+        <v>6.49367494331976E-06</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>17.2052965685299</v>
+        <v>12.23250900181676</v>
       </c>
       <c r="C5">
-        <v>420.1208981291327</v>
+        <v>248.880094989379</v>
       </c>
       <c r="D5">
-        <v>20.49685093201228</v>
+        <v>15.77593404491091</v>
       </c>
       <c r="E5">
-        <v>0.1812057411591793</v>
+        <v>0.4524993171135955</v>
       </c>
       <c r="F5">
-        <v>0.09022860128797694</v>
+        <v>0.4068742602063952</v>
       </c>
       <c r="G5">
-        <v>19.74295354983274</v>
+        <v>16.02764055785559</v>
       </c>
       <c r="H5">
-        <v>14.15877479478122</v>
+        <v>7.75906641742332</v>
       </c>
       <c r="I5">
-        <v>0.7069957253830426</v>
+        <v>0.5691504293723822</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>65.49041319640749</v>
+        <v>56.87433699333061</v>
       </c>
       <c r="C6">
-        <v>11487.0151092387</v>
+        <v>9277.417305026873</v>
       </c>
       <c r="D6">
-        <v>70.31822686371589</v>
+        <v>62.66107261418601</v>
       </c>
       <c r="E6">
-        <v>-10.41255790285233</v>
+        <v>-3.36311947070695</v>
       </c>
       <c r="F6">
-        <v>-11.68061989205815</v>
+        <v>-3.726712759932529</v>
       </c>
       <c r="G6">
-        <v>43.18148569896135</v>
+        <v>48.04105268799751</v>
       </c>
       <c r="H6">
-        <v>62.38336618439817</v>
+        <v>55.75779116055718</v>
       </c>
       <c r="I6">
-        <v>0.3294904261412629</v>
+        <v>0.2432151680756126</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/models/tables/all_model_metrics.xlsx
+++ b/outputs/models/tables/all_model_metrics.xlsx
@@ -13,27 +13,33 @@
     <sheet name="metrics__Ridge Regression" sheetId="4" r:id="rId4"/>
     <sheet name="metrics__Lasso Regression" sheetId="5" r:id="rId5"/>
     <sheet name="metrics__Elastic Net Regression" sheetId="6" r:id="rId6"/>
-    <sheet name="metrics__Polynomial Regression " sheetId="7" r:id="rId7"/>
-    <sheet name="metrics__Polynomial Ridge Degre" sheetId="8" r:id="rId8"/>
-    <sheet name="metrics__Stochastic Gradient Re" sheetId="9" r:id="rId9"/>
-    <sheet name="metrics__Decision Tree" sheetId="10" r:id="rId10"/>
-    <sheet name="metrics__Random Forest" sheetId="11" r:id="rId11"/>
-    <sheet name="metrics__Extra Trees" sheetId="12" r:id="rId12"/>
-    <sheet name="metrics__Gradient Boosting" sheetId="13" r:id="rId13"/>
-    <sheet name="metrics__Adaptive Boosting" sheetId="14" r:id="rId14"/>
-    <sheet name="metrics__Histogram Gradient Boo" sheetId="15" r:id="rId15"/>
-    <sheet name="metrics__Bagging Regressor" sheetId="16" r:id="rId16"/>
-    <sheet name="metrics__K Nearest Neighbors Fi" sheetId="17" r:id="rId17"/>
-    <sheet name="metrics__K Nearest Neighbors Th" sheetId="18" r:id="rId18"/>
-    <sheet name="metrics__Support Vector Regress" sheetId="19" r:id="rId19"/>
-    <sheet name="metrics__Gaussian Process Regre" sheetId="20" r:id="rId20"/>
+    <sheet name="metrics__Huber Regression" sheetId="7" r:id="rId7"/>
+    <sheet name="metrics__Theil Sen Regression" sheetId="8" r:id="rId8"/>
+    <sheet name="metrics__RANSAC Regression" sheetId="9" r:id="rId9"/>
+    <sheet name="metrics__Bayesian Ridge Regress" sheetId="10" r:id="rId10"/>
+    <sheet name="metrics__ARD Regression" sheetId="11" r:id="rId11"/>
+    <sheet name="metrics__Polynomial Regression " sheetId="12" r:id="rId12"/>
+    <sheet name="metrics__Polynomial Ridge Degre" sheetId="13" r:id="rId13"/>
+    <sheet name="metrics__Stochastic Gradient Re" sheetId="14" r:id="rId14"/>
+    <sheet name="metrics__Kernel Ridge Regressio" sheetId="15" r:id="rId15"/>
+    <sheet name="metrics__Decision Tree" sheetId="16" r:id="rId16"/>
+    <sheet name="metrics__Random Forest" sheetId="17" r:id="rId17"/>
+    <sheet name="metrics__Extra Trees" sheetId="18" r:id="rId18"/>
+    <sheet name="metrics__Gradient Boosting" sheetId="19" r:id="rId19"/>
+    <sheet name="metrics__Adaptive Boosting" sheetId="20" r:id="rId20"/>
+    <sheet name="metrics__Histogram Gradient Boo" sheetId="21" r:id="rId21"/>
+    <sheet name="metrics__Bagging Regressor" sheetId="22" r:id="rId22"/>
+    <sheet name="metrics__K Nearest Neighbors Fi" sheetId="23" r:id="rId23"/>
+    <sheet name="metrics__K Nearest Neighbors Th" sheetId="24" r:id="rId24"/>
+    <sheet name="metrics__Support Vector Regress" sheetId="25" r:id="rId25"/>
+    <sheet name="metrics__Gaussian Process Regre" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="48">
   <si>
     <t>model</t>
   </si>
@@ -101,6 +107,15 @@
     <t>Ridge Regression</t>
   </si>
   <si>
+    <t>Bayesian Ridge Regression</t>
+  </si>
+  <si>
+    <t>ARD Regression</t>
+  </si>
+  <si>
+    <t>Huber Regression</t>
+  </si>
+  <si>
     <t>K Nearest Neighbors Five</t>
   </si>
   <si>
@@ -111,6 +126,15 @@
   </si>
   <si>
     <t>Histogram Gradient Boosting</t>
+  </si>
+  <si>
+    <t>Kernel Ridge Regression</t>
+  </si>
+  <si>
+    <t>Theil Sen Regression</t>
+  </si>
+  <si>
+    <t>RANSAC Regression</t>
   </si>
   <si>
     <t>Stochastic Gradient Regression</t>
@@ -516,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -892,19 +916,19 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>20.55809523809524</v>
+        <v>17.56917343216907</v>
       </c>
       <c r="C17">
-        <v>29.28115086549835</v>
+        <v>24.13531616499252</v>
       </c>
       <c r="D17">
-        <v>0.09571559727788351</v>
+        <v>0.3236340906910181</v>
       </c>
       <c r="E17">
-        <v>0.02035856371770714</v>
+        <v>0.2672702649152696</v>
       </c>
       <c r="F17">
-        <v>38.56851652347636</v>
+        <v>38.33727603024025</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -915,19 +939,19 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>20.55809523809524</v>
+        <v>17.56917343216907</v>
       </c>
       <c r="C18">
-        <v>29.28115086549835</v>
+        <v>24.13531616499252</v>
       </c>
       <c r="D18">
-        <v>0.09571559727788351</v>
+        <v>0.3236340906910181</v>
       </c>
       <c r="E18">
-        <v>0.02035856371770714</v>
+        <v>0.2672702649152696</v>
       </c>
       <c r="F18">
-        <v>38.56851652347636</v>
+        <v>38.33727603024025</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -938,19 +962,19 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>21.08132541145396</v>
+        <v>16.2715137120993</v>
       </c>
       <c r="C19">
-        <v>29.78566177295085</v>
+        <v>24.81725687316666</v>
       </c>
       <c r="D19">
-        <v>0.06338891693132301</v>
+        <v>0.2815534835374435</v>
       </c>
       <c r="E19">
-        <v>-0.2175944079892801</v>
+        <v>0.2216829404988971</v>
       </c>
       <c r="F19">
-        <v>49.73564455388451</v>
+        <v>37.85555828845195</v>
       </c>
       <c r="G19">
         <v>18</v>
@@ -961,19 +985,19 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>21.80005102040816</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C20">
-        <v>30.8200775199298</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="E20">
-        <v>-0.08333333333333326</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="F20">
-        <v>51.86540618403083</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -984,22 +1008,160 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>56.87433699333061</v>
+        <v>20.55809523809524</v>
       </c>
       <c r="C21">
-        <v>62.66107261418601</v>
+        <v>29.28115086549835</v>
       </c>
       <c r="D21">
-        <v>-3.36311947070695</v>
+        <v>0.09571559727788351</v>
       </c>
       <c r="E21">
-        <v>-3.726712759932529</v>
+        <v>0.02035856371770714</v>
       </c>
       <c r="F21">
-        <v>48.04105268799751</v>
+        <v>38.56851652347636</v>
       </c>
       <c r="G21">
         <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>21.08132541145396</v>
+      </c>
+      <c r="C22">
+        <v>29.78566177295085</v>
+      </c>
+      <c r="D22">
+        <v>0.06338891693132301</v>
+      </c>
+      <c r="E22">
+        <v>-0.2175944079892801</v>
+      </c>
+      <c r="F22">
+        <v>49.73564455388451</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>21.80005102040816</v>
+      </c>
+      <c r="C23">
+        <v>30.8200775199298</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="F23">
+        <v>51.86540618403083</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
+        <v>26.70499493863093</v>
+      </c>
+      <c r="C24">
+        <v>31.86005853528316</v>
+      </c>
+      <c r="D24">
+        <v>-0.1756461895250861</v>
+      </c>
+      <c r="E24">
+        <v>-0.2736167053188433</v>
+      </c>
+      <c r="F24">
+        <v>35.60357253216966</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
+        <v>20.29500914141204</v>
+      </c>
+      <c r="C25">
+        <v>33.81975526068013</v>
+      </c>
+      <c r="D25">
+        <v>-0.1806837958833397</v>
+      </c>
+      <c r="E25">
+        <v>-0.2790741122069513</v>
+      </c>
+      <c r="F25">
+        <v>38.36346684702566</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>20.1202592296975</v>
+      </c>
+      <c r="C26">
+        <v>34.99768010898507</v>
+      </c>
+      <c r="D26">
+        <v>-1.027851374414385</v>
+      </c>
+      <c r="E26">
+        <v>-1.196838988948917</v>
+      </c>
+      <c r="F26">
+        <v>56.06014171810725</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>56.87433699333061</v>
+      </c>
+      <c r="C27">
+        <v>62.66107261418601</v>
+      </c>
+      <c r="D27">
+        <v>-3.36311947070695</v>
+      </c>
+      <c r="E27">
+        <v>-3.726712759932529</v>
+      </c>
+      <c r="F27">
+        <v>48.04105268799751</v>
+      </c>
+      <c r="G27">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1014,176 +1176,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>11.18523809523809</v>
+        <v>18.09743140653623</v>
       </c>
       <c r="C2">
-        <v>201.3859261904761</v>
+        <v>470.6185449835385</v>
       </c>
       <c r="D2">
-        <v>14.19105091917002</v>
+        <v>21.6937443744398</v>
       </c>
       <c r="E2">
-        <v>0.8803477478228072</v>
+        <v>0.7203847861226714</v>
       </c>
       <c r="F2">
-        <v>0.8703767268080411</v>
+        <v>0.6970835182995607</v>
       </c>
       <c r="G2">
-        <v>58.07192754245103</v>
+        <v>102.4514769731611</v>
       </c>
       <c r="H2">
-        <v>9.435833333333328</v>
+        <v>15.75634632822069</v>
       </c>
       <c r="I2">
-        <v>0.8803477478228072</v>
+        <v>0.7203847861226714</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>4.207142857142858</v>
+        <v>9.353700830464478</v>
       </c>
       <c r="C3">
-        <v>23.39107142857144</v>
+        <v>159.3046109319126</v>
       </c>
       <c r="D3">
-        <v>4.83643168343888</v>
+        <v>12.62159304255658</v>
       </c>
       <c r="E3">
-        <v>0.8531707765440903</v>
+        <v>2.133773540125006E-05</v>
       </c>
       <c r="F3">
-        <v>0.8409350079227645</v>
+        <v>-0.08331021745331535</v>
       </c>
       <c r="G3">
-        <v>7.268140300799806</v>
+        <v>17.74260092367239</v>
       </c>
       <c r="H3">
-        <v>3.524999999999999</v>
+        <v>7.064082669368744</v>
       </c>
       <c r="I3">
-        <v>0.8531707765440903</v>
+        <v>2.13377354014721E-05</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>15.00714285714286</v>
+        <v>32.1031453166423</v>
       </c>
       <c r="C4">
-        <v>336.815773809524</v>
+        <v>2334.071474360047</v>
       </c>
       <c r="D4">
-        <v>18.35254134471638</v>
+        <v>48.31222903530789</v>
       </c>
       <c r="E4">
-        <v>0.8556964367356024</v>
+        <v>2.800182344775415E-06</v>
       </c>
       <c r="F4">
-        <v>0.8436711397969026</v>
+        <v>-0.08333029980245987</v>
       </c>
       <c r="G4">
-        <v>6.80814351818554</v>
+        <v>16.64107669905803</v>
       </c>
       <c r="H4">
-        <v>15.44583333333333</v>
+        <v>22.53605311998928</v>
       </c>
       <c r="I4">
-        <v>0.8556964367356024</v>
+        <v>2.800182344664393E-06</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>7.223809523809522</v>
+        <v>10.72241617503328</v>
       </c>
       <c r="C5">
-        <v>105.027619047619</v>
+        <v>193.5909978140026</v>
       </c>
       <c r="D5">
-        <v>10.24829834887817</v>
+        <v>13.9136982076658</v>
       </c>
       <c r="E5">
-        <v>0.7689542301365704</v>
+        <v>0.574127438723655</v>
       </c>
       <c r="F5">
-        <v>0.7497004159812846</v>
+        <v>0.538638058617293</v>
       </c>
       <c r="G5">
-        <v>11.21539909324933</v>
+        <v>16.5139495250695</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>0.7689542301365704</v>
+        <v>0.574127438723655</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>9.405833333333334</v>
+        <v>17.56917343216907</v>
       </c>
       <c r="C6">
-        <v>166.6550976190477</v>
+        <v>789.3964070223751</v>
       </c>
       <c r="D6">
-        <v>11.90708057405086</v>
+        <v>24.13531616499252</v>
       </c>
       <c r="E6">
-        <v>0.8395422978097675</v>
+        <v>0.3236340906910181</v>
       </c>
       <c r="F6">
-        <v>0.8261708226272482</v>
+        <v>0.2672702649152696</v>
       </c>
       <c r="G6">
-        <v>20.84090261367143</v>
+        <v>38.33727603024025</v>
       </c>
       <c r="H6">
-        <v>8.351666666666663</v>
+        <v>13.83912052939468</v>
       </c>
       <c r="I6">
-        <v>0.8395422978097675</v>
+        <v>0.3236340906910181</v>
       </c>
     </row>
   </sheetData>
@@ -1198,176 +1360,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>11.20179695011338</v>
+        <v>18.09743140653623</v>
       </c>
       <c r="C2">
-        <v>224.7096343972572</v>
+        <v>470.6185449835385</v>
       </c>
       <c r="D2">
-        <v>14.99031802188523</v>
+        <v>21.6937443744398</v>
       </c>
       <c r="E2">
-        <v>0.8664901050924733</v>
+        <v>0.7203847861226714</v>
       </c>
       <c r="F2">
-        <v>0.855364280516846</v>
+        <v>0.6970835182995607</v>
       </c>
       <c r="G2">
-        <v>58.90464254253096</v>
+        <v>102.451476973161</v>
       </c>
       <c r="H2">
-        <v>8.386608544973544</v>
+        <v>15.75634632822069</v>
       </c>
       <c r="I2">
-        <v>0.8678324828815218</v>
+        <v>0.7203847861226714</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>4.73816678004534</v>
+        <v>9.353700830464478</v>
       </c>
       <c r="C3">
-        <v>42.66476898952453</v>
+        <v>159.3046109319126</v>
       </c>
       <c r="D3">
-        <v>6.531827385159878</v>
+        <v>12.62159304255658</v>
       </c>
       <c r="E3">
-        <v>0.7321869193214529</v>
+        <v>2.133773540125006E-05</v>
       </c>
       <c r="F3">
-        <v>0.7098691625982405</v>
+        <v>-0.08331021745331535</v>
       </c>
       <c r="G3">
-        <v>8.831622888899272</v>
+        <v>17.74260092367239</v>
       </c>
       <c r="H3">
-        <v>3.799534920634933</v>
+        <v>7.064082669368744</v>
       </c>
       <c r="I3">
-        <v>0.7323021588655974</v>
+        <v>2.13377354014721E-05</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>19.56376118154327</v>
+        <v>32.1031453166423</v>
       </c>
       <c r="C4">
-        <v>621.5268394215173</v>
+        <v>2334.071474360047</v>
       </c>
       <c r="D4">
-        <v>24.93044001660455</v>
+        <v>48.31222903530789</v>
       </c>
       <c r="E4">
-        <v>0.7337163382267701</v>
+        <v>2.800182344775415E-06</v>
       </c>
       <c r="F4">
-        <v>0.711526033079001</v>
+        <v>-0.08333029980245987</v>
       </c>
       <c r="G4">
-        <v>9.410596220698149</v>
+        <v>16.64107669905803</v>
       </c>
       <c r="H4">
-        <v>17.369032539682</v>
+        <v>22.53605311998928</v>
       </c>
       <c r="I4">
-        <v>0.7337254489870485</v>
+        <v>2.800182344664393E-06</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>7.093999470899462</v>
+        <v>10.72241617503328</v>
       </c>
       <c r="C5">
-        <v>107.2273667275214</v>
+        <v>193.5909978140027</v>
       </c>
       <c r="D5">
-        <v>10.35506478625418</v>
+        <v>13.91369820766581</v>
       </c>
       <c r="E5">
-        <v>0.7641150992411256</v>
+        <v>0.5741274387236548</v>
       </c>
       <c r="F5">
-        <v>0.7444580241778862</v>
+        <v>0.5386380586172927</v>
       </c>
       <c r="G5">
-        <v>11.83427841832139</v>
+        <v>16.51394952506951</v>
       </c>
       <c r="H5">
-        <v>4.789012433862396</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>0.76548862857474</v>
+        <v>0.574127438723655</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>10.64943109565036</v>
+        <v>17.56917343216907</v>
       </c>
       <c r="C6">
-        <v>249.0321523839551</v>
+        <v>789.3964070223751</v>
       </c>
       <c r="D6">
-        <v>14.20191255247596</v>
+        <v>24.13531616499252</v>
       </c>
       <c r="E6">
-        <v>0.7741271154704554</v>
+        <v>0.3236340906910181</v>
       </c>
       <c r="F6">
-        <v>0.7553043750929934</v>
+        <v>0.2672702649152696</v>
       </c>
       <c r="G6">
-        <v>22.24528501761244</v>
+        <v>38.33727603024025</v>
       </c>
       <c r="H6">
-        <v>8.586047109788218</v>
+        <v>13.83912052939468</v>
       </c>
       <c r="I6">
-        <v>0.7748371798272269</v>
+        <v>0.3236340906910181</v>
       </c>
     </row>
   </sheetData>
@@ -1382,176 +1544,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>9.744504761904759</v>
+        <v>10.18400410812769</v>
       </c>
       <c r="C2">
-        <v>174.6017692153439</v>
+        <v>189.9897117553252</v>
       </c>
       <c r="D2">
-        <v>13.21369627376624</v>
+        <v>13.78367555317976</v>
       </c>
       <c r="E2">
-        <v>0.8962613956400378</v>
+        <v>0.8871187409565098</v>
       </c>
       <c r="F2">
-        <v>0.8876165119433743</v>
+        <v>0.8532543632434627</v>
       </c>
       <c r="G2">
-        <v>56.14016639137427</v>
+        <v>61.13097625092665</v>
       </c>
       <c r="H2">
-        <v>8.945161111110981</v>
+        <v>7.830349026907371</v>
       </c>
       <c r="I2">
-        <v>0.8962613956400378</v>
+        <v>0.8871187409565098</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>2.996882539682586</v>
+        <v>7.668926701638179</v>
       </c>
       <c r="C3">
-        <v>12.10389356684306</v>
+        <v>137.1628170144274</v>
       </c>
       <c r="D3">
-        <v>3.479065042054123</v>
+        <v>11.71165304363254</v>
       </c>
       <c r="E3">
-        <v>0.9240220654859893</v>
+        <v>0.139008661028941</v>
       </c>
       <c r="F3">
-        <v>0.9176905709431551</v>
+        <v>-0.1192887406623766</v>
       </c>
       <c r="G3">
-        <v>4.85607386447903</v>
+        <v>15.07332819570342</v>
       </c>
       <c r="H3">
-        <v>3.131877777777873</v>
+        <v>4.656081911799802</v>
       </c>
       <c r="I3">
-        <v>0.9240220654859893</v>
+        <v>0.1390086610289412</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>10.21884021164004</v>
+        <v>33.34258327838067</v>
       </c>
       <c r="C4">
-        <v>141.4562546553184</v>
+        <v>2086.174194799422</v>
       </c>
       <c r="D4">
-        <v>11.89353835724754</v>
+        <v>45.67465593520571</v>
       </c>
       <c r="E4">
-        <v>0.9393952327056326</v>
+        <v>0.1062105954988986</v>
       </c>
       <c r="F4">
-        <v>0.934344835431102</v>
+        <v>-0.1619262258514318</v>
       </c>
       <c r="G4">
-        <v>4.368872825302105</v>
+        <v>16.7996861714309</v>
       </c>
       <c r="H4">
-        <v>10.70506666666506</v>
+        <v>22.61631116938514</v>
       </c>
       <c r="I4">
-        <v>0.9393952327056326</v>
+        <v>0.1062105954988986</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>6.1551809523809</v>
+        <v>6.724952823598907</v>
       </c>
       <c r="C5">
-        <v>96.16453862328039</v>
+        <v>103.3948511812794</v>
       </c>
       <c r="D5">
-        <v>9.806351952855882</v>
+        <v>10.16832587898713</v>
       </c>
       <c r="E5">
-        <v>0.7884517419203456</v>
+        <v>0.7725460863750298</v>
       </c>
       <c r="F5">
-        <v>0.7708227204137078</v>
+        <v>0.7043099122875387</v>
       </c>
       <c r="G5">
-        <v>9.099110063463067</v>
+        <v>9.331852024183938</v>
       </c>
       <c r="H5">
-        <v>4.25</v>
+        <v>3.850313105553319</v>
       </c>
       <c r="I5">
-        <v>0.7884517419203456</v>
+        <v>0.7725460863750298</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>7.27885211640207</v>
+        <v>14.48011672793636</v>
       </c>
       <c r="C6">
-        <v>106.0816140151965</v>
+        <v>629.1803936876136</v>
       </c>
       <c r="D6">
-        <v>9.598162906480946</v>
+        <v>20.33457760275129</v>
       </c>
       <c r="E6">
-        <v>0.8870326089380014</v>
+        <v>0.4762210209648448</v>
       </c>
       <c r="F6">
-        <v>0.8776186596828348</v>
+        <v>0.3190873272542982</v>
       </c>
       <c r="G6">
-        <v>18.61605578615462</v>
+        <v>25.58396066056122</v>
       </c>
       <c r="H6">
-        <v>6.758026388888479</v>
+        <v>9.738263803411408</v>
       </c>
       <c r="I6">
-        <v>0.8870326089380014</v>
+        <v>0.4762210209648448</v>
       </c>
     </row>
   </sheetData>
@@ -1566,176 +1728,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>5.547003887826607</v>
+        <v>27.70739324299376</v>
       </c>
       <c r="C2">
-        <v>141.3121283968491</v>
+        <v>1454.16764252894</v>
       </c>
       <c r="D2">
-        <v>11.88747779795399</v>
+        <v>38.1335500908182</v>
       </c>
       <c r="E2">
-        <v>0.9160402380519714</v>
+        <v>0.1360149303222999</v>
       </c>
       <c r="F2">
-        <v>0.9090435912229691</v>
+        <v>-0.1231805905810099</v>
       </c>
       <c r="G2">
-        <v>32.57685910751209</v>
+        <v>133.9881443826817</v>
       </c>
       <c r="H2">
-        <v>0.01996302596227473</v>
+        <v>21.87642648980349</v>
       </c>
       <c r="I2">
-        <v>0.9188843216893332</v>
+        <v>0.1360149303223001</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>1.103320129706783</v>
+        <v>9.230217882112072</v>
       </c>
       <c r="C3">
-        <v>4.993944690047625</v>
+        <v>157.7967482820635</v>
       </c>
       <c r="D3">
-        <v>2.234713558836484</v>
+        <v>12.56171756894986</v>
       </c>
       <c r="E3">
-        <v>0.9686522687487583</v>
+        <v>0.009486415153149741</v>
       </c>
       <c r="F3">
-        <v>0.9660399578111548</v>
+        <v>-0.2876676603009054</v>
       </c>
       <c r="G3">
-        <v>1.556304175908757</v>
+        <v>17.56462955776416</v>
       </c>
       <c r="H3">
-        <v>0.004925863845340217</v>
+        <v>6.969089569453757</v>
       </c>
       <c r="I3">
-        <v>0.9687861808663898</v>
+        <v>0.00948641515314963</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>2.964023435646182</v>
+        <v>32.09597830566354</v>
       </c>
       <c r="C4">
-        <v>42.20397466564071</v>
+        <v>2333.922165194635</v>
       </c>
       <c r="D4">
-        <v>6.496458624946419</v>
+        <v>48.31068375830169</v>
       </c>
       <c r="E4">
-        <v>0.9819183529937157</v>
+        <v>6.676940906247264E-05</v>
       </c>
       <c r="F4">
-        <v>0.9804115490765253</v>
+        <v>-0.2999131997682187</v>
       </c>
       <c r="G4">
-        <v>1.066088054274457</v>
+        <v>16.63859364620697</v>
       </c>
       <c r="H4">
-        <v>0.007191736280468319</v>
+        <v>22.53272535000156</v>
       </c>
       <c r="I4">
-        <v>0.9821539730635134</v>
+        <v>6.676940906247264E-05</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>3.795172832343855</v>
+        <v>15.29171221504644</v>
       </c>
       <c r="C5">
-        <v>87.28676004046827</v>
+        <v>405.4865126565633</v>
       </c>
       <c r="D5">
-        <v>9.342738358771921</v>
+        <v>20.13669567373364</v>
       </c>
       <c r="E5">
-        <v>0.8079815875546916</v>
+        <v>0.1079875528407799</v>
       </c>
       <c r="F5">
-        <v>0.7919800531842492</v>
+        <v>-0.1596161813069863</v>
       </c>
       <c r="G5">
-        <v>6.130674094144062</v>
+        <v>30.75121062888524</v>
       </c>
       <c r="H5">
-        <v>0.007198414576095047</v>
+        <v>12.7769672298138</v>
       </c>
       <c r="I5">
-        <v>0.8105557421850719</v>
+        <v>0.10798755284078</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>3.352380071380857</v>
+        <v>21.08132541145396</v>
       </c>
       <c r="C6">
-        <v>68.94920194825141</v>
+        <v>1087.843267165551</v>
       </c>
       <c r="D6">
-        <v>7.490347085127204</v>
+        <v>29.78566177295085</v>
       </c>
       <c r="E6">
-        <v>0.9186481118372842</v>
+        <v>0.06338891693132301</v>
       </c>
       <c r="F6">
-        <v>0.9118687878237246</v>
+        <v>-0.2175944079892801</v>
       </c>
       <c r="G6">
-        <v>10.33248135795984</v>
+        <v>49.73564455388451</v>
       </c>
       <c r="H6">
-        <v>0.009819760166044578</v>
+        <v>16.03880215976815</v>
       </c>
       <c r="I6">
-        <v>0.9200950544510771</v>
+        <v>0.06338891693132304</v>
       </c>
     </row>
   </sheetData>
@@ -1750,176 +1912,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>6.385833333333335</v>
+        <v>24.10753027245121</v>
       </c>
       <c r="C2">
-        <v>139.9965470238095</v>
+        <v>1136.101462228707</v>
       </c>
       <c r="D2">
-        <v>11.83201365042356</v>
+        <v>33.70610422799863</v>
       </c>
       <c r="E2">
-        <v>0.9168218829125843</v>
+        <v>0.3249920626087158</v>
       </c>
       <c r="F2">
-        <v>0.9098903731552996</v>
+        <v>0.2687414011594421</v>
       </c>
       <c r="G2">
-        <v>30.71379985486174</v>
+        <v>91.66700786904762</v>
       </c>
       <c r="H2">
-        <v>0.8333333333333357</v>
+        <v>15.17144749610551</v>
       </c>
       <c r="I2">
-        <v>0.9173606543729681</v>
+        <v>0.3894790409600025</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>1.738095238095237</v>
+        <v>8.859216086972451</v>
       </c>
       <c r="C3">
-        <v>7.060634920634918</v>
+        <v>158.0302394259915</v>
       </c>
       <c r="D3">
-        <v>2.657185526197769</v>
+        <v>12.57100789220942</v>
       </c>
       <c r="E3">
-        <v>0.9556793477516298</v>
+        <v>0.008020756623934089</v>
       </c>
       <c r="F3">
-        <v>0.9519859600642656</v>
+        <v>-0.07464418032407139</v>
       </c>
       <c r="G3">
-        <v>2.401144235243257</v>
+        <v>16.91965977373152</v>
       </c>
       <c r="H3">
-        <v>0.7499999999999929</v>
+        <v>7.26766547681919</v>
       </c>
       <c r="I3">
-        <v>0.9558958453142707</v>
+        <v>0.01422470829512235</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>6.759285714285718</v>
+        <v>182.298092612082</v>
       </c>
       <c r="C4">
-        <v>87.81028650793662</v>
+        <v>35566.65742346342</v>
       </c>
       <c r="D4">
-        <v>9.370714300838364</v>
+        <v>188.5912442916251</v>
       </c>
       <c r="E4">
-        <v>0.9623790266974587</v>
+        <v>-14.23799001917405</v>
       </c>
       <c r="F4">
-        <v>0.9592439455889136</v>
+        <v>-15.50782252077188</v>
       </c>
       <c r="G4">
-        <v>2.454784806808297</v>
+        <v>67.54990255135532</v>
       </c>
       <c r="H4">
-        <v>5.683333333333337</v>
+        <v>192.8329852518807</v>
       </c>
       <c r="I4">
-        <v>0.9625806183610094</v>
+        <v>6.49367494331976E-06</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>5.094999999999998</v>
+        <v>12.23250900181676</v>
       </c>
       <c r="C5">
-        <v>91.03139563492061</v>
+        <v>248.880094989379</v>
       </c>
       <c r="D5">
-        <v>9.541037450661255</v>
+        <v>15.77593404491091</v>
       </c>
       <c r="E5">
-        <v>0.7997439237704067</v>
+        <v>0.4524993171135955</v>
       </c>
       <c r="F5">
-        <v>0.7830559174179406</v>
+        <v>0.4068742602063952</v>
       </c>
       <c r="G5">
-        <v>7.357244732313917</v>
+        <v>16.02764055785559</v>
       </c>
       <c r="H5">
-        <v>0.62083333333333</v>
+        <v>7.75906641742332</v>
       </c>
       <c r="I5">
-        <v>0.799940969249874</v>
+        <v>0.5691504293723822</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>4.994553571428572</v>
+        <v>56.87433699333061</v>
       </c>
       <c r="C6">
-        <v>81.47471602182542</v>
+        <v>9277.417305026873</v>
       </c>
       <c r="D6">
-        <v>8.350237732030237</v>
+        <v>62.66107261418601</v>
       </c>
       <c r="E6">
-        <v>0.9086560452830199</v>
+        <v>-3.36311947070695</v>
       </c>
       <c r="F6">
-        <v>0.901044049056605</v>
+        <v>-3.726712759932529</v>
       </c>
       <c r="G6">
-        <v>10.7317434073068</v>
+        <v>48.04105268799751</v>
       </c>
       <c r="H6">
-        <v>1.971874999999999</v>
+        <v>55.75779116055718</v>
       </c>
       <c r="I6">
-        <v>0.9089445218245306</v>
+        <v>0.2432151680756126</v>
       </c>
     </row>
   </sheetData>
@@ -1934,176 +2096,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>29.58285714285715</v>
+        <v>19.90424533527296</v>
       </c>
       <c r="C2">
-        <v>1683.093485714286</v>
+        <v>739.1535231056032</v>
       </c>
       <c r="D2">
-        <v>41.02552236979178</v>
+        <v>27.18737801086385</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.5608363234844826</v>
       </c>
       <c r="F2">
-        <v>-0.08333333333333326</v>
+        <v>0.5242393504415228</v>
       </c>
       <c r="G2">
-        <v>140.2043443286067</v>
+        <v>73.12252338226155</v>
       </c>
       <c r="H2">
-        <v>21.79</v>
+        <v>12.38887325851016</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.627954300240959</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>9.354081632653058</v>
+        <v>14.93563361960503</v>
       </c>
       <c r="C3">
-        <v>159.3080102040817</v>
+        <v>280.9378681491963</v>
       </c>
       <c r="D3">
-        <v>12.62172770281793</v>
+        <v>16.76120127404943</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-0.7634886518844886</v>
       </c>
       <c r="F3">
-        <v>-0.08333333333333326</v>
+        <v>-0.9104460395415293</v>
       </c>
       <c r="G3">
-        <v>17.74311782890865</v>
+        <v>25.28355525915003</v>
       </c>
       <c r="H3">
-        <v>7.064285714285703</v>
+        <v>12.74075791853362</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-0.2376284328775833</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>32.10306122448979</v>
+        <v>60.16787149107972</v>
       </c>
       <c r="C4">
-        <v>2334.078010204082</v>
+        <v>4843.972436877133</v>
       </c>
       <c r="D4">
-        <v>48.31229667697534</v>
+        <v>69.59865255072927</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>-1.075325852735143</v>
       </c>
       <c r="F4">
-        <v>-0.08333333333333326</v>
+        <v>-1.248269673796405</v>
       </c>
       <c r="G4">
-        <v>16.6410616884347</v>
+        <v>25.61801496017499</v>
       </c>
       <c r="H4">
-        <v>22.53571428571428</v>
+        <v>50.75652110070396</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>-0.4684887862410099</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>16.16020408163265</v>
+        <v>11.81222930856601</v>
       </c>
       <c r="C5">
-        <v>454.5749489795918</v>
+        <v>193.0155130603527</v>
       </c>
       <c r="D5">
-        <v>21.32076333013412</v>
+        <v>13.89300230549008</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.5753934230348049</v>
       </c>
       <c r="F5">
-        <v>-0.08333333333333326</v>
+        <v>0.5400095416210386</v>
       </c>
       <c r="G5">
-        <v>32.8731008901733</v>
+        <v>18.39019652709208</v>
       </c>
       <c r="H5">
-        <v>13.29285714285713</v>
+        <v>13.0256948339919</v>
       </c>
       <c r="I5">
-        <v>-2.220446049250313E-16</v>
+        <v>0.7306836652249162</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>21.80005102040816</v>
+        <v>26.70499493863093</v>
       </c>
       <c r="C6">
-        <v>1157.76361377551</v>
+        <v>1514.269835298071</v>
       </c>
       <c r="D6">
-        <v>30.8200775199298</v>
+        <v>31.86005853528316</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>-0.1756461895250861</v>
       </c>
       <c r="F6">
-        <v>-0.08333333333333326</v>
+        <v>-0.2736167053188433</v>
       </c>
       <c r="G6">
-        <v>51.86540618403083</v>
+        <v>35.60357253216966</v>
       </c>
       <c r="H6">
-        <v>16.17071428571428</v>
+        <v>22.22796177793491</v>
       </c>
       <c r="I6">
-        <v>-5.551115123125783E-17</v>
+        <v>0.1631301865868205</v>
       </c>
     </row>
   </sheetData>
@@ -2118,176 +2280,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>11.30476428571428</v>
+        <v>11.18523809523809</v>
       </c>
       <c r="C2">
-        <v>225.6083918291567</v>
+        <v>201.3859261904761</v>
       </c>
       <c r="D2">
-        <v>15.02026603722972</v>
+        <v>14.19105091917002</v>
       </c>
       <c r="E2">
-        <v>0.865956113701307</v>
+        <v>0.8803477478228072</v>
       </c>
       <c r="F2">
-        <v>0.8547857898430826</v>
+        <v>0.8703767268080411</v>
       </c>
       <c r="G2">
-        <v>55.43836192495155</v>
+        <v>58.07192754245103</v>
       </c>
       <c r="H2">
-        <v>8.551895833333329</v>
+        <v>9.435833333333328</v>
       </c>
       <c r="I2">
-        <v>0.870053822148988</v>
+        <v>0.8803477478228072</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>4.348476190476187</v>
+        <v>4.207142857142858</v>
       </c>
       <c r="C3">
-        <v>30.45792862003967</v>
+        <v>23.39107142857144</v>
       </c>
       <c r="D3">
-        <v>5.518870230404016</v>
+        <v>4.83643168343888</v>
       </c>
       <c r="E3">
-        <v>0.8088110661791487</v>
+        <v>0.8531707765440903</v>
       </c>
       <c r="F3">
-        <v>0.7928786550274111</v>
+        <v>0.8409350079227645</v>
       </c>
       <c r="G3">
-        <v>7.648256241692383</v>
+        <v>7.268140300799806</v>
       </c>
       <c r="H3">
-        <v>3.654999999999987</v>
+        <v>3.524999999999999</v>
       </c>
       <c r="I3">
-        <v>0.8097421870952792</v>
+        <v>0.8531707765440903</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>17.01513988095239</v>
+        <v>15.00714285714286</v>
       </c>
       <c r="C4">
-        <v>425.9112810809776</v>
+        <v>336.815773809524</v>
       </c>
       <c r="D4">
-        <v>20.63761810580324</v>
+        <v>18.35254134471638</v>
       </c>
       <c r="E4">
-        <v>0.8175248302674606</v>
+        <v>0.8556964367356024</v>
       </c>
       <c r="F4">
-        <v>0.8023185661230823</v>
+        <v>0.8436711397969026</v>
       </c>
       <c r="G4">
-        <v>7.808682415642464</v>
+        <v>6.80814351818554</v>
       </c>
       <c r="H4">
-        <v>15.90499999999994</v>
+        <v>15.44583333333333</v>
       </c>
       <c r="I4">
-        <v>0.8177246363479393</v>
+        <v>0.8556964367356024</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>7.113553571428571</v>
+        <v>7.223809523809522</v>
       </c>
       <c r="C5">
-        <v>108.1679850183531</v>
+        <v>105.027619047619</v>
       </c>
       <c r="D5">
-        <v>10.40038388802803</v>
+        <v>10.24829834887817</v>
       </c>
       <c r="E5">
-        <v>0.7620458732687239</v>
+        <v>0.7689542301365704</v>
       </c>
       <c r="F5">
-        <v>0.7422163627077842</v>
+        <v>0.7497004159812846</v>
       </c>
       <c r="G5">
-        <v>12.66473414599422</v>
+        <v>11.21539909324933</v>
       </c>
       <c r="H5">
-        <v>5.110416666666669</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>0.7673903392117379</v>
+        <v>0.7689542301365704</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>9.945483482142858</v>
+        <v>9.405833333333334</v>
       </c>
       <c r="C6">
-        <v>197.5363966371318</v>
+        <v>166.6550976190477</v>
       </c>
       <c r="D6">
-        <v>12.89428456536625</v>
+        <v>11.90708057405086</v>
       </c>
       <c r="E6">
-        <v>0.81358447085416</v>
+        <v>0.8395422978097675</v>
       </c>
       <c r="F6">
-        <v>0.79804984342534</v>
+        <v>0.8261708226272482</v>
       </c>
       <c r="G6">
-        <v>20.89000868207015</v>
+        <v>20.84090261367143</v>
       </c>
       <c r="H6">
-        <v>8.305578124999982</v>
+        <v>8.351666666666663</v>
       </c>
       <c r="I6">
-        <v>0.8162277462009861</v>
+        <v>0.8395422978097675</v>
       </c>
     </row>
   </sheetData>
@@ -2302,176 +2464,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>23.82523809523809</v>
+        <v>11.20179695011338</v>
       </c>
       <c r="C2">
-        <v>1358.989868430335</v>
+        <v>224.7096343972572</v>
       </c>
       <c r="D2">
-        <v>36.8644797661697</v>
+        <v>14.99031802188523</v>
       </c>
       <c r="E2">
-        <v>0.192564239618814</v>
+        <v>0.8664901050924733</v>
       </c>
       <c r="F2">
-        <v>0.1252779262537151</v>
+        <v>0.855364280516846</v>
       </c>
       <c r="G2">
-        <v>89.51563936683232</v>
+        <v>58.90464254253096</v>
       </c>
       <c r="H2">
-        <v>13.88888888888889</v>
+        <v>8.386608544973544</v>
       </c>
       <c r="I2">
-        <v>0.250581756450024</v>
+        <v>0.8678324828815218</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>9.28809523809524</v>
+        <v>4.73816678004534</v>
       </c>
       <c r="C3">
-        <v>153.5173985890652</v>
+        <v>42.66476898952453</v>
       </c>
       <c r="D3">
-        <v>12.39021382337953</v>
+        <v>6.531827385159878</v>
       </c>
       <c r="E3">
-        <v>0.03634852765782681</v>
+        <v>0.7321869193214529</v>
       </c>
       <c r="F3">
-        <v>-0.04395576170402093</v>
+        <v>0.7098691625982405</v>
       </c>
       <c r="G3">
-        <v>17.46387395743525</v>
+        <v>8.831622888899272</v>
       </c>
       <c r="H3">
-        <v>7.044444444444444</v>
+        <v>3.799534920634933</v>
       </c>
       <c r="I3">
-        <v>0.0368868892004296</v>
+        <v>0.7323021588655974</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>35.8015873015873</v>
+        <v>19.56376118154327</v>
       </c>
       <c r="C4">
-        <v>2324.184144620812</v>
+        <v>621.5268394215173</v>
       </c>
       <c r="D4">
-        <v>48.20979303648598</v>
+        <v>24.93044001660455</v>
       </c>
       <c r="E4">
-        <v>0.004238875281809995</v>
+        <v>0.7337163382267701</v>
       </c>
       <c r="F4">
-        <v>-0.07874121844470583</v>
+        <v>0.711526033079001</v>
       </c>
       <c r="G4">
-        <v>17.42832607359704</v>
+        <v>9.410596220698149</v>
       </c>
       <c r="H4">
-        <v>31.50555555555555</v>
+        <v>17.369032539682</v>
       </c>
       <c r="I4">
-        <v>0.02928593934982482</v>
+        <v>0.7337254489870485</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>13.31746031746031</v>
+        <v>7.093999470899462</v>
       </c>
       <c r="C5">
-        <v>386.5201940035274</v>
+        <v>107.2273667275214</v>
       </c>
       <c r="D5">
-        <v>19.66011683595821</v>
+        <v>10.35506478625418</v>
       </c>
       <c r="E5">
-        <v>0.1497107465530833</v>
+        <v>0.7641150992411256</v>
       </c>
       <c r="F5">
-        <v>0.07885330876584018</v>
+        <v>0.7444580241778862</v>
       </c>
       <c r="G5">
-        <v>29.86622669604085</v>
+        <v>11.83427841832139</v>
       </c>
       <c r="H5">
-        <v>8.049999999999997</v>
+        <v>4.789012433862396</v>
       </c>
       <c r="I5">
-        <v>0.215911185649081</v>
+        <v>0.76548862857474</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>20.55809523809524</v>
+        <v>10.64943109565036</v>
       </c>
       <c r="C6">
-        <v>1055.802901410935</v>
+        <v>249.0321523839551</v>
       </c>
       <c r="D6">
-        <v>29.28115086549835</v>
+        <v>14.20191255247596</v>
       </c>
       <c r="E6">
-        <v>0.09571559727788351</v>
+        <v>0.7741271154704554</v>
       </c>
       <c r="F6">
-        <v>0.02035856371770714</v>
+        <v>0.7553043750929934</v>
       </c>
       <c r="G6">
-        <v>38.56851652347636</v>
+        <v>22.24528501761244</v>
       </c>
       <c r="H6">
-        <v>15.12222222222222</v>
+        <v>8.586047109788218</v>
       </c>
       <c r="I6">
-        <v>0.1331664426623398</v>
+        <v>0.7748371798272269</v>
       </c>
     </row>
   </sheetData>
@@ -2486,176 +2648,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>23.82523809523809</v>
+        <v>9.744504761904759</v>
       </c>
       <c r="C2">
-        <v>1358.989868430335</v>
+        <v>174.6017692153439</v>
       </c>
       <c r="D2">
-        <v>36.8644797661697</v>
+        <v>13.21369627376624</v>
       </c>
       <c r="E2">
-        <v>0.192564239618814</v>
+        <v>0.8962613956400378</v>
       </c>
       <c r="F2">
-        <v>0.1252779262537151</v>
+        <v>0.8876165119433743</v>
       </c>
       <c r="G2">
-        <v>89.51563936683232</v>
+        <v>56.14016639137427</v>
       </c>
       <c r="H2">
-        <v>13.88888888888889</v>
+        <v>8.945161111110981</v>
       </c>
       <c r="I2">
-        <v>0.250581756450024</v>
+        <v>0.8962613956400378</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>9.28809523809524</v>
+        <v>2.996882539682586</v>
       </c>
       <c r="C3">
-        <v>153.5173985890652</v>
+        <v>12.10389356684306</v>
       </c>
       <c r="D3">
-        <v>12.39021382337953</v>
+        <v>3.479065042054123</v>
       </c>
       <c r="E3">
-        <v>0.03634852765782681</v>
+        <v>0.9240220654859893</v>
       </c>
       <c r="F3">
-        <v>-0.04395576170402093</v>
+        <v>0.9176905709431551</v>
       </c>
       <c r="G3">
-        <v>17.46387395743525</v>
+        <v>4.85607386447903</v>
       </c>
       <c r="H3">
-        <v>7.044444444444444</v>
+        <v>3.131877777777873</v>
       </c>
       <c r="I3">
-        <v>0.0368868892004296</v>
+        <v>0.9240220654859893</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>35.8015873015873</v>
+        <v>10.21884021164004</v>
       </c>
       <c r="C4">
-        <v>2324.184144620812</v>
+        <v>141.4562546553184</v>
       </c>
       <c r="D4">
-        <v>48.20979303648598</v>
+        <v>11.89353835724754</v>
       </c>
       <c r="E4">
-        <v>0.004238875281809995</v>
+        <v>0.9393952327056326</v>
       </c>
       <c r="F4">
-        <v>-0.07874121844470583</v>
+        <v>0.934344835431102</v>
       </c>
       <c r="G4">
-        <v>17.42832607359704</v>
+        <v>4.368872825302105</v>
       </c>
       <c r="H4">
-        <v>31.50555555555555</v>
+        <v>10.70506666666506</v>
       </c>
       <c r="I4">
-        <v>0.02928593934982482</v>
+        <v>0.9393952327056326</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>13.31746031746031</v>
+        <v>6.1551809523809</v>
       </c>
       <c r="C5">
-        <v>386.5201940035274</v>
+        <v>96.16453862328039</v>
       </c>
       <c r="D5">
-        <v>19.66011683595821</v>
+        <v>9.806351952855882</v>
       </c>
       <c r="E5">
-        <v>0.1497107465530833</v>
+        <v>0.7884517419203456</v>
       </c>
       <c r="F5">
-        <v>0.07885330876584018</v>
+        <v>0.7708227204137078</v>
       </c>
       <c r="G5">
-        <v>29.86622669604085</v>
+        <v>9.099110063463067</v>
       </c>
       <c r="H5">
-        <v>8.049999999999997</v>
+        <v>4.25</v>
       </c>
       <c r="I5">
-        <v>0.215911185649081</v>
+        <v>0.7884517419203456</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>20.55809523809524</v>
+        <v>7.27885211640207</v>
       </c>
       <c r="C6">
-        <v>1055.802901410935</v>
+        <v>106.0816140151965</v>
       </c>
       <c r="D6">
-        <v>29.28115086549835</v>
+        <v>9.598162906480946</v>
       </c>
       <c r="E6">
-        <v>0.09571559727788351</v>
+        <v>0.8870326089380014</v>
       </c>
       <c r="F6">
-        <v>0.02035856371770714</v>
+        <v>0.8776186596828348</v>
       </c>
       <c r="G6">
-        <v>38.56851652347636</v>
+        <v>18.61605578615462</v>
       </c>
       <c r="H6">
-        <v>15.12222222222222</v>
+        <v>6.758026388888479</v>
       </c>
       <c r="I6">
-        <v>0.1331664426623398</v>
+        <v>0.8870326089380014</v>
       </c>
     </row>
   </sheetData>
@@ -2670,176 +2832,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>9.446195671540888</v>
+        <v>5.547003887826607</v>
       </c>
       <c r="C2">
-        <v>192.4685111243765</v>
+        <v>141.3121283968491</v>
       </c>
       <c r="D2">
-        <v>13.87330209879308</v>
+        <v>11.88747779795399</v>
       </c>
       <c r="E2">
-        <v>0.8856459770309817</v>
+        <v>0.9160402380519714</v>
       </c>
       <c r="F2">
-        <v>0.8761164751168968</v>
+        <v>0.9090435912229691</v>
       </c>
       <c r="G2">
-        <v>63.97577783465798</v>
+        <v>32.57685910751209</v>
       </c>
       <c r="H2">
-        <v>5.117490080971982</v>
+        <v>0.01996302596227473</v>
       </c>
       <c r="I2">
-        <v>0.8875182305539248</v>
+        <v>0.9188843216893332</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>6.703953457269698</v>
+        <v>1.103320129706783</v>
       </c>
       <c r="C3">
-        <v>142.6746175357007</v>
+        <v>4.993944690047625</v>
       </c>
       <c r="D3">
-        <v>11.94464807081819</v>
+        <v>2.234713558836484</v>
       </c>
       <c r="E3">
-        <v>0.1044102719447233</v>
+        <v>0.9686522687487583</v>
       </c>
       <c r="F3">
-        <v>0.02977779460678354</v>
+        <v>0.9660399578111548</v>
       </c>
       <c r="G3">
-        <v>14.26744988320347</v>
+        <v>1.556304175908757</v>
       </c>
       <c r="H3">
-        <v>2.823378514546043</v>
+        <v>0.004925863845340217</v>
       </c>
       <c r="I3">
-        <v>0.1237868851464625</v>
+        <v>0.9687861808663898</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>26.73518541278025</v>
+        <v>2.964023435646182</v>
       </c>
       <c r="C4">
-        <v>2598.207069926513</v>
+        <v>42.20397466564071</v>
       </c>
       <c r="D4">
-        <v>50.97261097811759</v>
+        <v>6.496458624946419</v>
       </c>
       <c r="E4">
-        <v>-0.1131620530966473</v>
+        <v>0.9819183529937157</v>
       </c>
       <c r="F4">
-        <v>-0.2059255575213679</v>
+        <v>0.9804115490765253</v>
       </c>
       <c r="G4">
-        <v>15.88588951691986</v>
+        <v>1.066088054274457</v>
       </c>
       <c r="H4">
-        <v>10.09913308669061</v>
+        <v>0.007191736280468319</v>
       </c>
       <c r="I4">
-        <v>0.08419040624466256</v>
+        <v>0.9821539730635134</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>6.362135142658091</v>
+        <v>3.795172832343855</v>
       </c>
       <c r="C5">
-        <v>105.3601690489118</v>
+        <v>87.28676004046827</v>
       </c>
       <c r="D5">
-        <v>10.2645101709196</v>
+        <v>9.342738358771921</v>
       </c>
       <c r="E5">
-        <v>0.7682226676031767</v>
+        <v>0.8079815875546916</v>
       </c>
       <c r="F5">
-        <v>0.7489078899034414</v>
+        <v>0.7919800531842492</v>
       </c>
       <c r="G5">
-        <v>8.703613141130717</v>
+        <v>6.130674094144062</v>
       </c>
       <c r="H5">
-        <v>3.207255368886877</v>
+        <v>0.007198414576095047</v>
       </c>
       <c r="I5">
-        <v>0.7708767769947198</v>
+        <v>0.8105557421850719</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>12.31186742106223</v>
+        <v>3.352380071380857</v>
       </c>
       <c r="C6">
-        <v>759.6775919088756</v>
+        <v>68.94920194825141</v>
       </c>
       <c r="D6">
-        <v>21.76376782966211</v>
+        <v>7.490347085127204</v>
       </c>
       <c r="E6">
-        <v>0.4112792158705586</v>
+        <v>0.9186481118372842</v>
       </c>
       <c r="F6">
-        <v>0.3622191505264385</v>
+        <v>0.9118687878237246</v>
       </c>
       <c r="G6">
-        <v>25.70818259397801</v>
+        <v>10.33248135795984</v>
       </c>
       <c r="H6">
-        <v>5.311814262773879</v>
+        <v>0.009819760166044578</v>
       </c>
       <c r="I6">
-        <v>0.4665930747349424</v>
+        <v>0.9200950544510771</v>
       </c>
     </row>
   </sheetData>
@@ -2854,21 +3016,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -2882,7 +3044,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -2896,7 +3058,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -2910,7 +3072,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -2934,36 +3096,1140 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>6.385833333333335</v>
+      </c>
+      <c r="C2">
+        <v>139.9965470238095</v>
+      </c>
+      <c r="D2">
+        <v>11.83201365042356</v>
+      </c>
+      <c r="E2">
+        <v>0.9168218829125843</v>
+      </c>
+      <c r="F2">
+        <v>0.9098903731552996</v>
+      </c>
+      <c r="G2">
+        <v>30.71379985486174</v>
+      </c>
+      <c r="H2">
+        <v>0.8333333333333357</v>
+      </c>
+      <c r="I2">
+        <v>0.9173606543729681</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>1.738095238095237</v>
+      </c>
+      <c r="C3">
+        <v>7.060634920634918</v>
+      </c>
+      <c r="D3">
+        <v>2.657185526197769</v>
+      </c>
+      <c r="E3">
+        <v>0.9556793477516298</v>
+      </c>
+      <c r="F3">
+        <v>0.9519859600642656</v>
+      </c>
+      <c r="G3">
+        <v>2.401144235243257</v>
+      </c>
+      <c r="H3">
+        <v>0.7499999999999929</v>
+      </c>
+      <c r="I3">
+        <v>0.9558958453142707</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>6.759285714285718</v>
+      </c>
+      <c r="C4">
+        <v>87.81028650793662</v>
+      </c>
+      <c r="D4">
+        <v>9.370714300838364</v>
+      </c>
+      <c r="E4">
+        <v>0.9623790266974587</v>
+      </c>
+      <c r="F4">
+        <v>0.9592439455889136</v>
+      </c>
+      <c r="G4">
+        <v>2.454784806808297</v>
+      </c>
+      <c r="H4">
+        <v>5.683333333333337</v>
+      </c>
+      <c r="I4">
+        <v>0.9625806183610094</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>5.094999999999998</v>
+      </c>
+      <c r="C5">
+        <v>91.03139563492061</v>
+      </c>
+      <c r="D5">
+        <v>9.541037450661255</v>
+      </c>
+      <c r="E5">
+        <v>0.7997439237704067</v>
+      </c>
+      <c r="F5">
+        <v>0.7830559174179406</v>
+      </c>
+      <c r="G5">
+        <v>7.357244732313917</v>
+      </c>
+      <c r="H5">
+        <v>0.62083333333333</v>
+      </c>
+      <c r="I5">
+        <v>0.799940969249874</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>4.994553571428572</v>
+      </c>
+      <c r="C6">
+        <v>81.47471602182542</v>
+      </c>
+      <c r="D6">
+        <v>8.350237732030237</v>
+      </c>
+      <c r="E6">
+        <v>0.9086560452830199</v>
+      </c>
+      <c r="F6">
+        <v>0.901044049056605</v>
+      </c>
+      <c r="G6">
+        <v>10.7317434073068</v>
+      </c>
+      <c r="H6">
+        <v>1.971874999999999</v>
+      </c>
+      <c r="I6">
+        <v>0.9089445218245306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>29.58285714285715</v>
+      </c>
+      <c r="C2">
+        <v>1683.093485714286</v>
+      </c>
+      <c r="D2">
+        <v>41.02552236979178</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="G2">
+        <v>140.2043443286067</v>
+      </c>
+      <c r="H2">
+        <v>21.79</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>9.354081632653058</v>
+      </c>
+      <c r="C3">
+        <v>159.3080102040817</v>
+      </c>
+      <c r="D3">
+        <v>12.62172770281793</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="G3">
+        <v>17.74311782890865</v>
+      </c>
+      <c r="H3">
+        <v>7.064285714285703</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>32.10306122448979</v>
+      </c>
+      <c r="C4">
+        <v>2334.078010204082</v>
+      </c>
+      <c r="D4">
+        <v>48.31229667697534</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="G4">
+        <v>16.6410616884347</v>
+      </c>
+      <c r="H4">
+        <v>22.53571428571428</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>16.16020408163265</v>
+      </c>
+      <c r="C5">
+        <v>454.5749489795918</v>
+      </c>
+      <c r="D5">
+        <v>21.32076333013412</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="G5">
+        <v>32.8731008901733</v>
+      </c>
+      <c r="H5">
+        <v>13.29285714285713</v>
+      </c>
+      <c r="I5">
+        <v>-2.220446049250313E-16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>21.80005102040816</v>
+      </c>
+      <c r="C6">
+        <v>1157.76361377551</v>
+      </c>
+      <c r="D6">
+        <v>30.8200775199298</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="G6">
+        <v>51.86540618403083</v>
+      </c>
+      <c r="H6">
+        <v>16.17071428571428</v>
+      </c>
+      <c r="I6">
+        <v>-5.551115123125783E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>11.30476428571428</v>
+      </c>
+      <c r="C2">
+        <v>225.6083918291567</v>
+      </c>
+      <c r="D2">
+        <v>15.02026603722972</v>
+      </c>
+      <c r="E2">
+        <v>0.865956113701307</v>
+      </c>
+      <c r="F2">
+        <v>0.8547857898430826</v>
+      </c>
+      <c r="G2">
+        <v>55.43836192495155</v>
+      </c>
+      <c r="H2">
+        <v>8.551895833333329</v>
+      </c>
+      <c r="I2">
+        <v>0.870053822148988</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>4.348476190476187</v>
+      </c>
+      <c r="C3">
+        <v>30.45792862003967</v>
+      </c>
+      <c r="D3">
+        <v>5.518870230404016</v>
+      </c>
+      <c r="E3">
+        <v>0.8088110661791487</v>
+      </c>
+      <c r="F3">
+        <v>0.7928786550274111</v>
+      </c>
+      <c r="G3">
+        <v>7.648256241692383</v>
+      </c>
+      <c r="H3">
+        <v>3.654999999999987</v>
+      </c>
+      <c r="I3">
+        <v>0.8097421870952792</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>17.01513988095239</v>
+      </c>
+      <c r="C4">
+        <v>425.9112810809776</v>
+      </c>
+      <c r="D4">
+        <v>20.63761810580324</v>
+      </c>
+      <c r="E4">
+        <v>0.8175248302674606</v>
+      </c>
+      <c r="F4">
+        <v>0.8023185661230823</v>
+      </c>
+      <c r="G4">
+        <v>7.808682415642464</v>
+      </c>
+      <c r="H4">
+        <v>15.90499999999994</v>
+      </c>
+      <c r="I4">
+        <v>0.8177246363479393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>7.113553571428571</v>
+      </c>
+      <c r="C5">
+        <v>108.1679850183531</v>
+      </c>
+      <c r="D5">
+        <v>10.40038388802803</v>
+      </c>
+      <c r="E5">
+        <v>0.7620458732687239</v>
+      </c>
+      <c r="F5">
+        <v>0.7422163627077842</v>
+      </c>
+      <c r="G5">
+        <v>12.66473414599422</v>
+      </c>
+      <c r="H5">
+        <v>5.110416666666669</v>
+      </c>
+      <c r="I5">
+        <v>0.7673903392117379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>9.945483482142858</v>
+      </c>
+      <c r="C6">
+        <v>197.5363966371318</v>
+      </c>
+      <c r="D6">
+        <v>12.89428456536625</v>
+      </c>
+      <c r="E6">
+        <v>0.81358447085416</v>
+      </c>
+      <c r="F6">
+        <v>0.79804984342534</v>
+      </c>
+      <c r="G6">
+        <v>20.89000868207015</v>
+      </c>
+      <c r="H6">
+        <v>8.305578124999982</v>
+      </c>
+      <c r="I6">
+        <v>0.8162277462009861</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>23.82523809523809</v>
+      </c>
+      <c r="C2">
+        <v>1358.989868430335</v>
+      </c>
+      <c r="D2">
+        <v>36.8644797661697</v>
+      </c>
+      <c r="E2">
+        <v>0.192564239618814</v>
+      </c>
+      <c r="F2">
+        <v>0.1252779262537151</v>
+      </c>
+      <c r="G2">
+        <v>89.51563936683232</v>
+      </c>
+      <c r="H2">
+        <v>13.88888888888889</v>
+      </c>
+      <c r="I2">
+        <v>0.250581756450024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>9.28809523809524</v>
+      </c>
+      <c r="C3">
+        <v>153.5173985890652</v>
+      </c>
+      <c r="D3">
+        <v>12.39021382337953</v>
+      </c>
+      <c r="E3">
+        <v>0.03634852765782681</v>
+      </c>
+      <c r="F3">
+        <v>-0.04395576170402093</v>
+      </c>
+      <c r="G3">
+        <v>17.46387395743525</v>
+      </c>
+      <c r="H3">
+        <v>7.044444444444444</v>
+      </c>
+      <c r="I3">
+        <v>0.0368868892004296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>35.8015873015873</v>
+      </c>
+      <c r="C4">
+        <v>2324.184144620812</v>
+      </c>
+      <c r="D4">
+        <v>48.20979303648598</v>
+      </c>
+      <c r="E4">
+        <v>0.004238875281809995</v>
+      </c>
+      <c r="F4">
+        <v>-0.07874121844470583</v>
+      </c>
+      <c r="G4">
+        <v>17.42832607359704</v>
+      </c>
+      <c r="H4">
+        <v>31.50555555555555</v>
+      </c>
+      <c r="I4">
+        <v>0.02928593934982482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>13.31746031746031</v>
+      </c>
+      <c r="C5">
+        <v>386.5201940035274</v>
+      </c>
+      <c r="D5">
+        <v>19.66011683595821</v>
+      </c>
+      <c r="E5">
+        <v>0.1497107465530833</v>
+      </c>
+      <c r="F5">
+        <v>0.07885330876584018</v>
+      </c>
+      <c r="G5">
+        <v>29.86622669604085</v>
+      </c>
+      <c r="H5">
+        <v>8.049999999999997</v>
+      </c>
+      <c r="I5">
+        <v>0.215911185649081</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>20.55809523809524</v>
+      </c>
+      <c r="C6">
+        <v>1055.802901410935</v>
+      </c>
+      <c r="D6">
+        <v>29.28115086549835</v>
+      </c>
+      <c r="E6">
+        <v>0.09571559727788351</v>
+      </c>
+      <c r="F6">
+        <v>0.02035856371770714</v>
+      </c>
+      <c r="G6">
+        <v>38.56851652347636</v>
+      </c>
+      <c r="H6">
+        <v>15.12222222222222</v>
+      </c>
+      <c r="I6">
+        <v>0.1331664426623398</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>23.82523809523809</v>
+      </c>
+      <c r="C2">
+        <v>1358.989868430335</v>
+      </c>
+      <c r="D2">
+        <v>36.8644797661697</v>
+      </c>
+      <c r="E2">
+        <v>0.192564239618814</v>
+      </c>
+      <c r="F2">
+        <v>0.1252779262537151</v>
+      </c>
+      <c r="G2">
+        <v>89.51563936683232</v>
+      </c>
+      <c r="H2">
+        <v>13.88888888888889</v>
+      </c>
+      <c r="I2">
+        <v>0.250581756450024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>9.28809523809524</v>
+      </c>
+      <c r="C3">
+        <v>153.5173985890652</v>
+      </c>
+      <c r="D3">
+        <v>12.39021382337953</v>
+      </c>
+      <c r="E3">
+        <v>0.03634852765782681</v>
+      </c>
+      <c r="F3">
+        <v>-0.04395576170402093</v>
+      </c>
+      <c r="G3">
+        <v>17.46387395743525</v>
+      </c>
+      <c r="H3">
+        <v>7.044444444444444</v>
+      </c>
+      <c r="I3">
+        <v>0.0368868892004296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>35.8015873015873</v>
+      </c>
+      <c r="C4">
+        <v>2324.184144620812</v>
+      </c>
+      <c r="D4">
+        <v>48.20979303648598</v>
+      </c>
+      <c r="E4">
+        <v>0.004238875281809995</v>
+      </c>
+      <c r="F4">
+        <v>-0.07874121844470583</v>
+      </c>
+      <c r="G4">
+        <v>17.42832607359704</v>
+      </c>
+      <c r="H4">
+        <v>31.50555555555555</v>
+      </c>
+      <c r="I4">
+        <v>0.02928593934982482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>13.31746031746031</v>
+      </c>
+      <c r="C5">
+        <v>386.5201940035274</v>
+      </c>
+      <c r="D5">
+        <v>19.66011683595821</v>
+      </c>
+      <c r="E5">
+        <v>0.1497107465530833</v>
+      </c>
+      <c r="F5">
+        <v>0.07885330876584018</v>
+      </c>
+      <c r="G5">
+        <v>29.86622669604085</v>
+      </c>
+      <c r="H5">
+        <v>8.049999999999997</v>
+      </c>
+      <c r="I5">
+        <v>0.215911185649081</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>20.55809523809524</v>
+      </c>
+      <c r="C6">
+        <v>1055.802901410935</v>
+      </c>
+      <c r="D6">
+        <v>29.28115086549835</v>
+      </c>
+      <c r="E6">
+        <v>0.09571559727788351</v>
+      </c>
+      <c r="F6">
+        <v>0.02035856371770714</v>
+      </c>
+      <c r="G6">
+        <v>38.56851652347636</v>
+      </c>
+      <c r="H6">
+        <v>15.12222222222222</v>
+      </c>
+      <c r="I6">
+        <v>0.1331664426623398</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>9.446195671540888</v>
+      </c>
+      <c r="C2">
+        <v>192.4685111243765</v>
+      </c>
+      <c r="D2">
+        <v>13.87330209879308</v>
+      </c>
+      <c r="E2">
+        <v>0.8856459770309817</v>
+      </c>
+      <c r="F2">
+        <v>0.8761164751168968</v>
+      </c>
+      <c r="G2">
+        <v>63.97577783465798</v>
+      </c>
+      <c r="H2">
+        <v>5.117490080971982</v>
+      </c>
+      <c r="I2">
+        <v>0.8875182305539248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>6.703953457269698</v>
+      </c>
+      <c r="C3">
+        <v>142.6746175357007</v>
+      </c>
+      <c r="D3">
+        <v>11.94464807081819</v>
+      </c>
+      <c r="E3">
+        <v>0.1044102719447233</v>
+      </c>
+      <c r="F3">
+        <v>0.02977779460678354</v>
+      </c>
+      <c r="G3">
+        <v>14.26744988320347</v>
+      </c>
+      <c r="H3">
+        <v>2.823378514546043</v>
+      </c>
+      <c r="I3">
+        <v>0.1237868851464625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>26.73518541278025</v>
+      </c>
+      <c r="C4">
+        <v>2598.207069926513</v>
+      </c>
+      <c r="D4">
+        <v>50.97261097811759</v>
+      </c>
+      <c r="E4">
+        <v>-0.1131620530966473</v>
+      </c>
+      <c r="F4">
+        <v>-0.2059255575213679</v>
+      </c>
+      <c r="G4">
+        <v>15.88588951691986</v>
+      </c>
+      <c r="H4">
+        <v>10.09913308669061</v>
+      </c>
+      <c r="I4">
+        <v>0.08419040624466256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>6.362135142658091</v>
+      </c>
+      <c r="C5">
+        <v>105.3601690489118</v>
+      </c>
+      <c r="D5">
+        <v>10.2645101709196</v>
+      </c>
+      <c r="E5">
+        <v>0.7682226676031767</v>
+      </c>
+      <c r="F5">
+        <v>0.7489078899034414</v>
+      </c>
+      <c r="G5">
+        <v>8.703613141130717</v>
+      </c>
+      <c r="H5">
+        <v>3.207255368886877</v>
+      </c>
+      <c r="I5">
+        <v>0.7708767769947198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>12.31186742106223</v>
+      </c>
+      <c r="C6">
+        <v>759.6775919088756</v>
+      </c>
+      <c r="D6">
+        <v>21.76376782966211</v>
+      </c>
+      <c r="E6">
+        <v>0.4112792158705586</v>
+      </c>
+      <c r="F6">
+        <v>0.3622191505264385</v>
+      </c>
+      <c r="G6">
+        <v>25.70818259397801</v>
+      </c>
+      <c r="H6">
+        <v>5.311814262773879</v>
+      </c>
+      <c r="I6">
+        <v>0.4665930747349424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>37</v>
       </c>
       <c r="B2">
         <v>10.08782696009768</v>
@@ -2992,7 +4258,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>1.136230829833945</v>
@@ -3021,7 +4287,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>2.983787378796376</v>
@@ -3050,7 +4316,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>3.877356776757563</v>
@@ -3079,7 +4345,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>4.52130048637139</v>
@@ -3118,36 +4384,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>17.95974911175558</v>
@@ -3176,7 +4442,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>8.696079553061745</v>
@@ -3205,7 +4471,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>33.11990447568959</v>
@@ -3234,7 +4500,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>10.56976793335318</v>
@@ -3263,7 +4529,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>17.58637526846502</v>
@@ -3302,36 +4568,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>17.95978215412796</v>
@@ -3360,7 +4626,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>8.696083677245394</v>
@@ -3389,7 +4655,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>33.11988792692743</v>
@@ -3418,7 +4684,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>10.56978718705986</v>
@@ -3447,7 +4713,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>17.58638523634016</v>
@@ -3486,36 +4752,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>17.95975043968054</v>
@@ -3544,7 +4810,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>8.696082729744493</v>
@@ -3573,7 +4839,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>33.11989984783138</v>
@@ -3602,7 +4868,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>10.56976959922311</v>
@@ -3631,7 +4897,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>17.58637565411988</v>
@@ -3670,36 +4936,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>17.95977618491867</v>
@@ -3728,7 +4994,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>8.696084810296183</v>
@@ -3757,7 +5023,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>33.11988844469191</v>
@@ -3786,7 +5052,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>10.56978426526622</v>
@@ -3815,7 +5081,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>17.58638342629325</v>
@@ -3854,176 +5120,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>10.18400410812769</v>
+        <v>17.57558243910309</v>
       </c>
       <c r="C2">
-        <v>189.9897117553252</v>
+        <v>471.6994952662943</v>
       </c>
       <c r="D2">
-        <v>13.78367555317976</v>
+        <v>21.71864395551192</v>
       </c>
       <c r="E2">
-        <v>0.8871187409565098</v>
+        <v>0.7197425459310656</v>
       </c>
       <c r="F2">
-        <v>0.8532543632434627</v>
+        <v>0.6963877580919877</v>
       </c>
       <c r="G2">
-        <v>61.13097625092665</v>
+        <v>102.9482028406972</v>
       </c>
       <c r="H2">
-        <v>7.830349026907371</v>
+        <v>14.69892059121153</v>
       </c>
       <c r="I2">
-        <v>0.8871187409565098</v>
+        <v>0.7200865743816629</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>7.668926701638179</v>
+        <v>7.688261223134083</v>
       </c>
       <c r="C3">
-        <v>137.1628170144274</v>
+        <v>170.5347770923641</v>
       </c>
       <c r="D3">
-        <v>11.71165304363254</v>
+        <v>13.05889647299358</v>
       </c>
       <c r="E3">
-        <v>0.139008661028941</v>
+        <v>-0.07047208030469032</v>
       </c>
       <c r="F3">
-        <v>-0.1192887406623766</v>
+        <v>-0.1596780869967478</v>
       </c>
       <c r="G3">
-        <v>15.07332819570342</v>
+        <v>16.31690754732949</v>
       </c>
       <c r="H3">
-        <v>4.656081911799802</v>
+        <v>3.656045849813388</v>
       </c>
       <c r="I3">
-        <v>0.1390086610289412</v>
+        <v>-0.00208515413196797</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>33.34258327838067</v>
+        <v>29.10473155618492</v>
       </c>
       <c r="C4">
-        <v>2086.174194799422</v>
+        <v>2551.394555507617</v>
       </c>
       <c r="D4">
-        <v>45.67465593520571</v>
+        <v>50.51133096155373</v>
       </c>
       <c r="E4">
-        <v>0.1062105954988986</v>
+        <v>-0.09310594776758685</v>
       </c>
       <c r="F4">
-        <v>-0.1619262258514318</v>
+        <v>-0.1841981100815524</v>
       </c>
       <c r="G4">
-        <v>16.7996861714309</v>
+        <v>16.40328155860542</v>
       </c>
       <c r="H4">
-        <v>22.61631116938514</v>
+        <v>16.05000000000001</v>
       </c>
       <c r="I4">
-        <v>0.1062105954988986</v>
+        <v>-0.02114552817064341</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>6.724952823598907</v>
+        <v>10.71747962997509</v>
       </c>
       <c r="C5">
-        <v>103.3948511812794</v>
+        <v>195.444764653271</v>
       </c>
       <c r="D5">
-        <v>10.16832587898713</v>
+        <v>13.9801561026074</v>
       </c>
       <c r="E5">
-        <v>0.7725460863750298</v>
+        <v>0.5700494162909855</v>
       </c>
       <c r="F5">
-        <v>0.7043099122875387</v>
+        <v>0.534220200981901</v>
       </c>
       <c r="G5">
-        <v>9.331852024183938</v>
+        <v>15.75384120717569</v>
       </c>
       <c r="H5">
-        <v>3.850313105553319</v>
+        <v>9.837635580519869</v>
       </c>
       <c r="I5">
-        <v>0.7725460863750298</v>
+        <v>0.5734645982343662</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>14.48011672793636</v>
+        <v>16.2715137120993</v>
       </c>
       <c r="C6">
-        <v>629.1803936876136</v>
+        <v>847.2683981298865</v>
       </c>
       <c r="D6">
-        <v>20.33457760275129</v>
+        <v>24.81725687316666</v>
       </c>
       <c r="E6">
-        <v>0.4762210209648448</v>
+        <v>0.2815534835374435</v>
       </c>
       <c r="F6">
-        <v>0.3190873272542982</v>
+        <v>0.2216829404988971</v>
       </c>
       <c r="G6">
-        <v>25.58396066056122</v>
+        <v>37.85555828845195</v>
       </c>
       <c r="H6">
-        <v>9.738263803411408</v>
+        <v>11.0606505053862</v>
       </c>
       <c r="I6">
-        <v>0.4762210209648448</v>
+        <v>0.3175801225783544</v>
       </c>
     </row>
   </sheetData>
@@ -4038,176 +5304,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>27.70739324299376</v>
+        <v>29.02302618033499</v>
       </c>
       <c r="C2">
-        <v>1454.16764252894</v>
+        <v>2468.627031331897</v>
       </c>
       <c r="D2">
-        <v>38.1335500908182</v>
+        <v>49.6852798254362</v>
       </c>
       <c r="E2">
-        <v>0.1360149303222999</v>
+        <v>-0.4667200914774139</v>
       </c>
       <c r="F2">
-        <v>-0.1231805905810099</v>
+        <v>-0.5889467657671983</v>
       </c>
       <c r="G2">
-        <v>133.9881443826817</v>
+        <v>86.81251050841237</v>
       </c>
       <c r="H2">
-        <v>21.87642648980349</v>
+        <v>12.67138259041958</v>
       </c>
       <c r="I2">
-        <v>0.1360149303223001</v>
+        <v>-0.2805300512685571</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>9.230217882112072</v>
+        <v>7.98719930545519</v>
       </c>
       <c r="C3">
-        <v>157.7967482820635</v>
+        <v>181.1869010248145</v>
       </c>
       <c r="D3">
-        <v>12.56171756894986</v>
+        <v>13.46056837673709</v>
       </c>
       <c r="E3">
-        <v>0.009486415153149741</v>
+        <v>-0.137337041575655</v>
       </c>
       <c r="F3">
-        <v>-0.2876676603009054</v>
+        <v>-0.2321151283736262</v>
       </c>
       <c r="G3">
-        <v>17.56462955776416</v>
+        <v>17.09435623689846</v>
       </c>
       <c r="H3">
-        <v>6.969089569453757</v>
+        <v>3.83654083060609</v>
       </c>
       <c r="I3">
-        <v>0.00948641515314963</v>
+        <v>0.007181389337885924</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>32.09597830566354</v>
+        <v>29.62569832963566</v>
       </c>
       <c r="C4">
-        <v>2333.922165194635</v>
+        <v>2557.005530932233</v>
       </c>
       <c r="D4">
-        <v>48.31068375830169</v>
+        <v>50.56684220842975</v>
       </c>
       <c r="E4">
-        <v>6.676940906247264E-05</v>
+        <v>-0.09550988431130403</v>
       </c>
       <c r="F4">
-        <v>-0.2999131997682187</v>
+        <v>-0.1868023746705794</v>
       </c>
       <c r="G4">
-        <v>16.63859364620697</v>
+        <v>16.62434963563749</v>
       </c>
       <c r="H4">
-        <v>22.53272535000156</v>
+        <v>16.05000000000001</v>
       </c>
       <c r="I4">
-        <v>6.676940906247264E-05</v>
+        <v>-0.0112969191371759</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>15.29171221504644</v>
+        <v>14.54411275022233</v>
       </c>
       <c r="C5">
-        <v>405.4865126565633</v>
+        <v>465.1066169338093</v>
       </c>
       <c r="D5">
-        <v>20.13669567373364</v>
+        <v>21.56633063211749</v>
       </c>
       <c r="E5">
-        <v>0.1079875528407799</v>
+        <v>-0.02316816616898598</v>
       </c>
       <c r="F5">
-        <v>-0.1596161813069863</v>
+        <v>-0.1084321800164014</v>
       </c>
       <c r="G5">
-        <v>30.75121062888524</v>
+        <v>32.92265100715431</v>
       </c>
       <c r="H5">
-        <v>12.7769672298138</v>
+        <v>9.409763831879488</v>
       </c>
       <c r="I5">
-        <v>0.10798755284078</v>
+        <v>0.09255589061204739</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>21.08132541145396</v>
+        <v>20.29500914141204</v>
       </c>
       <c r="C6">
-        <v>1087.843267165551</v>
+        <v>1417.981520055688</v>
       </c>
       <c r="D6">
-        <v>29.78566177295085</v>
+        <v>33.81975526068013</v>
       </c>
       <c r="E6">
-        <v>0.06338891693132301</v>
+        <v>-0.1806837958833397</v>
       </c>
       <c r="F6">
-        <v>-0.2175944079892801</v>
+        <v>-0.2790741122069513</v>
       </c>
       <c r="G6">
-        <v>49.73564455388451</v>
+        <v>38.36346684702566</v>
       </c>
       <c r="H6">
-        <v>16.03880215976815</v>
+        <v>10.49192181322629</v>
       </c>
       <c r="I6">
-        <v>0.06338891693132304</v>
+        <v>-0.04802242261394993</v>
       </c>
     </row>
   </sheetData>
@@ -4222,176 +5488,176 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>24.10753027245121</v>
+        <v>17.54773599470262</v>
       </c>
       <c r="C2">
-        <v>1136.101462228707</v>
+        <v>527.6794416927642</v>
       </c>
       <c r="D2">
-        <v>33.70610422799863</v>
+        <v>22.97127427228982</v>
       </c>
       <c r="E2">
-        <v>0.3249920626087158</v>
+        <v>0.6864823931816104</v>
       </c>
       <c r="F2">
-        <v>0.2687414011594421</v>
+        <v>0.6603559259467446</v>
       </c>
       <c r="G2">
-        <v>91.66700786904762</v>
+        <v>120.9773351579284</v>
       </c>
       <c r="H2">
-        <v>15.17144749610551</v>
+        <v>9.883399766959476</v>
       </c>
       <c r="I2">
-        <v>0.3894790409600025</v>
+        <v>0.7200502657784622</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>8.859216086972451</v>
+        <v>8.402487892596605</v>
       </c>
       <c r="C3">
-        <v>158.0302394259915</v>
+        <v>223.3139069413178</v>
       </c>
       <c r="D3">
-        <v>12.57100789220942</v>
+        <v>14.94369120871138</v>
       </c>
       <c r="E3">
-        <v>0.008020756623934089</v>
+        <v>-0.4017745037129103</v>
       </c>
       <c r="F3">
-        <v>-0.07464418032407139</v>
+        <v>-0.5185890456889863</v>
       </c>
       <c r="G3">
-        <v>16.91965977373152</v>
+        <v>18.28151887591551</v>
       </c>
       <c r="H3">
-        <v>7.26766547681919</v>
+        <v>3.957352310113002</v>
       </c>
       <c r="I3">
-        <v>0.01422470829512235</v>
+        <v>-0.08325713135512935</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4">
-        <v>182.298092612082</v>
+        <v>29.3968752076566</v>
       </c>
       <c r="C4">
-        <v>35566.65742346342</v>
+        <v>2875.654851574982</v>
       </c>
       <c r="D4">
-        <v>188.5912442916251</v>
+        <v>53.62513264855372</v>
       </c>
       <c r="E4">
-        <v>-14.23799001917405</v>
+        <v>-0.232030308757138</v>
       </c>
       <c r="F4">
-        <v>-15.50782252077188</v>
+        <v>-0.3346995011535663</v>
       </c>
       <c r="G4">
-        <v>67.54990255135532</v>
+        <v>17.0217034305537</v>
       </c>
       <c r="H4">
-        <v>192.8329852518807</v>
+        <v>11.1447284598116</v>
       </c>
       <c r="I4">
-        <v>6.49367494331976E-06</v>
+        <v>-0.06138524754905683</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>12.23250900181676</v>
+        <v>25.1339378238342</v>
       </c>
       <c r="C5">
-        <v>248.880094989379</v>
+        <v>2347.462801876008</v>
       </c>
       <c r="D5">
-        <v>15.77593404491091</v>
+        <v>48.45062230638538</v>
       </c>
       <c r="E5">
-        <v>0.4524993171135955</v>
+        <v>-4.164083078369102</v>
       </c>
       <c r="F5">
-        <v>0.4068742602063952</v>
+        <v>-4.594423334899861</v>
       </c>
       <c r="G5">
-        <v>16.02764055785559</v>
+        <v>67.96000940803145</v>
       </c>
       <c r="H5">
-        <v>7.75906641742332</v>
+        <v>7.79414109206855</v>
       </c>
       <c r="I5">
-        <v>0.5691504293723822</v>
+        <v>-3.387758718696268</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>56.87433699333061</v>
+        <v>20.1202592296975</v>
       </c>
       <c r="C6">
-        <v>9277.417305026873</v>
+        <v>1493.527750521268</v>
       </c>
       <c r="D6">
-        <v>62.66107261418601</v>
+        <v>34.99768010898507</v>
       </c>
       <c r="E6">
-        <v>-3.36311947070695</v>
+        <v>-1.027851374414385</v>
       </c>
       <c r="F6">
-        <v>-3.726712759932529</v>
+        <v>-1.196838988948917</v>
       </c>
       <c r="G6">
-        <v>48.04105268799751</v>
+        <v>56.06014171810725</v>
       </c>
       <c r="H6">
-        <v>55.75779116055718</v>
+        <v>8.194905407238158</v>
       </c>
       <c r="I6">
-        <v>0.2432151680756126</v>
+        <v>-0.7030877079554979</v>
       </c>
     </row>
   </sheetData>
